--- a/기획안/국가별_각색_기획안.xlsx
+++ b/기획안/국가별_각색_기획안.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 가상 아마존 주 ‘타피라주(Estado de Tapirá)’와 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’에서 시작해 브라질리아로. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회. 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
+          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 상파울루 파우리스타 대로의 대형 로펌에서 시작해 가상 아마존 주 ‘타피라주(Estado de Tapirá)’의 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’(주인공의 고향)와 강변 파벨라 ‘빌라 히반세이라(Vila Ribanceira)’, 아루아칸 원주민 영토를 거쳐 브라질리아로. 교도소에서 태어난 가상 조직범죄 파벌(facção) ‘이르만다지 두 노르치(Irmandade do Norte)’가 강의 코카인 경로·불법 금광·숲속 비행장을 잇고, 도시에서는 전·현직 경찰 출신 민병대(milícia)와 파벨라의 통제권을 다툰다. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회, 헌법기관으로서의 공설변호인청(Defensoria Pública). 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>노바 카라자이 노동·환경 변호사 → 전국 인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 땅과노동당(PTT) 창당 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
+          <t>상파울루 대형 로펌 ‘케이로스 타바리스’ 기업소송 변호사(프라두 그룹 담당) → 사직 → 공설변호인 시험 합격, 노바 카라자이 공설변호인(Defensoria Pública)·인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 출마를 위한 공직 사퇴(desincompatibilização)·땅과노동당(PTT) 창당 참여 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 7부 민병대·파벌 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
+          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 7부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 6부 테러와 암살이 같은 돈(전 재무차관 오타실리우)에서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
+          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 6부 테러와 암살의 돈이 이르만다지 두 노르치의 주유소 체인·무허가 핀테크 세탁망을 거쳐 전 재무차관 오타실리우에게서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 그의 법정에는 공설변호인이 붙는다 — 하파가 지킨 ‘누구나 변호받을 권리’다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>무게중심을 아마존과 제도 공격 두 곳에 둔다. 1~2부를 수은 강마을·불법 비행장·원주민 영토 ‘기준일’ 법안까지 포함한 아마존 서사로 확장하고, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
+          <t>무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다.</t>
+          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다. [4차 개정 추가] 파벨라 주민을 범죄의 배경으로만 소비하지 말 것: 빌라 히반세이라에는 파벌과 민병대 말고도 일하는 어머니, 교회, 삼바·펑크 모임, 공동체 라디오, 대학에 간 아이(카이우)와 변호인이 되려는 청년(제페르송)이 있다. 가상 파벌 ‘이르만다지 두 노르치’는 교도소 태생 파벌이라는 구조만 참고하고 코만두 베르멜류(CV)·PCC의 이름·상징·수감자 규약·실존 지도자·실제 사건을 복제하지 않으며, 멕시코식 카르텔 액션 문법(참수·거물 두목의 쇼)으로 그리지 않는다. 5부 경찰 작전은 2025년 리우 작전을 연상시키므로 지명·날짜·사망자 수·작전명을 겹치지 않게 하고, 경찰관 개인도 일괴암적 악으로 그리지 않는다. 공설변호인을 이상화된 영웅으로 만들지 않는다: 하루 수십 건의 구금심사, 만성 인력 부족, 이기지 못하는 사건, 조직 내부의 신중론과 관료주의, 하파 자신의 조급함까지 보여 준다. 대형 로펌 변호사들도 만화적 악당이 아니라 ‘모든 사람은 변호받을 권리가 있다’는 같은 원칙을 반대편에서 말하는 사람들로 그리고, 오타비우의 선택에는 설득력 있는 논리를 준다. 로펌·기업 이름은 모두 가상이며 실존 로펌을 연상시키는 이름·주소·사건을 쓰지 않는다.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -25654,7 +25654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25699,11 +25699,11 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2015년 아마존의 광산도시에서 수은에 중독된 강마을과 원주민 영토를 변호하던 젊은 변호사 하파엘 멘지스는, 불법 채굴의 돈줄을 건드린 스승이 날조된 혐의로 구금 중 숨지자 법정 밖으로 나선다. 신생 노동자 정당과 주지사직을 거쳐 대통령에 오른 그는 대선 불복 세력과 민병대가 수도의 헌법기관을 점거한 밤을 헌법 절차만으로 넘기고, 두 번째 임기에는 군을 풀라는 유혹 앞에서 권력을 스스로 묶는다. 퇴임 전날 밤 그는 저격당하지만, 그가 세운 수사·사법 제도는 그 없이도 암살의 돈줄을 끝까지 밝혀내 법정에 세운다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
+          <t>2015년, 상파울루 최상위 로펌의 떠오르는 별 하파엘 멘지스(32)는 최대 고객 프라두 그룹을 대리해 고향 아마존 광산도시의 수은 오염 소송에서 늙은 상대 변호사 세베리누를 꺾어 간다. 그러나 떨리는 강마을 아이들과 로펌 전략이 덮은 보고서를 보고, 자기 쪽이 만든 ‘증거’로 구금된 세베리누가 석방 당일 숨지자 사직서를 낸다. 공설변호인으로 파벨라 청년과 원주민을 변호하던 그는 공직을 버리고 출마해 주지사와 대통령에 오르고, 헌법기관 점거의 밤과 파벨라에 군을 풀라는 유혹 앞에서 권력을 스스로 묶는다. 퇴임 전날 밤 그는 저격당하지만, 그가 세운 제도는 파벌의 연료·핀테크 세탁망을 거쳐 간 암살의 돈줄을 끝까지 밝혀내 법정에 세운다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>시대·배경</t>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 가상 아마존 주 ‘타피라주(Estado de Tapirá)’와 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’에서 시작해 브라질리아로. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회. 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
+          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 상파울루 파우리스타 대로의 대형 로펌에서 시작해 가상 아마존 주 ‘타피라주(Estado de Tapirá)’의 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’(주인공의 고향)와 강변 파벨라 ‘빌라 히반세이라(Vila Ribanceira)’, 아루아칸 원주민 영토를 거쳐 브라질리아로. 교도소에서 태어난 가상 조직범죄 파벌(facção) ‘이르만다지 두 노르치(Irmandade do Norte)’가 강의 코카인 경로·불법 금광·숲속 비행장을 잇고, 도시에서는 전·현직 경찰 출신 민병대(milícia)와 파벨라의 통제권을 다툰다. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회, 헌법기관으로서의 공설변호인청(Defensoria Pública). 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
         </is>
       </c>
     </row>
@@ -25727,7 +25727,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>경로</t>
@@ -25735,7 +25735,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>노바 카라자이 노동·환경 변호사 → 전국 인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 땅과노동당(PTT) 창당 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
+          <t>상파울루 대형 로펌 ‘케이로스 타바리스’ 기업소송 변호사(프라두 그룹 담당) → 사직 → 공설변호인 시험 합격, 노바 카라자이 공설변호인(Defensoria Pública)·인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 출마를 위한 공직 사퇴(desincompatibilização)·땅과노동당(PTT) 창당 참여 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>마모</t>
@@ -25759,11 +25759,11 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>부마다 핵심 인물을 하나씩 잃는다: 스승 세베리누(구금 중 사망) → 친구 오타비우의 배신·원주민 지도자 모에마의 투옥 → 아버지 뺑소니 사망·기자 루시아 실종 → 모에마 옥중 사망 → 오타비우 피살·루시아 유해 발견·브랑당 퇴장 → 공동체 라디오 진행자 도나 테레자 피살(민병대) → 감사인 질다 테러 사망과 하파 자신의 원칙의 흔들림 → 카이우 사망 → 브랑당의 고독사와 하파 암살. 폭력의 방식(청부 총격, 뺑소니, 실종, 호송 지연)은 브라질에서 활동가·기자가 실제로 당해 온 위협의 가상 등가물이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t>부마다 핵심 인물을 하나씩 잃는다: 상대 변호인이자 뒤늦은 스승 세베리누(하파의 로펌 측이 만든 ‘증거’로 구금 중 사망) → 로펌에 남아 프라두 편에 선 친구 오타비우의 배신·원주민 지도자 모에마의 투옥 → 아버지 뺑소니 사망·기자 루시아 실종 → 모에마 옥중 사망 → 오타비우 피살·루시아 유해 발견·브랑당 퇴장 → 파벌과 민병대 사이 파벨라의 공동체 라디오 진행자 도나 테레자 피살(민병대) → 감사인 질다 테러 사망과 하파 자신의 원칙의 흔들림 → 카이우 사망 → 브랑당의 고독사와 하파 암살. 1부의 상실에는 죄책감이 겹친다: 하파는 스승을 잃는 것이 아니라 자기 손으로 스승을 죽음에 몰아넣은 쪽에 서 있었다. 폭력의 방식(청부 총격, 뺑소니, 실종, 호송 지연)은 브라질에서 활동가·기자가 실제로 당해 온 위협의 가상 등가물이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>권력의 유혹</t>
@@ -25771,11 +25771,11 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 7부 민병대·파벌 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 7부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>자기 제한</t>
@@ -25783,7 +25783,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>점거의 밤에도 비상권한 없이 헌법 절차와 사법부에 수습을 맡기고, 가담자 사면 요구와 보복 입법을 모두 거부한다. 7부에서 백지 GLO 서명을 거부하고 모든 군 투입을 의회 승인·기한·사법 통제에 묶는 위기결정위원회 법을 만들며, 「권력의 한계」법에 두 번의 임기 뒤 평생 재출마 금지를 스스로 넣는다. 퇴임 직전 경호 강화와 비상권한 제안도 거절한다.</t>
+          <t>점거의 밤에도 비상권한 없이 헌법 절차와 사법부에 수습을 맡기고, 가담자 사면 요구와 보복 입법을 모두 거부한다. 대통령으로서 가장 먼저 한 일 중 하나가 자기 정부를 상대로 소송할 수 있는 공설변호인청의 예산 자율과 독립을 헌법 개정으로 굳히는 것이다. 7부에서 백지 GLO 서명을 거부하고 모든 군 투입을 의회 승인·기한·사법 통제·공설변호인 입회에 묶는 위기결정위원회 법을 만들며, 「권력의 한계」법에 두 번의 임기 뒤 평생 재출마 금지를 스스로 넣는다. 퇴임 직전 경호 강화와 비상권한 제안도 거절한다.</t>
         </is>
       </c>
     </row>
@@ -25799,7 +25799,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>결말</t>
@@ -25807,11 +25807,11 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 6부 테러와 암살이 같은 돈(전 재무차관 오타실리우)에서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 6부 테러와 암살의 돈이 이르만다지 두 노르치의 주유소 체인·무허가 핀테크 세탁망을 거쳐 전 재무차관 오타실리우에게서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 그의 법정에는 공설변호인이 붙는다 — 하파가 지킨 ‘누구나 변호받을 권리’다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>구성·무게중심</t>
@@ -25819,11 +25819,11 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>9부 × 12화 + 에필로그. 무게중심을 아마존과 제도 공격 두 곳에 둔다. 1~2부를 수은 강마을·불법 비행장·원주민 영토 ‘기준일’ 법안까지 포함한 아마존 서사로 확장하고, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>9부 × 12화 + 에필로그. 무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>작은 모티프</t>
@@ -25831,11 +25831,11 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>‘먼저 커피부터(Primeiro o cafezinho)’. 세베리누는 사무실에 온 사람에게 늘 작은 잔의 커피부터 내고, 부솔라 감사의 질다도 그렇다. 질다가 남긴 카드 ‘커피를 잊지 말 것(Não esquecer o cafezinho)’이 8부에서 ‘고통을 안고 온 사람에게는 먼저 커피를’로 해독된다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="225" customHeight="1">
+          <t>‘먼저 커피부터(Primeiro o cafezinho)’. 세베리누는 사무실에 온 사람에게, 심지어 자신을 무너뜨리러 온 상대편 로펌 변호사 하파에게도 작은 잔의 커피부터 낸다. 구치소 면회에서도 교도관에게 얻은 커피를 하파에게 먼저 민다. 하파는 공설변호인실에서 겁먹은 피의자 가족에게 같은 커피를 내게 되고, 부솔라 감사의 질다도 그렇다. 질다가 남긴 카드 ‘커피를 잊지 말 것(Não esquecer o cafezinho)’이 8부에서 ‘고통을 안고 온 사람에게는 먼저 커피를’로 해독된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="240" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>실제 현안</t>
@@ -25847,8 +25847,8 @@
 · 환경 인허가를 대폭 완화한 이른바 ‘파괴 법안’과 대통령 거부권을 뒤집은 의회 농업 로비, 원주민 영토 ‘기준일’ 논쟁
 · 쿠데타 모의에 대한 사법 심판(전직 대통령 유죄 판결)과 의회의 사면 법안 논쟁
 · 외국 정부가 재판을 문제 삼아 가한 50% 관세·대법관 제재와 사법 주권
-· 조직범죄의 합법 경제 침투(연료 유통·무허가 핀테크를 통한 돈세탁)와 도시 민병대
-· 파벌 소탕을 내건 초대형 경찰 작전의 대량 사망과 연방-주 치안 권한 갈등
+· 조직범죄 파벌(facção)의 아마존 확산(강의 코카인 경로와 불법 금 채굴·비행장의 융합, 파벌 영향 아래 놓인 지자체 급증)과 합법 경제 침투(연료 유통·무허가 핀테크를 통한 돈세탁), 도시 민병대
+· 파벨라에서의 초대형 경찰 작전의 대량 사망과 연방-주 치안 권한 갈등, 과밀 교도소와 구금심사·공공 변호 접근성
 · 민간은행 파산 스캔들로 드러난 금융·정치·사법 유착
 · 연금 수급자 수백만 명에게서 몰래 회비를 떼 간 연금 부정 공제 스캔들
 · 플랫폼 책임을 넓힌 대법원 판결과 메신저 기반 허위정보
@@ -25856,7 +25856,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="510" customHeight="1">
+    <row r="18" ht="600" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>현안 출처(웹 확인)</t>
@@ -25870,6 +25870,7 @@
 · 환경 인허가 완화 ‘파괴 법안’ 하원 통과, 이후 의회가 대통령 거부 조항 다수 부활 — Mongabay, 2025-07, https://news.mongabay.com/2025/07/brazils-congress-passes-devastation-bill-in-major-environmental-setback/ / Climate Home News, 2025-12-03, https://www.climatechangenews.com/2025/12/03/brazils-congress-lula-push-devastation-bill-cop30-heels-licensing-senate/
 · COP30 벨렝: 열대림 영구기금(TFFF) 출범했으나 규모 축소, 원주민 시위대 회의장 진입 — Carbon Brief, 2025-11, https://www.carbonbrief.org/cop30-key-outcomes-for-food-forests-land-and-nature-at-the-un-climate-talks-in-belem
 · PCC의 연료 유통·핀테크 침투와 금융가 돈세탁을 겨냥한 사상 최대 단속 — PBS NewsHour, 2025-08-28, https://www.pbs.org/newshour/world/brazilian-police-crack-down-on-4-8-billion-tax-evasion-and-money-laundering-scheme
+· 아마존 법정지역 772개 지자체 중 344곳이 범죄 파벌의 영향 아래(2024년 260곳에서 32% 증가) — 브라질 공공안전포럼 『아마존 폭력 지도(Cartografias da Violência na Amazônia)』, 2025-11-19, https://fontesegura.forumseguranca.org.br/municipios-da-amazonia-sob-influencia-de-faccoes-criminosas-aumentam-32-e-chegam-a-344-em-2025-aponta-estudo-do-forum-brasileiro-de-seguranca-publica/ / 마약 밀매 조직이 코카인 수익을 불법 금 채굴에 투자·세탁 — Mongabay, 2025-06, https://news.mongabay.com/2025/06/organized-crime-gold-trade-are-increasingly-connected-report-shows/
 · 방쿠 마스테르 청산과 대법관·의원·감독관 연루 의혹이 대선을 뒤흔듦 — The Conversation, 2026, https://theconversation.com/banking-scandal-rocks-brazils-politics-and-the-countrys-presidential-election-in-october-291931
 · 연금(INSS) 수급자 600만여 명에게서 약 63억 헤알 무단 공제, 장관 사임 — UPI, 2025-06-03, https://www.upi.com/Top_News/World-News/2025/06/03/chile-brazil-pension-fraud-lula-freezing-assets/6841748975361/
 · 대법원, 인터넷 기본법 19조 일부 위헌·플랫폼 책임 확대(8대3) — RSF, 2025-06, https://rsf.org/en/brazil-supreme-court-increases-social-media-platforms-responsibility-welcome-decision
@@ -25896,7 +25897,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="135" customHeight="1">
+    <row r="20" ht="240" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>민감도·주의</t>
@@ -25904,7 +25905,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다.</t>
+          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다. [4차 개정 추가] 파벨라 주민을 범죄의 배경으로만 소비하지 말 것: 빌라 히반세이라에는 파벌과 민병대 말고도 일하는 어머니, 교회, 삼바·펑크 모임, 공동체 라디오, 대학에 간 아이(카이우)와 변호인이 되려는 청년(제페르송)이 있다. 가상 파벌 ‘이르만다지 두 노르치’는 교도소 태생 파벌이라는 구조만 참고하고 코만두 베르멜류(CV)·PCC의 이름·상징·수감자 규약·실존 지도자·실제 사건을 복제하지 않으며, 멕시코식 카르텔 액션 문법(참수·거물 두목의 쇼)으로 그리지 않는다. 5부 경찰 작전은 2025년 리우 작전을 연상시키므로 지명·날짜·사망자 수·작전명을 겹치지 않게 하고, 경찰관 개인도 일괴암적 악으로 그리지 않는다. 공설변호인을 이상화된 영웅으로 만들지 않는다: 하루 수십 건의 구금심사, 만성 인력 부족, 이기지 못하는 사건, 조직 내부의 신중론과 관료주의, 하파 자신의 조급함까지 보여 준다. 대형 로펌 변호사들도 만화적 악당이 아니라 ‘모든 사람은 변호받을 권리가 있다’는 같은 원칙을 반대편에서 말하는 사람들로 그리고, 오타비우의 선택에는 설득력 있는 논리를 준다. 로펌·기업 이름은 모두 가상이며 실존 로펌을 연상시키는 이름·주소·사건을 쓰지 않는다.</t>
         </is>
       </c>
     </row>
@@ -25961,12 +25962,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>노바 카라자이의 노변호사. 1980년 군정 말기 댐 부실을 고발한 기술자를 변호하다 변호사회에서 제명된 과거</t>
+          <t>노바 카라자이의 노변호사. 1부 수은 소송에서 강마을 주민과 아루아칸을 대리하는 하파의 상대편 변호인이자 뒤늦게 스승이 되는 사람. 1980년 군정 말기 댐 부실을 고발한 기술자를 변호하다 변호사회에서 제명된 과거. 적에게도 먼저 커피를 낸다</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1부 10화 날조된 증인 매수 혐의로 체포, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망</t>
+          <t>1부 2화 상대편으로 첫 대면, 9화 하파의 로펌 측 ‘리스크 정보’ 업체가 만든 증인매수 자료로 날조 혐의 체포, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -25989,12 +25990,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>소꿉친구이자 기업 자문 변호사</t>
+          <t>하파의 법대 동기이자 케이로스 타바리스 로펌의 동료 변호사. ‘모든 고객은 변호받을 권리가 있다’를 끝까지 로펌의 논리로 믿는 사람</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2부 6화 프라두 측에 변절, 11화 발각. 3부 2화 귀환, 9화 대신 체포. 5부 6화 사법 부패 조사 중 청부 총격으로 피살</t>
+          <t>1부 9화 증거 조작 정황을 눈치채고 침묵, 12화 사직을 말린다. 2부 6화 파트너 승진과 함께 프라두 변호를 맡아 공익소송의 맞상대가 되고, 11화 증인 명단 유출로 배신 발각. 3부 3화 임신한 아내 앞에서 흔들려 귀환, 10화 대신 체포. 5부 6화 사법 부패 조사 중 청부 총격으로 피살</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -26017,12 +26018,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>지역 탐사보도 기자, 땅 세탁·민병대 구조 추적</t>
+          <t>지역 탐사보도 기자. 프라두의 금·땅 세탁, 파벌·민병대 구조 추적</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 첫 만남, 2부 4화 불법 비행장 취재. 3부 7화 폭로 기사 공개일 밤 실종, 5부 9화 정보기관 하부 조직에 살해된 사실 확인·유해 발견</t>
+          <t>1부 3화 프라두 측 변호사인 하파를 적으로 처음 만나고 11화 처음 손잡는다. 2부 4~5화 강의 코카인 경로·불법 금광·비행장의 겹침 추적. 3부 8화 폭로 기사 공개일 밤 실종, 5부 9화 정보기관 하부 조직에 살해된 사실 확인·유해 발견</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -26045,12 +26046,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>가상 원주민 ‘아루아칸’의 여성 지도자, 헤지 클라레이라 공동 설립자</t>
+          <t>가상 원주민 ‘아루아칸’의 여성 지도자, 세베리누의 의뢰인에서 헤지 클라레이라 공동 설립자로</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>1부 7화 첫 등장, 2부 8화 연방도로 봉쇄로 구속, 12화 징역 4년. 4부 5화 옥중 단식 14일째 병원 이송 지연 중 사망</t>
+          <t>1부 7화 현장검증에서 상대편 변호사 하파와 첫 대면, 2부 7화 헤지 클라레이라 공동 설립, 9화 연방도로 봉쇄로 구속(공설변호인 하파가 변호), 12화 징역 4년. 4부 5화 옥중 단식 14일째 병원 이송 지연 중 사망</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -26073,12 +26074,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>제련소 정비공 출신 아버지. ‘체제는 못 이긴다’던 사람</t>
+          <t>프라두 제련소 정비공 출신 아버지. 아들이 상파울루 대형 로펌 변호사가 된 것을 평생의 자랑으로 여기며 ‘체제는 못 이긴다, 안정된 자리를 지켜라’고 말하는 사람</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2부 10화 재취업한 정비소에서 해고, 3부 4화 새벽 뺑소니로 사망(공식 미제)</t>
+          <t>1부 12화 로펌 사직에 격분, 2부 10화 재취업한 정비소에서 해고, 3부 1화 공설변호인직 사퇴에 다시 반대하지만 유세 영상에서 ‘아들이 자랑스럽다’고 말한 뒤 3부 5화 새벽 뺑소니로 사망(공식 미제)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -26129,12 +26130,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>농업·광업 복합기업 ‘프라두 그룹’ 총수, 제련소·도축공장·원주민 영토 광산의 주인</t>
+          <t>농업·광업 복합기업 ‘프라두 그룹’ 총수, 제련소·도축공장·원주민 영토 광산의 주인. 1부에서 하파 로펌의 최대 고객</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1부 6화 첫 대면, 4부 4화 조건부 공개 지지, 5부 8화 공항에서 체포, 8부 11화 유죄 판결·해외 자산 환수</t>
+          <t>1부 5화 첫 승소 축하연에서 하파를 직접 치하, 4부 4화 조건부 공개 지지, 5부 8화 공항에서 체포, 8부 11화 유죄 판결·해외 자산 환수</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -26157,12 +26158,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>가상 정보기관 ANSI(국가제도안보청) 청장. 군정 말기 정보 기관원 출신, 적대자에서 불편한 협력자로</t>
+          <t>가상 정보기관 ANSI(국가제도안보청) 청장. 군정 말기 정보 기관원 출신, 1부에서는 로펌이 쓰는 ‘리스크 정보’ 업체의 그림자 고문. 적대자에서 불편한 협력자로</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1부 9화 첫 등장, 4부 7화 진압 대신 협상 선택, 5부 9화 루시아 사건 방조가 드러나 사임, 8부 5화 마지막 대화, 9부 7화 홀로 병사(아무도 오지 않은 장례식)</t>
+          <t>1부 8화 로펌 만찬에서 첫 등장, 4부 7화 진압 대신 협상 선택, 5부 9화 루시아 사건 방조가 드러나 사임, 8부 5화 마지막 대화, 9부 7화 홀로 병사(아무도 오지 않은 장례식)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -26213,7 +26214,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>법대생 자원활동가 출신 실무 총괄·선거본부장</t>
+          <t>공설변호인청 인턴 법대생 출신 실무 총괄·선거본부장</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -26241,7 +26242,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>금속노조 원로, 땅과노동당 공동 창당자·선거 전략가</t>
+          <t>금속노조 원로, 2년간 서명을 모아 땅과노동당을 등록시킨 공동 창당자·선거 전략가</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -26269,7 +26270,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>민간 감사사 ‘부솔라 감사(Bússola Auditoria)’. 질다는 경력 30년 감사인으로 손님에게 먼저 커피를 내고, 카이우는 공동창업자에서 재정투명성청장이 된다(아내 나지아, 포렌식 회계사 벤자밍과 함께)</t>
+          <t>민간 감사사 ‘부솔라 감사(Bússola Auditoria)’. 질다는 경력 30년 감사인으로 손님에게 먼저 커피를 내고, 카이우는 노바 카라자이 강변 파벨라 빌라 히반세이라에서 자라 장학금으로 회계를 공부한 공동창업자로 재정투명성청장이 된다(아내 나지아, 포렌식 회계사 벤자밍과 함께). 파벌 자금이 어떻게 동네 주유소와 송금 앱을 거치는지 몸으로 안다</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -26302,7 +26303,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>7부 11화 세베리누의 기록을 건넨다. 에필로그까지 생존</t>
+          <t>1부 12화 장례식에서 하파에게 세베리누의 커피잔을 건넨다. 7부 11화 세베리누의 기록을 건넨다. 에필로그까지 생존</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -26358,7 +26359,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>5부 1화 ‘1년 뒤엔 당신 없다’, 6부 10화 민병대 자금 경로에 이름이 스친다. 8부 12화 해외 도피, 9부 12화 테러·암살 자금원으로 확정·기소, 에필로그에서 국제 사법공조로 인도되어 재판정에 선다</t>
+          <t>5부 1화 ‘1년 뒤엔 당신 없다’, 6부 10화 이르만다지 두 노르치의 연료·핀테크 세탁망에 이름이 스친다. 8부 12화 해외 도피, 9부 12화 테러·암살 자금원으로 확정·기소, 에필로그에서 국제 사법공조로 인도되어 공설변호인이 붙은 재판정에 선다</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -26391,448 +26392,448 @@
       </c>
       <c r="F39" s="4" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>신규(파벨라 청년)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Jéferson ‘Jé’ Souza</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>제페르송 ‘제’ 소우자</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>빌라 히반세이라의 열아홉 살 배달 노동자. 이르만다지 두 노르치의 ‘운반책’으로 몰려 구금심사에 선 하파의 첫 의뢰인</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2부 2~3화 무죄, 3부 4화 파벌 통제 구역에서 유세단의 길을 협상, 8부 4화 공개 공모에 지원, 에필로그 공설변호인 시험 합격</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>신규(공동체 라디오)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Tereza Conceição (Dona Tereza)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>테레자 콘세이상(도나 테레자)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>수도권 위성도시 파벨라의 공동체 라디오 진행자, 파벌과 민병대 양쪽의 ‘보호’를 모두 거부하고 가스값·통근 밴·실종을 방송하는 60대 여성</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>6부 1화 등장, 2화 민병대 총격으로 사망. 9부 6화 하파가 무덤을 찾는다</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>3. 부 구성</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>부</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>제목(한국어)</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>제목(현지어)</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>시기·주인공 신분</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>줄거리</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>핵심 상실</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>강의 금</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>O Ouro do Rio</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>2015년 가을, 노바 카라자이와 아루아칸 영토 / 세베리누 사무소의 신참 변호사</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>제련소 폭발에서 시작한 사건이 상류 불법 금광의 수은 오염, 원주민 영토의 무장 채굴로 이어지며 한 이름(프라두)으로 모인다. 숲의 경계까지 들어간 스승 세베리누가 날조된 혐의로 구금돼 숨지고, 하파는 떠나기로 한다.</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>스승 세베리누 아우부케르키의 구금 중 사망</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>2부</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>숲의 경계선</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>A Linha da Floresta</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>2016~2017년, 브라질리아와 아마존 / 전국 인권 네트워크 ‘헤지 클라레이라’ 공동 설립자</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>불법 비행장과 금 세탁 경로, 원주민 영토를 줄이려는 ‘기준일’ 법안에 맞서 원주민 행진과 함께 싸운다. 정보기관의 거래 제안과 가족 압박 속에 친구 오타비우가 변절하고, 도로를 막은 모에마가 투옥된다.</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>오타비우의 배신과 모에마의 징역 4년</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3부</t>
+          <t>1부</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>문턱의 정치</t>
+          <t>강의 금</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>A Política do Limiar</t>
+          <t>O Ouro do Rio</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2018~2020년, 타피라주 / 땅과노동당 창당자 → 타피라주 주지사</t>
+          <t>2015년, 상파울루와 노바 카라자이·아루아칸 영토 / 상파울루 대형 로펌 ‘케이로스 타바리스’의 떠오르는 별(32세), 프라두 그룹 담당 소송 변호사</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>신당을 세워 고향 주지사 선거에 나선다. 아버지가 뺑소니로 죽고 루시아는 폭로 기사 공개일에 사라진다. 민병대의 선거 목장을 막고 당선되며, 1년 반 뒤 대선 후보로 지명된다.</t>
+          <t>하파는 최대 고객 프라두 그룹을 대리해 고향 노바 카라자이의 수은 오염 소송에서 강마을과 아루아칸을 대리한 노변호사 세베리누를 꺾어 가고, 프라두를 쫓는 기자 루시아와는 적으로 만난다. 떨리는 아이들과 로펌 전략이 덮은 내부 보고서를 본 뒤, 자기가 제출한 날조 ‘증거’로 세베리누가 구금돼 석방 당일 숨지자 죄책감 속에 사직서를 낸다.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>아버지 니바우두의 죽음과 루시아의 실종</t>
+          <t>상대 변호인이자 뒤늦은 스승 세베리누 아우부케르키의 구금 중 사망(하파 자신이 가담한 죽음)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>4부</t>
+          <t>2부</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>플라나우투로 가는 길</t>
+          <t>변호받을 권리</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>O Caminho do Planalto</t>
+          <t>O Direito de Defesa</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2021~2022년 / 대선 후보 → 대통령 당선인</t>
+          <t>2016~2017년, 노바 카라자이·빌라 히반세이라와 브라질리아 / 노바 카라자이 공설변호인(Defensoria Pública), 헤지 클라레이라 공동 설립자</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>물가·가뭄·원주민 영토 침탈로 나라가 흔들린다. 모에마가 옥중 단식 끝에 숨지자 전국 파업이 번지고, 정권의 비밀 자금이 드러나 대통령이 사임한다. 하파는 결선에서 이긴다.</t>
+          <t>공설변호인 시험에 붙은 하파는 파벨라 청년들이 경찰 조서 한 장으로 파벌의 ‘운반책’이 되는 구금심사장에서 일하고, 수은 강마을을 위해 공익소송(ação civil pública)을 낸다. 루시아가 강의 코카인 경로와 불법 금광·비행장의 겹침을 추적하는 사이, 로펌에 남은 오타비우는 프라두 편에서 그를 배신하고 도로를 막은 모에마는 하파의 변론에도 투옥된다.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>모에마의 옥중 사망</t>
+          <t>오타비우의 배신과 모에마의 징역 4년</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>5부</t>
+          <t>3부</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>권력과 전장</t>
+          <t>문턱의 정치</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>O Poder e a Trincheira</t>
+          <t>A Política do Limiar</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2023~2024년, 첫 임기 전반 / 대통령(1기)</t>
+          <t>2018~2020년, 타피라주 / 공설변호인 사퇴 → 땅과노동당 후보 → 타피라주 주지사</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>재정투명성청이 정보기관 비밀 운영비와 프라두의 제국을 파헤치고, 세하 파리마주의 반란과 군경 파업을 협상으로 넘긴다. 오타비우가 피살되고 루시아의 죽음이 확인되며 브랑당이 물러나지만, 그 사이 불복의 씨앗이 자란다.</t>
+          <t>출마하려면 공직을 떠나야 한다: 하파는 선거 여섯 달 전 공설변호인직을 사퇴하고(아버지는 두 번째로 ‘안정’을 버리는 아들에게 반대한다) 신생 땅과노동당의 주지사 후보가 된다. 파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할 수 있는지 정하는 선거에서 아버지가 뺑소니로 죽고 루시아는 폭로 기사 공개일에 사라진다. 선거 목장을 막고 당선되며, 1년 반 뒤 대선 후보로 지명된다.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>오타비우 피살, 루시아 사망 확인, 브랑당의 퇴장</t>
+          <t>아버지 니바우두의 죽음과 루시아의 실종</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>6부</t>
+          <t>4부</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>삼권의 밤</t>
+          <t>플라나우투로 가는 길</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>A Noite dos Três Poderes</t>
+          <t>O Caminho do Planalto</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2025~2026년, 첫 임기 후반 / 대통령(1기)</t>
+          <t>2021~2022년 / 대선 후보 → 대통령 당선인</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>수도권 위성도시를 장악한 민병대와 대선 불복 단체방, 예비역 장교들이 하나의 망으로 엮인다. 민병대가 공동체 라디오 진행자를 죽이고, 불복 세력이 의회·대법원·대통령궁을 점거한 밤을 하파는 비상권한 없이 헌법 절차로 넘긴다. 사면도 보복도 없이 법원에 맡기자 외국 정부가 관세와 대법관 제재로 압박하지만 사법 주권을 지키고, 점거 자금이 핀테크로 세탁된 조직범죄의 돈임이 드러난다.</t>
+          <t>물가·가뭄·원주민 영토 침탈로 나라가 흔들린다. 모에마가 옥중 단식 끝에 숨지자 전국 파업이 번지고, 정권의 비밀 자금이 드러나 대통령이 사임한다. 하파는 결선에서 이긴다.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>민병대에 살해된 공동체 라디오 진행자 도나 테레자</t>
+          <t>모에마의 옥중 사망</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>7부</t>
+          <t>5부</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>재신임과 유혹</t>
+          <t>권력과 전장</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>A Reeleição e a Tentação</t>
+          <t>O Poder e a Trincheira</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2026~2027년, 재선 캠페인과 두 번째 임기 1~7개월 / 대통령(재선 후보 → 2기)</t>
+          <t>2023~2024년, 첫 임기 전반 / 대통령(1기)</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>박빙의 재선전은 레시피 유세장 테러로 질다를 잃은 채 끝난다. 두 번째 임기 초 주 경찰의 초대형 소탕 작전이 하루 120여 명의 죽음을 낳고 민병대·파벌 전쟁이 번지자 무기한 GLO·군인 면책·선거 연기·플랫폼 차단의 유혹이 오고, 하파는 한 번 선을 넘은 뒤 루아나와 부딪치고 벼랑 끝에서 백지 권한을 포기한다.</t>
+          <t>재정투명성청이 정보기관 비밀 운영비와 프라두의 제국을 파헤치고, 공설변호인청 예산 자율 개헌을 밀며 세하 파리마주의 반란과 군경 파업을 협상으로 넘긴다. 남동부 한 주 경찰이 파벨라에서 벌인 치명적 소탕 작전이 연방-주 권한 충돌로 번지고, 오타비우가 피살되고 루시아의 죽음이 확인되며 브랑당이 물러나지만, 그 사이 불복의 씨앗이 자란다.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>질다 페하스의 테러 사망, 하파 자신의 원칙에 대한 확신</t>
+          <t>오타비우 피살, 루시아 사망 확인, 브랑당의 퇴장</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>8부</t>
+          <t>6부</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>권력의 무게</t>
+          <t>삼권의 밤</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>O Peso do Poder</t>
+          <t>A Noite dos Três Poderes</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2027~2029년, 두 번째 임기 1~2년차 / 대통령(2기)</t>
+          <t>2025~2026년, 첫 임기 후반 / 대통령(1기)</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>「권력의 한계」법으로 권력을 나누고 루아나에게 실권을 넘긴다. 귀환 병사, 감시 체계 해체, 지방 부채를 다루는 사이 카이우가 쓰러지고, 질다를 죽인 돈은 해외로 빠져나간다.</t>
+          <t>수도권 위성도시 파벨라를 두고 이르만다지 두 노르치와 민병대가 다투는 사이, 민병대와 대선 불복 단체방, 예비역 장교들이 하나의 망으로 엮인다. 양쪽을 모두 방송하던 공동체 라디오 진행자 도나 테레자가 민병대에 살해되고, 불복 세력이 의회·대법원·대통령궁을 점거한 밤을 하파는 비상권한 없이 헌법 절차로 넘긴다. 사면도 보복도 없이 법원에 맡기자 외국 정부가 관세와 대법관 제재로 압박하지만 사법 주권을 지키고, 점거 자금이 파벌의 주유소 체인·핀테크로 세탁된 돈임이 드러난다.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>카이우 안드라지의 죽음, 자금원 오타실리우의 해외 도피</t>
+          <t>민병대에 살해된 공동체 라디오 진행자 도나 테레자</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>7부</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>재신임과 유혹</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>A Reeleição e a Tentação</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>2026~2027년, 재선 캠페인과 두 번째 임기 1~7개월 / 대통령(재선 후보 → 2기)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>박빙의 재선전은 레시피 유세장 테러로 질다를 잃은 채 끝난다. 두 번째 임기 초 이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고 원자재 가격이 폭락하자 파벨라 무기한 GLO·군인 면책·선거 연기·플랫폼 차단의 유혹이 오고, 하파는 한 번 선을 넘은 뒤 루아나와 부딪치고 벼랑 끝에서 백지 권한을 포기한다.</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>질다 페하스의 테러 사망, 하파 자신의 원칙에 대한 확신</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>8부</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>권력의 무게</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>O Peso do Poder</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>2027~2029년, 두 번째 임기 1~2년차 / 대통령(2기)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>「권력의 한계」법으로 권력을 나누고 루아나에게 실권을 넘긴다. 파벨라에서 돌아온 병사, 감시 체계 해체, 지방 부채를 다루는 사이 카이우가 쓰러지고, 질다를 죽인 돈은 파벌의 세탁망을 거쳐 해외로 빠져나간다.</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>카이우 안드라지의 죽음, 자금원 오타실리우의 해외 도피</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>9부</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>홀로 선 자리</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>O Lugar de Quem Fica Só</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>2030년(마지막 해)~2031년, 에필로그 2035년 / 대통령(임기 마지막 해) → 퇴임 → 사망</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>가뭄과 산불 속 귀향, 낙인법 폐지, 병사의 재판, 후계 선출. 브랑당이 홀로 죽고, 하파는 퇴임 전날 밤 저격당한다. 루아나는 홀로 선서하고, 수사기관·법원·의회가 각자의 절차로 암살의 돈줄을 끝까지 밝혀낸다.</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>가뭄과 산불 속 귀향, 낙인법 폐지, 파벨라 소년을 쏜 병사의 재판, 후계 선출. 브랑당이 홀로 죽고, 하파는 퇴임 전날 밤 저격당한다. 루아나는 홀로 선서하고, 수사기관·법원·의회가 각자의 절차로 파벌의 연료·핀테크 세탁망을 거친 암살의 돈줄을 끝까지 밝혀낸다.</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>브랑당의 고독한 죽음과 하파의 암살</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>4. 화별 구성</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>부·화</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>제목(한국어)</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>제목(현지어)</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>대응 원작 화</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>한 줄 줄거리</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>1부 1화</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>첫 사건</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>O Primeiro Caso</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>1부 1화</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>제련소 폭발 사망이 ‘작업자 과실’로 덮이고, 세베리누는 미망인에게 먼저 커피를 낸 뒤 하파에게 첫 상담을 맡긴다.</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>1부 2화</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>스승과 제자</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Mestre e Aprendiz</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>1부 2화</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>목격 노동자를 설득하던 하파가 1980년 군정 말기 댐 부실 고발자를 변호하다 제명된 스승의 과거를 알게 된다.</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>1부 3화</t>
+          <t>1부 1화</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>수은의 강</t>
+          <t>떠오르는 별</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>O Rio de Mercúrio</t>
+          <t>A Estrela da Casa</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 확장</t>
+          <t>1부 1화 변형</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>상류 불법 금광의 수은으로 강마을 아이들이 떨기 시작하고, 어부 가족이 세베리누를 찾아온다.</t>
+          <t>상파울루 로펌 케이로스 타바리스의 서른두 살 하파가 인수합병을 따내고, 최대 고객 프라두 그룹의 타피라 수은 소송을 맡는다.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -26840,27 +26841,27 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>1부 4화</t>
+          <t>1부 2화</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>첫 협박</t>
+          <t>상대편의 커피</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>A Primeira Ameaça</t>
+          <t>O Cafezinho do Adversário</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1부 4화</t>
+          <t>1부 2화 변형</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>한밤중 집으로 협박 전화가 오고, 제련소 정비공 출신 아버지 니바우두는 ‘체제는 못 이긴다’며 아들과 부딪친다.</t>
+          <t>고향 노바 카라자이로 간 하파에게 상대 변호인 세베리누가 먼저 커피를 내고, 하파는 그가 군정 말기 제명된 변호사임을 안다.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
@@ -26868,27 +26869,27 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>1부 5화</t>
+          <t>1부 3화</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>작은 승리</t>
+          <t>적으로 만난 기자</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Uma Pequena Vitória</t>
+          <t>A Jornalista do Outro Lado</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 확장</t>
+          <t>1부 6화 변형</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>주 정부에 강마을 의료 지원과 정화를 명령하는 첫 승소 판결, 하파는 기자 루시아 폰치스를 처음 만난다.</t>
+          <t>법원 계단에서 프라두의 금을 쫓는 기자 루시아가 하파를 ‘독의 변호인’이라 몰아붙이고, 둘은 적으로 만난다.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -26896,27 +26897,27 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>1부 6화</t>
+          <t>1부 4화</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>회색지대</t>
+          <t>아버지의 식탁</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Zona Cinzenta</t>
+          <t>A Mesa do Pai</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1부 3화 변형</t>
+          <t>1부 4화 변형</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>프라두 측 변호사가 강마을에 합의금과 비밀유지 서약을, 하파에게는 사내변호사 자리를 내밀고 한 가족이 빠져나간다.</t>
+          <t>프라두 제련소 정비공 출신 아버지는 아들을 자랑하지만, 렌터카에 ‘살인자’가 긁히고 밤의 전화가 온다.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -26924,27 +26925,27 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>1부 7화</t>
+          <t>1부 5화</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>모에마의 등장</t>
+          <t>작은 승리</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>A Chegada de Moema</t>
+          <t>Uma Pequena Vitória</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1부 7화</t>
+          <t>1부 5화 변형</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>아루아칸 원주민 영토에 광산 허가가 떨어지고, 여성 지도자 모에마가 세베리누의 사무소를 찾아온다.</t>
+          <t>수은을 무허가 채굴꾼 탓으로 돌린 감정서로 하파가 첫 판결을 이기고, 축하연에서 프라두가 직접 그를 치하한다.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -26952,27 +26953,27 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 6화</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>숲의 경계</t>
+          <t>회색지대</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>A Divisa da Mata</t>
+          <t>Zona Cinzenta</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>1부 3화 변형</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>하파와 모에마가 영토 안의 무장 금광을 기록하러 들어가고, 숲 지킴이 청년이 총에 맞는다.</t>
+          <t>로펌이 강마을에 합의금과 비밀유지 서약을 내밀고, 서명하러 간 하파는 손이 떨리는 아이들을 처음 본다.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -26980,27 +26981,27 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>1부 9화</t>
+          <t>1부 7화</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>브랑당의 그림자</t>
+          <t>숲의 현장검증</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>A Sombra de Brandão</t>
+          <t>A Inspeção Judicial</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 7화 변형</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>정보기관 ANSI의 브랑당 장군이 세베리누를 불러 ‘1980년처럼 끝날 수 있다’고 조용히 경고한다.</t>
+          <t>아루아칸 영토 현장검증에서 모에마와 마주하고, 프라두 광구 경계의 무장 준설선을 기록하던 숲 지킴이 청년이 총에 맞는다.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -27008,27 +27009,27 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>1부 10화</t>
+          <t>1부 8화</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>세베리누의 체포</t>
+          <t>브랑당의 그림자</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>A Prisão de Severino</t>
+          <t>A Sombra de Brandão</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1부 9화</t>
+          <t>1부 8화 변형</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>새벽, 세베리누가 목격자를 매수했다는 날조된 혐의로 체포되고 사진이 방송에 먼저 흘러나간다.</t>
+          <t>로펌 만찬에서 ‘리스크 정보’ 업체 고문 브랑당 장군이 세베리누가 증인을 매수했다는 자료를 건넨다.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -27036,27 +27037,27 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>1부 11화</t>
+          <t>1부 9화</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>세베리누의 죽음</t>
+          <t>고발장</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>A Morte de Severino</t>
+          <t>A Representação</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1부 11화 변형</t>
+          <t>1부 9화 변형</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>학대 흔적과 끊긴 심장약을 오타비우와 함께 증거로 모았지만, 석방이 결정된 날 세베리누가 숨진다.</t>
+          <t>하파가 그 자료로 형사 고발장을 내고, 오타비우는 증인이 업체에서 돈을 받은 정황을 보고도 침묵한다. 새벽 세베리누가 체포된다.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -27064,111 +27065,111 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
+          <t>1부 10화</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>덮인 보고서</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>O Laudo Enterrado</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>하파는 로펌 자료실에서 제련소 수은을 확인한 2013년 내부 보고서를 찾고, 구치소의 세베리누는 교도관의 커피를 그에게 먼저 민다.</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>석방의 날</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>O Dia da Soltura</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>하파가 루시아와 손잡고 날조 증거와 끊긴 심장약을 판사에게 넘겨 석방이 결정되지만, 그날 세베리누가 숨진다.</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
           <t>1부 12화</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>결심</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>A Decisão</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>1부 12화</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>강마을과 공장, 아루아칸 사람들로 가득한 장례식. 하파는 무심코 조문객에게 커피부터 내고 떠날 결심을 한다.</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>수도 상경</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>Rumo a Brasília</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>반년 뒤 하파는 브라질리아로 옮겨 모에마와 함께 전국 인권 네트워크 ‘헤지 클라레이라’를 출범시킨다.</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>2부 2화</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>자금의 유혹</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>A Tentação do Dinheiro</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>2부 2화</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>정체불명의 환경 재단이 거액 후원을 제안하고, 법대생 비아가 돈의 출처가 프라두 그룹임을 밝혀낸다.</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr"/>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>사직서</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>A Demissão</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>1부 12화 변형</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>강마을과 아루아칸 사람들로 가득한 장례식에서 하파는 무심코 조문객에게 커피를 내고, 사직서를 낸다. 아버지와 오타비우가 말린다.</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2부 3화</t>
+          <t>2부 1화</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>루시아의 특종</t>
+          <t>공설변호인 시험</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>O Furo de Lúcia</t>
+          <t>O Concurso</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>2부 3화</t>
+          <t>2부 1화 변형</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>루시아가 불법 금이 가짜 채굴권 서류로 세탁돼 의원들의 선거 자금이 되는 경로를 추적한다.</t>
+          <t>반년 동안 부모 집에서 공부한 하파가 공설변호인 시험에 붙고, 로펌 동료들의 비웃음 속에 노바 카라자이 부임을 고른다.</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr"/>
@@ -27176,17 +27177,17 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2부 4화</t>
+          <t>2부 2화</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>강 위의 비행장</t>
+          <t>구금심사</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>As Pistas Clandestinas</t>
+          <t>Audiência de Custódia</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -27196,7 +27197,7 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>하파·루시아·모에마가 숲속 불법 비행장 마흔 곳을 좌표로 기록하고, 협조한 원주민 보호청 직원이 협박받는다.</t>
+          <t>하루 마흔 건의 구금심사, 빌라 히반세이라의 열아홉 살 제페르송이 파벌 ‘운반책’으로 멍든 채 서 있다.</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr"/>
@@ -27204,27 +27205,27 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2부 5화</t>
+          <t>2부 3화</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>거리의 목소리</t>
+          <t>운반책이 아닌 소년</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>A Voz das Ruas</t>
+          <t>O Menino Que Não Era Mula</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>2부 4화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>원주민 수천 명이 수도로 행진해 천막 농성을 벌이고, 헤지 클라레이라가 첫 대규모 집회를 연다.</t>
+          <t>똑같은 문장이 반복된 경찰 조서를 파고든 하파가 제의 무죄를 받아 내지만, 다른 서른 건은 이기지 못한다.</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr"/>
@@ -27232,27 +27233,27 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>2부 4화</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>오타비우의 균열</t>
+          <t>루시아의 강</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>A Rachadura de Otávio</t>
+          <t>O Rio de Lúcia</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>2부 5화</t>
+          <t>2부 3화 변형</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>고객을 잃고 빚에 몰린 오타비우가 프라두 측 변호사의 ‘자문’ 제안을 은밀히 받아들인다.</t>
+          <t>이제 편이 된 루시아가 이르만다지 두 노르치의 코카인 배가 불법 금 준설선과 같은 강길을 쓰는 것을 추적한다.</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
@@ -27260,17 +27261,17 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2부 7화</t>
+          <t>2부 5화</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>기준일</t>
+          <t>강 위의 비행장</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>O Marco</t>
+          <t>As Pistas Clandestinas</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -27280,7 +27281,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>원주민 영토 ‘기준일’ 법안과 환경 인허가를 사실상 없애는 ‘일괄 허가’ 법안이 함께 오르고, 모에마가 상원에서 증언한다.</t>
+          <t>코카인과 금을 함께 싣는 숲속 불법 비행장 마흔 곳을 좌표로 기록하고, 협조한 원주민 보호청 직원이 협박받는다.</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr"/>
@@ -27288,27 +27289,27 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2부 8화</t>
+          <t>2부 6화</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>모에마의 구금</t>
+          <t>공익소송</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>A Prisão de Moema</t>
+          <t>A Ação Civil Pública</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>2부 5화 변형</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>광산 트럭을 막으려 연방도로를 봉쇄한 모에마가 ‘범죄 결사’ 혐의로 구속된다.</t>
+          <t>하파가 수은 강마을을 위한 공익소송을 내고, 파트너로 승진한 오타비우가 프라두 측 대리인으로 맞은편에 앉는다.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr"/>
@@ -27316,27 +27317,27 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2부 9화</t>
+          <t>2부 7화</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 제안</t>
+          <t>헤지 클라레이라</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>A Proposta de Brandão</t>
+          <t>A Rede Clareira</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>2부 7화</t>
+          <t>2부 1·2화 변형</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>브랑당이 처음 하파를 직접 불러 ‘조용히 하면 모에마는 풀려난다’는 거래를 내민다.</t>
+          <t>모에마·루시아·파벨라 어머니들과 인권 네트워크를 세우고, 인턴 비아가 거액 후원 재단의 돈이 프라두의 것임을 밝힌다.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -27344,27 +27345,27 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2부 10화</t>
+          <t>2부 8화</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>가족의 대가</t>
+          <t>기준일</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>O Preço da Família</t>
+          <t>O Marco</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>2부 8화 변형</t>
+          <t>2부 4화 변형</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>아버지가 재취업한 정비소에서 해고되고, 신상털기와 협박에 자원활동가들이 하나둘 떠난다.</t>
+          <t>원주민 영토 ‘기준일’ 법안과 일괄 허가 법안이 오르고, 모에마가 상원에서 증언하며 원주민들이 수도로 행진한다.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -27372,27 +27373,27 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2부 11화</t>
+          <t>2부 9화</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>오타비우의 배신 발각</t>
+          <t>모에마의 구금</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>A Traição Descoberta</t>
+          <t>A Prisão de Moema</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>2부 10화</t>
+          <t>2부 6화</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>금광 노동자 산재 소송 서류가 제출 전날 유출되고, 비아의 추적 끝에 오타비우가 드러난다.</t>
+          <t>광산 트럭을 막으려 연방도로를 봉쇄한 모에마가 ‘범죄 결사’로 구속되고, 청장의 신중론을 넘어 하파가 변호를 맡는다.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -27400,111 +27401,111 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
+          <t>2부 10화</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>브랑당의 제안</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>A Proposta de Brandão</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>2부 7·8화 변형</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>브랑당이 ‘공익소송을 내리면 모에마는 풀려난다’는 거래를 내밀고, 아버지가 정비소에서 해고되며 동료들이 떠난다.</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>2부 11화</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>오타비우의 배신 발각</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>A Traição Descoberta</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>2부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>공익소송 감정 증인 명단이 새어 나가 증인 가족이 협박받고, 비아의 추적 끝에 오타비우가 드러난다.</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
           <t>2부 12화</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>모에마의 재판</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>O Julgamento de Moema</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>2부 11화 변형</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>통역도 없는 재판에서 모에마에게 징역 4년이 선고되고, ‘모에마에게 자유를’ 운동이 전국으로 번진다.</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>정당 창당</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>A Fundação do Partido</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>하파가 금속노조 원로 안셀무, 지역 활동가들과 함께 신생 정당 ‘땅과노동당(PTT)’을 창당한다.</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>3부 2화</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>오타비우의 귀환</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>A Volta de Otávio</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>3부 2화</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>임신한 아내 앞에서 흔들린 오타비우가 프라두 측 내부 자료를 들고 하파를 찾아온다.</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>2부 11·12화 변형</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>통역도 없는 재판에서 하파의 변론에도 모에마에게 징역 4년이 선고되고, ‘모에마에게 자유를’ 운동이 전국으로 번진다.</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>3부 3화</t>
+          <t>3부 1화</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>주지사 선거 도전</t>
+          <t>사퇴</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>A Disputa pelo Governo</t>
+          <t>A Desincompatibilização</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3부 3화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>하파가 고향 타피라주 주지사 선거에 출마하고, 농업 로비 소유 방송들이 공세를 시작한다.</t>
+          <t>출마하려면 선거 여섯 달 전 공직을 떠나야 한다. 하파가 공설변호인직 사퇴서를 쓰고, 아버지는 ‘또 안정을 버리냐’며 반대한다.</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr"/>
@@ -27512,27 +27513,27 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>3부 4화</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>아버지의 죽음</t>
+          <t>정당 창당</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>A Morte do Pai</t>
+          <t>A Fundação do Partido</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>3부 4화</t>
+          <t>3부 1화 변형</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>‘아들이 자랑스럽다’는 유세 영상으로 화제가 된 아버지 니바우두가 새벽길 뺑소니로 숨진다.</t>
+          <t>안셀무가 2년간 서명을 모아 등록시킨 땅과노동당(PTT)에 하파가 입당하고, 창당대회에서 주지사 후보로 추대된다.</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr"/>
@@ -27540,27 +27541,27 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>3부 5화</t>
+          <t>3부 3화</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>루시아의 폭로전</t>
+          <t>오타비우의 귀환</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>A Denúncia de Lúcia</t>
+          <t>A Volta de Otávio</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>3부 5화</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>루시아가 주정부·프라두 그룹·민병대를 잇는 ‘토지 세탁’ 구조의 최종 기사를 준비한다.</t>
+          <t>임신한 아내 앞에서 흔들린 오타비우가 로펌의 프라두 내부 자료를 들고 하파를 찾아온다.</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
@@ -27568,27 +27569,27 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>3부 6화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>선거 조작 저지</t>
+          <t>들어갈 수 없는 동네</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Contra o Curral Eleitoral</t>
+          <t>Onde Não Se Pode Entrar</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>3부 6화</t>
+          <t>3부 3화 변형</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>민병대가 투표소 길목을 막고 표를 사는 ‘선거 목장’을 참관인단이 영상 기록으로 막아선다.</t>
+          <t>파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할지 정하고, 제가 유세단의 길을 협상하며 농업 로비 방송들이 공세를 시작한다.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr"/>
@@ -27596,27 +27597,27 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>루시아의 실종</t>
+          <t>아버지의 죽음</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>O Desaparecimento de Lúcia</t>
+          <t>A Morte do Pai</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>폭로 기사가 공개되어 전국이 들끓은 날 밤, 루시아가 강변 도로에서 흔적 없이 사라진다.</t>
+          <t>‘아들이 자랑스럽다’는 유세 영상으로 화제가 된 아버지 니바우두가 새벽길 뺑소니로 숨진다.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
@@ -27624,27 +27625,27 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 6화</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>거리로 나선 사람들</t>
+          <t>루시아의 폭로전</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>O Povo nas Ruas</t>
+          <t>A Denúncia de Lúcia</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>루시아의 사진을 든 자발적 시위가 투표 이틀 전 전국 열두 개 도시로 번진다.</t>
+          <t>루시아가 주정부·프라두 그룹·민병대·파벌 비행장을 잇는 ‘토지 세탁’ 구조의 최종 기사를 준비한다.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr"/>
@@ -27652,27 +27653,27 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 7화</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>오타비우의 희생</t>
+          <t>선거 조작 저지</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>O Sacrifício de Otávio</t>
+          <t>Contra o Curral Eleitoral</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 6화</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>투표 전날 밤, 선거본부 압수수색 직전 루시아의 취재원 자료를 빼돌린 오타비우가 대신 체포된다.</t>
+          <t>민병대가 투표소 길목을 막고 표를 사는 ‘선거 목장’을 파벨라 주민 참관인단이 영상 기록으로 막아선다.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
@@ -27680,27 +27681,27 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3부 10화</t>
+          <t>3부 8화</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>브랑당과의 첫 담판</t>
+          <t>루시아의 실종</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>O Primeiro Acerto com Brandão</t>
+          <t>O Desaparecimento de Lúcia</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>3부 10화</t>
+          <t>3부 7화</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>투표일 밤 브랑당이 나타나 결과 인정의 대가를 묻고, 하파는 아무것도 약속하지 않는다.</t>
+          <t>폭로 기사가 공개되어 전국이 들끓은 날 밤, 루시아가 강변 도로에서 흔적 없이 사라진다.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr"/>
@@ -27708,27 +27709,27 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3부 11화</t>
+          <t>3부 9화</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>당선, 그러나</t>
+          <t>거리로 나선 사람들</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Vitória, Mas…</t>
+          <t>O Povo nas Ruas</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>3부 11화</t>
+          <t>3부 8화</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>하파가 주지사에 당선되지만 전임 정부의 인수 방해와 연방의 재정 압박이 기다린다.</t>
+          <t>루시아의 사진을 든 자발적 시위가 투표 이틀 전 전국 열두 개 도시로 번진다.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
@@ -27736,111 +27737,111 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
+          <t>3부 10화</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>오타비우의 희생</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>O Sacrifício de Otávio</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>3부 9화</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>투표 전날 밤, 선거본부 압수수색 직전 루시아의 취재원 자료를 빼돌린 오타비우가 대신 체포된다.</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>3부 11화</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>당선, 그러나</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Vitória, Mas…</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>3부 10·11화 압축</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>투표일 밤 브랑당의 담판에 아무것도 약속하지 않은 하파가 당선되지만, 인수 방해와 연방의 재정 압박이 기다린다.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>전국 무대로</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>Rumo ao Palco Nacional</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>1년 반 뒤 투명 예산의 타피라주가 모범이 되고, 하파는 대선 후보로 지명되며 부솔라의 질다를 만난다.</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>나라의 균열</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>O País Rachado</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>물가 폭등과 가뭄, 원주민 영토 침탈이 겹친 위기 속에 경제 자문을 영입한 대선 캠프가 출범한다.</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>4부 2화</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>모에마의 옥중 투쟁</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>A Luta de Moema na Prisão</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>4부 2화</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>프라두 그룹이 아루아칸 영토 채굴을 재개하자 수감 중인 모에마가 옥중 단식을 시작한다.</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>1년 반 뒤 투명 예산의 타피라주가 모범이 되고, 대선 후보가 된 하파는 부솔라의 질다와 파벨라 출신 카이우를 만난다.</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>4부 3화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>루아나의 등장</t>
+          <t>나라의 균열</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>A Chegada de Luana</t>
+          <t>O País Rachado</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>4부 3화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>단식 아흐레째, 스물두 살 법대생 루아나 마르키스가 캠프 자원활동가로 합류한다.</t>
+          <t>물가 폭등과 가뭄, 원주민 영토 침탈이 겹친 위기 속에 경제 자문을 영입한 대선 캠프가 출범한다.</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr"/>
@@ -27848,27 +27849,27 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>4부 4화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>프라두의 배신적 지지</t>
+          <t>모에마의 옥중 투쟁</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>O Apoio Traiçoeiro de Prado</t>
+          <t>A Luta de Moema na Prisão</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>4부 4화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>프라두가 은밀히 지지를 제안하고, 하파는 원주민 영토 철수와 노동자 보상을 공개 조건으로 건다.</t>
+          <t>프라두 그룹이 아루아칸 영토 채굴을 재개하자 수감 중인 모에마가 옥중 단식을 시작한다.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr"/>
@@ -27876,27 +27877,27 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>4부 5화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>모에마의 옥중 사망</t>
+          <t>루아나의 등장</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>A Morte de Moema</t>
+          <t>A Chegada de Luana</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>4부 5화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>법원이 병원 이송을 승인했지만 ‘호송 절차’로 지연되는 사이, 단식 14일째 모에마가 숨진다.</t>
+          <t>단식 아흐레째, 스물두 살 법대생 루아나 마르키스가 캠프 자원활동가로 합류한다.</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr"/>
@@ -27904,27 +27905,27 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>거리의 혁명</t>
+          <t>프라두의 배신적 지지</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>A Revolução nas Ruas</t>
+          <t>O Apoio Traiçoeiro de Prado</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>원주민 행진과 트럭·교원 파업이 47개 도시로 번지고, 한 주 군경 장교가 진압 명령을 거부한다.</t>
+          <t>프라두가 은밀히 지지를 제안하고, 하파는 원주민 영토 철수와 노동자 보상을 공개 조건으로 건다.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
@@ -27932,27 +27933,27 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 선택</t>
+          <t>모에마의 옥중 사망</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>A Escolha de Brandão</t>
+          <t>A Morte de Moema</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>대통령궁 긴급회의에서 강경파가 ‘방위 상태’ 선포를 밀어붙이자 브랑당이 협상을 택한다.</t>
+          <t>법원이 병원 이송을 승인했지만 ‘호송 절차’로 지연되는 사이, 단식 14일째 모에마가 숨진다.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -27960,27 +27961,27 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 6화</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>암살 시도</t>
+          <t>거리의 혁명</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>O Atentado</t>
+          <t>A Revolução nas Ruas</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 6화</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>농업 로비의 아성 도시에서 유세를 강행한 하파를 겨눈 저격이 벌어지고, 저격범이 사살된다.</t>
+          <t>원주민 행진과 트럭·교원 파업이 47개 도시로 번지고, 한 주 군경 장교가 진압 명령을 거부한다.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -27988,27 +27989,27 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 7화</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>구체제의 붕괴</t>
+          <t>브랑당의 선택</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>A Queda do Velho Regime</t>
+          <t>A Escolha de Brandão</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 7화</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>부솔라가 찾은 자금 흐름이 대통령 비서실장과 암살 배후에 닿고, 대통령이 사임한다.</t>
+          <t>대통령궁 긴급회의에서 강경파가 ‘방위 상태’ 선포를 밀어붙이자 브랑당이 협상을 택한다.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -28016,27 +28017,27 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 8화</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>선거전 최종전</t>
+          <t>암살 시도</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>A Batalha Final</t>
+          <t>O Atentado</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 8화</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>부통령 권한대행 아래 치러지는 대선, 마지막 TV 토론과 단체방 가짜뉴스의 공방이 벌어진다.</t>
+          <t>농업 로비의 아성 도시에서 유세를 강행한 하파를 겨눈 저격이 벌어지고, 저격범이 사살된다.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -28044,27 +28045,27 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 9화</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>당선의 밤</t>
+          <t>구체제의 붕괴</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>A Noite da Vitória</t>
+          <t>A Queda do Velho Regime</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 9화</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>결선 개표가 밤새 이어지고, 새벽 무렵 하파의 승리가 확정되자 비아와 안셀무가 말없이 커피를 따른다.</t>
+          <t>부솔라가 찾은 자금 흐름이 대통령 비서실장과 암살 배후에 닿고, 대통령이 사임한다.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -28072,111 +28073,111 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
+          <t>4부 10화</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>선거전 최종전</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>A Batalha Final</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>4부 10화</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>부통령 권한대행 아래 치러지는 대선, 마지막 TV 토론과 단체방 가짜뉴스의 공방이 벌어진다.</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>당선의 밤</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>A Noite da Vitória</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>결선 개표가 밤새 이어지고, 새벽 무렵 하파의 승리가 확정되자 비아와 안셀무가 말없이 커피를 따른다.</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>취임 전야</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>A Véspera da Posse</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="E104" s="9" t="inlineStr">
         <is>
           <t>취임 준비 대신 하파는 세베리누와 아버지, 모에마의 무덤을 차례로 찾아간다.</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>취임과 첫 벽</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>A Posse e o Primeiro Muro</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>재무부가 예비비 자료를 감추자 하파는 부솔라 팀에 신설 재정투명성청을 맡긴다.</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>브랑당과의 재계약</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Um Novo Acordo com Brandão</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>감사가 ANSI의 비밀 운영비로 이어지고, 하파는 브랑당과 조건부 공조를 맺는다.</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr"/>
+      <c r="F104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>5부 3화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>프라두의 마지막 카드</t>
+          <t>취임과 첫 벽</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>A Última Carta de Prado</t>
+          <t>A Posse e o Primeiro Muro</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>5부 3화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>실소유자 공개·토지 등기 정비 법안이 프라두 제국을 겨누고, 의회 농업 로비가 반격한다.</t>
+          <t>재무부가 예비비 자료를 감추자 하파는 부솔라 팀에 신설 재정투명성청을 맡기고, 공설변호인청 예산 자율 개헌안을 첫 법안으로 보낸다.</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
@@ -28184,27 +28185,27 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>5부 4화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>지방의 반란</t>
+          <t>브랑당과의 재계약</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>A Rebelião de Serra Parima</t>
+          <t>Um Novo Acordo com Brandão</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>5부 4화 확장</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>희토류 산지 세하 파리마주 주지사가 법 적용을 거부하고 군경 파업을 부추기자 부지사 마릴리아가 자료를 넘긴다.</t>
+          <t>감사가 ANSI의 비밀 운영비로 이어지고, 하파는 브랑당과 조건부 공조를 맺는다.</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr"/>
@@ -28212,27 +28213,27 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>파업의 끝</t>
+          <t>프라두의 마지막 카드</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>O Fim da Greve</t>
+          <t>A Última Carta de Prado</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>5부 4화 확장</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>연방 개입 대신 군경 가족들과의 협상으로 파업이 풀리고, 반란 주지사는 법정에 선다.</t>
+          <t>실소유자 공개·토지 등기 정비 법안이 프라두 제국을 겨누고, 의회 농업 로비가 반격한다.</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr"/>
@@ -28240,27 +28241,27 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>5부 6화</t>
+          <t>5부 4화</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>개혁의 대가</t>
+          <t>지방의 반란</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>O Preço da Reforma</t>
+          <t>A Rebelião de Serra Parima</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 4화 확장</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>판·검사 부패망 조사에 자원한 오타비우가 하파와 옛 우정을 되찾은 직후 청부 총격에 숨진다.</t>
+          <t>희토류 산지 세하 파리마주 주지사가 법 적용을 거부하고 군경 파업을 부추기자 부지사 마릴리아가 자료를 넘긴다.</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
@@ -28268,27 +28269,27 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>5부 7화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>국제적 고립과 압박</t>
+          <t>파업의 끝</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Isolamento e Pressão</t>
+          <t>O Fim da Greve</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>5부 6화</t>
+          <t>5부 4화 확장</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>무역협정 중단과 자본 유출, 헤알화 급락이 몰아치는 가운데 국방장관이 사임한다.</t>
+          <t>연방 개입 대신 군경 가족들과의 협상으로 파업이 풀리고, 반란 주지사는 법정에 선다.</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr"/>
@@ -28296,27 +28297,27 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 6화</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>프라두의 최종 제거</t>
+          <t>개혁의 대가</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>O Fim de Prado</t>
+          <t>O Preço da Reforma</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>조세 피난처의 마지막 은닉 구조가 드러나고, 프라두가 출국 직전 공항에서 체포된다.</t>
+          <t>판·검사 부패망 조사에 자원한 오타비우가 하파와 옛 우정을 되찾은 직후 청부 총격에 숨진다.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
@@ -28324,27 +28325,27 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 7화</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>브랑당의 최후</t>
+          <t>국제적 고립과 압박</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>O Fim de Brandão</t>
+          <t>Isolamento e Pressão</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 6화</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>오타비우 청부금의 송금 사슬이 루시아 실종일과 겹치고 유해가 발견된다. 브랑당은 사임한다.</t>
+          <t>무역협정 중단과 자본 유출, 헤알화 급락이 몰아치는 가운데 국방장관이 사임한다.</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
@@ -28352,27 +28353,27 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 8화</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>대의의 완성</t>
+          <t>프라두의 최종 제거</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>A Obra Concluída</t>
+          <t>O Fim de Prado</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 8화</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>사법개혁과 GLO 의회 승인 조항을 묶은 개헌안이 통과된다. 제한 조항은 하파 자신이 요구했다.</t>
+          <t>조세 피난처의 마지막 은닉 구조가 드러나고, 프라두가 출국 직전 공항에서 체포된다.</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
@@ -28380,27 +28381,27 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>5부 9화</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>개혁의 피로</t>
+          <t>브랑당의 최후</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>O Cansaço das Reformas</t>
+          <t>O Fim de Brandão</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 9화</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>연금 수급자 수백만 명에게서 몰래 회비를 떼 간 부정 공제가 터지고, 금광촌 실업까지 겹쳐 지지율이 떨어진다.</t>
+          <t>오타비우 청부금의 송금 사슬이 루시아 실종일과 겹치고 유해가 발견된다. 브랑당은 사임한다.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
@@ -28408,101 +28409,101 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>대의의 완성</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>A Obra Concluída</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>사법개혁·GLO 의회 승인·공설변호인청 예산 자율을 묶은 개헌안이 통과된다. 자기 정부를 묶는 조항은 하파 자신이 요구했다.</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>파벨라의 새벽</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>A Madrugada no Morro</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>남동부 한 주 경찰의 파벨라 소탕 작전으로 수십 명이 죽고, 연방 법의학 조사를 보낸 하파와 주지사가 권한을 두고 충돌한다.</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>경고등</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>O Sinal de Alerta</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>새 정보청장 구르겔이 예비역 장교·민병대·불복 단체방을 잇는 보고서를 올리지만, 증거는 아직 흐릿하다.</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>6부 1화</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>민병대의 도시</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>A Cidade da Milícia</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>수도권 위성도시에서 민병대가 가스·인터넷·통근 밴을 장악하고 주민에게 ‘보호세’를 걷는 현실을 하파가 직접 본다.</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>6부 2화</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>테레자의 라디오</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>A Rádio de Dona Tereza</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>민병대 비리를 방송하던 공동체 라디오 진행자 도나 테레자가 출근길에 총격으로 숨진다.</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>6부 3화</t>
+          <t>6부 1화</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>민병대와 의원들</t>
+          <t>민병대의 도시</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Milícia e Mandato</t>
+          <t>A Cidade da Milícia</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
@@ -28512,7 +28513,7 @@
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>테레자 살해 수사가 민병대 두목과 주 의원, 불복 운동 자금책을 잇는 선을 드러낸다.</t>
+          <t>수도권 위성도시 파벨라에서 파벌과 민병대가 가스·인터넷·통근 밴을 두고 다투고, 하파는 도나 테레자의 라디오 방송을 직접 듣는다.</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -28520,27 +28521,27 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>6부 4화</t>
+          <t>6부 2화</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>병영 앞 천막</t>
+          <t>테레자의 라디오</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>O Acampamento</t>
+          <t>A Rádio de Dona Tereza</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>5부 7화 확장</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>대선 불복 시민들이 병영 앞에 천막을 치고 군의 개입을 요구하며, 예비역 장교 단체방이 들끓는다.</t>
+          <t>파벌과 민병대 양쪽의 ‘보호’를 거부하고 민병대 비리를 방송하던 도나 테레자가 출근길에 총격으로 숨진다.</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -28548,27 +28549,27 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>6부 5화</t>
+          <t>6부 3화</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>군 내부의 균열</t>
+          <t>민병대와 의원들</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>A Fissura nos Quartéis</t>
+          <t>Milícia e Mandato</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>5부 7화 확장</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>한 대령이 쿠데타 계획 문건을 들고 구르겔을 찾아오고, 합참의장은 침묵을 택한다.</t>
+          <t>테레자 살해 수사가 민병대 두목과 주 의원, 불복 운동 자금책을 잇는 선을 드러낸다.</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -28576,17 +28577,17 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>6부 6화</t>
+          <t>6부 4화</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>점거 전야</t>
+          <t>병영 앞 천막</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>A Véspera</t>
+          <t>O Acampamento</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -28596,7 +28597,7 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>수백 대의 버스가 수도로 향하고, 수도 경비 책임자가 방어선을 절반으로 줄인 사실이 드러난다.</t>
+          <t>대선 불복 시민들이 병영 앞에 천막을 치고 군의 개입을 요구하며, 예비역 장교 단체방이 들끓는다.</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -28604,17 +28605,17 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>6부 7화</t>
+          <t>6부 5화</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>삼권의 밤</t>
+          <t>군 내부의 균열</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>A Noite dos Três Poderes</t>
+          <t>A Fissura nos Quartéis</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
@@ -28624,7 +28625,7 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>불복 군중이 의회·대법원·대통령궁을 점거해 부수고, 하파는 ‘방위 상태’ 선포 요구를 받는다.</t>
+          <t>한 대령이 쿠데타 계획 문건을 들고 구르겔을 찾아오고, 합참의장은 침묵을 택한다.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -28632,17 +28633,17 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>6부 8화</t>
+          <t>6부 6화</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>새벽의 몇 시간</t>
+          <t>점거 전야</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>As Horas da Madrugada</t>
+          <t>A Véspera</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
@@ -28652,7 +28653,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>명령을 거부한 장교와 대법원장, 루아나가 버티는 사이 하파는 헌법 절차만으로 청사를 되찾는다.</t>
+          <t>수백 대의 버스가 수도로 향하고, 수도 경비 책임자가 방어선을 절반으로 줄인 사실이 드러난다.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -28660,27 +28661,27 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>6부 9화</t>
+          <t>6부 7화</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>사면은 없다</t>
+          <t>삼권의 밤</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Sem Anistia</t>
+          <t>A Noite dos Três Poderes</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 7화 확장</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>사면 법안과 보복 입법을 모두 물리치자, 외국 정부가 재판을 ‘마녀사냥’이라 부르며 관세와 대법관 제재로 압박한다.</t>
+          <t>불복 군중이 의회·대법원·대통령궁을 점거해 부수고, 하파는 ‘방위 상태’ 선포 요구를 받는다.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -28688,27 +28689,27 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>6부 10화</t>
+          <t>6부 8화</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>돈의 지도</t>
+          <t>새벽의 몇 시간</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>O Mapa do Dinheiro</t>
+          <t>As Horas da Madrugada</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 7화 확장</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>테레자 살해와 점거 자금이 주유소 체인과 무허가 핀테크로 세탁돼 옛 정보기관의 ‘지갑’에 닿은 흔적을 벤자밍이 찾는다.</t>
+          <t>명령을 거부한 장교와 대법원장, 루아나가 버티는 사이 하파는 헌법 절차만으로 청사를 되찾는다.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -28716,27 +28717,27 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>6부 11화</t>
+          <t>6부 9화</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>개혁의 피로</t>
+          <t>사면은 없다</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>O Cansaço das Reformas</t>
+          <t>Sem Anistia</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>불법 채굴 단속으로 일자리를 잃은 금광촌과 끝없는 재판 뉴스 속에 지지율이 떨어진다.</t>
+          <t>사면 법안과 보복 입법을 모두 물리치자, 외국 정부가 재판을 ‘마녀사냥’이라 부르며 관세와 대법관 제재로 압박한다.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -28744,111 +28745,111 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
+          <t>6부 10화</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>돈의 지도</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>O Mapa do Dinheiro</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>테레자 살해와 점거 자금이 이르만다지 두 노르치의 주유소 체인과 무허가 핀테크로 세탁돼 옛 정보기관의 ‘지갑’에 닿은 흔적을 벤자밍이 찾는다.</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>6부 11화</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>개혁의 피로</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>O Cansaço das Reformas</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>연금 수급자 부정 공제 파문, 불법 채굴 단속으로 일자리를 잃은 금광촌, 끝없는 재판 뉴스 속에 지지율이 떨어진다.</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
           <t>6부 12화</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
+      <c r="B128" s="9" t="inlineStr">
         <is>
           <t>재선의 기로</t>
         </is>
       </c>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="C128" s="9" t="inlineStr">
         <is>
           <t>Na Encruzilhada</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr">
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="E126" s="9" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>재선을 반년 앞두고 지지율이 45%로 떨어지고, 군경 사령관 출신 방송인 단타스가 부상한다.</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>7부 1화</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>거짓의 기계</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>A Máquina de Mentiras</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>6부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>단타스의 치안 공세와 딥페이크, 돈 받은 가짜 증인이 몰아치고 루아나가 처음 단독 유세에 나선다.</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>7부 2화</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>유세장 테러</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>O Atentado no Comício</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>6부 6화</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>레시피의 1만 5천 명 유세장에서 폭탄이 터져 질다가 숨지고, 루아나가 팔을 크게 다친다.</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="F128" s="9" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>7부 3화</t>
+          <t>7부 1화</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>배후와 토론</t>
+          <t>거짓의 기계</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Os Mandantes e o Debate</t>
+          <t>A Máquina de Mentiras</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>6부 9화 변형</t>
+          <t>6부 3화 변형</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>수사가 옛 정보기관 네트워크의 돈을 향하는 가운데, 하파는 마지막 토론에서 테러를 표로 바꾸지 않는다.</t>
+          <t>단타스의 치안 공세와 딥페이크, 돈 받은 가짜 증인이 몰아치고 루아나가 처음 단독 유세에 나선다.</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr"/>
@@ -28856,27 +28857,27 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>7부 4화</t>
+          <t>7부 2화</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>재선의 밤</t>
+          <t>유세장 테러</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>A Noite da Reeleição</t>
+          <t>O Atentado no Comício</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>6부 12화 변형</t>
+          <t>6부 6화</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>여론조사가 끝까지 동률이던 박빙 결선에서 하파가 재선되고, 단타스는 패배를 인정해 제도권 야당의 길을 연다.</t>
+          <t>레시피의 1만 5천 명 유세장에서 폭탄이 터져 질다가 숨지고, 루아나가 팔을 크게 다친다.</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr"/>
@@ -28884,27 +28885,27 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>7부 5화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>복합위기의 발생</t>
+          <t>배후와 토론</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>A Crise Múltipla</t>
+          <t>Os Mandantes e o Debate</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>7부 2화 변형</t>
+          <t>6부 9화 변형</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>주 경찰의 파벌 소탕 작전으로 하루에 120여 명이 죽고, 민병대·파벌 전쟁과 원자재 폭락이 한꺼번에 터진다.</t>
+          <t>수사가 옛 정보기관 네트워크의 돈을 향하는 가운데, 하파는 마지막 토론에서 테러를 표로 바꾸지 않는다.</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr"/>
@@ -28912,27 +28913,27 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>7부 4화</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>비상대권의 유혹</t>
+          <t>재선의 밤</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>A Tentação da Exceção</t>
+          <t>A Noite da Reeleição</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>7부 3화</t>
+          <t>6부 12화 변형</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>하벨루 국방장관이 무기한 GLO와 작전 중 살상 군인 면책 조항을 담은 법안을 들고 온다.</t>
+          <t>여론조사가 끝까지 동률이던 박빙 결선에서 하파가 재선되고, 단타스는 패배를 인정해 제도권 야당의 길을 연다.</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
@@ -28940,27 +28941,27 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 5화</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>연기와 재갈</t>
+          <t>복합위기의 발생</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Adiar e Calar</t>
+          <t>A Crise Múltipla</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>7부 4화 변형</t>
+          <t>7부 2화 변형</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>보궐선거 연기안과 플랫폼 전면 차단안이 오른 날, 대법원은 플랫폼이 불법 게시물에 직접 책임진다고 판결한다.</t>
+          <t>이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고, 원자재 가격 폭락이 한꺼번에 덮친다.</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
@@ -28968,27 +28969,27 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 6화</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>컨설턴트 팀에게 부탁</t>
+          <t>비상대권의 유혹</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Um Pedido à Bússola</t>
+          <t>A Tentação da Exceção</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>군 장비 조달 비리 보고서를 미뤄 달라는 하파의 부탁을 카이우가 거절한다.</t>
+          <t>하벨루 국방장관이 파벨라 무기한 GLO와 작전 중 살상 군인 면책 조항을 담은 법안을 들고 온다.</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -28996,27 +28997,27 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>7부 9화</t>
+          <t>7부 7화</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>작은 월권</t>
+          <t>연기와 재갈</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Um Pequeno Excesso</t>
+          <t>Adiar e Calar</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 4화 변형</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>하파가 영장 없는 감청 한 건을 구두로 허락하고, 그 사실이 청문회에서 드러난다.</t>
+          <t>보궐선거 연기안과 플랫폼 전면 차단안이 오른 날, 대법원은 플랫폼이 불법 게시물에 직접 책임진다고 판결한다.</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
@@ -29024,27 +29025,27 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>7부 10화</t>
+          <t>7부 8화</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>루아나의 정면 대결</t>
+          <t>컨설턴트 팀에게 부탁</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>O Confronto de Luana</t>
+          <t>Um Pedido à Bússola</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 6화</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>하벨루가 비상 치안 체계의 상설화를 밀자 루아나와 비아가 공개적으로 대통령에게 맞선다.</t>
+          <t>군 장비 조달 비리 보고서를 미뤄 달라는 하파의 부탁을 카이우가 거절한다.</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
@@ -29052,27 +29053,27 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>7부 11화</t>
+          <t>7부 9화</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>벼랑 끝의 포기</t>
+          <t>작은 월권</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>A Renúncia à Beira do Abismo</t>
+          <t>Um Pequeno Excesso</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>7부 10화 변형</t>
+          <t>7부 7화</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>세베리누의 고문실 기록을 읽은 새벽, 경찰서 습격으로 병사가 죽어도 하파는 백지 GLO를 거부한다.</t>
+          <t>하파가 영장 없는 감청 한 건을 구두로 허락하고, 그 사실이 청문회에서 드러난다.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
@@ -29080,111 +29081,111 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
+          <t>7부 10화</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>루아나의 정면 대결</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>O Confronto de Luana</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>7부 8화</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>하벨루가 비상 치안 체계의 상설화를 밀자 루아나와 비아가 공개적으로 대통령에게 맞선다.</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>7부 11화</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>벼랑 끝의 포기</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>A Renúncia à Beira do Abismo</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>7부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>세베리누의 고문실 기록을 읽은 새벽, 경찰서 습격으로 병사가 죽어도 하파는 백지 GLO를 거부한다.</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
           <t>7부 12화</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>새로운 균형</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>Um Novo Equilíbrio</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>7부 12화</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>인질이 풀려나고, 하파는 위기결정위원회 법으로 비상권한을 스스로 묶기로 한다.</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="inlineStr">
-        <is>
-          <t>권력의 한계</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>Os Limites do Poder</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="E139" s="9" t="inlineStr">
-        <is>
-          <t>위기결정위원회 법 통과 직후, 하파가 「권력의 한계」 법안 착수를 대국민 발표한다.</t>
-        </is>
-      </c>
-      <c r="F139" s="9" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>8부 2화</t>
-        </is>
-      </c>
-      <c r="B140" s="9" t="inlineStr">
-        <is>
-          <t>팀의 재편</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="inlineStr">
-        <is>
-          <t>A Equipe Refeita</t>
-        </is>
-      </c>
-      <c r="D140" s="9" t="inlineStr">
-        <is>
-          <t>8부 2화</t>
-        </is>
-      </c>
-      <c r="E140" s="9" t="inlineStr">
-        <is>
-          <t>38명이 된 재정투명성청을 재편하다가, 질다의 카드 ‘커피를 잊지 말 것’이 처음 발견된다.</t>
-        </is>
-      </c>
-      <c r="F140" s="9" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>인질이 풀려나고, 하파는 모든 군 투입을 의회 승인·기한·공설변호인 입회에 묶는 위기결정위원회 법으로 비상권한을 스스로 묶기로 한다.</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>8부 3화</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>돌아온 병사들</t>
+          <t>권력의 한계</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>Os Que Voltaram</t>
+          <t>Os Limites do Poder</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>8부 3화 변형</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>18개월 GLO가 끝나 군이 철수하고, 귀환 병사들의 트라우마와 일자리가 새 숙제가 된다.</t>
+          <t>위기결정위원회 법 통과 직후, 하파가 「권력의 한계」 법안 착수를 대국민 발표한다.</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr"/>
@@ -29192,27 +29193,27 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>8부 4화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>세대교체</t>
+          <t>팀의 재편</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>A Troca de Gerações</t>
+          <t>A Equipe Refeita</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>8부 4화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>핵심 요직 12자리를 익명 공모로 뽑고, 강마을 출신 청년 알리니가 지원서를 낸다.</t>
+          <t>38명이 된 재정투명성청을 재편하다가, 질다의 카드 ‘커피를 잊지 말 것’이 처음 발견된다.</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr"/>
@@ -29220,27 +29221,27 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>8부 3화</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 마지막 대화</t>
+          <t>돌아온 병사들</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>A Última Conversa com Brandão</t>
+          <t>Os Que Voltaram</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>8부 3화 변형</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>병든 브랑당을 찾아가 감시 체계 해체와 군정 기록 공개, 루시아 사건 방조를 마지막으로 묻는다.</t>
+          <t>18개월 파벨라 GLO가 끝나 군이 철수하고, 귀환 병사들의 트라우마와 주민들의 기억이 새 숙제가 된다.</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr"/>
@@ -29248,27 +29249,27 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>8부 6화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>루아나에게 실권 위임</t>
+          <t>세대교체</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>O Poder nas Mãos de Luana</t>
+          <t>A Troca de Gerações</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>8부 6화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>노후 송전망 붕괴로 북부 주가 암흑에 빠지고, 하파는 루아나에게 실권을 넘긴다.</t>
+          <t>핵심 요직 12자리를 익명 공모로 뽑고, 강마을 출신 청년 알리니와 빌라 히반세이라의 제가 지원서를 낸다.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr"/>
@@ -29276,27 +29277,27 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>세하 파리마의 빚</t>
+          <t>브랑당의 마지막 대화</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>As Dívidas de Serra Parima</t>
+          <t>A Última Conversa com Brandão</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>숨은 보증채무가 드러난 세하 파리마주에서 마릴리아가 주지사로 당선돼 부채를 공개한다.</t>
+          <t>병든 브랑당을 찾아가 감시 체계 해체와 군정 기록 공개, 루시아 사건 방조를 마지막으로 묻는다.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr"/>
@@ -29304,27 +29305,27 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 6화</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>마지막 정치적 결전</t>
+          <t>루아나에게 실권 위임</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>O Último Combate</t>
+          <t>O Poder nas Mãos de Luana</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 6화</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>구체제 잔존 세력이 대법원·의회·방송·검찰에서 총공세를 펴고, 카이우가 옛 과오를 고백한 뒤 쓰러진다.</t>
+          <t>노후 송전망 붕괴로 북부 주가 암흑에 빠지고, 하파는 루아나에게 실권을 넘긴다.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -29332,27 +29333,27 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>8부 7화</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>법안의 최종 완성</t>
+          <t>세하 파리마의 빚</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>A Lei Concluída</t>
+          <t>As Dívidas de Serra Parima</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>8부 7화</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>「권력의 한계」법이 서명되고, 두 번의 임기 뒤 평생 재출마 금지 조항을 하파가 스스로 넣는다.</t>
+          <t>숨은 보증채무가 드러난 세하 파리마주에서 마릴리아가 주지사로 당선돼 부채를 공개한다.</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
@@ -29360,27 +29361,27 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>8부 8화</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>질다를 기리며</t>
+          <t>마지막 정치적 결전</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>Em Memória de Zilda</t>
+          <t>O Último Combate</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>8부 8화</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>추모의 밤, 하파는 ‘커피를 잊지 말 것’이 세베리누의 원칙과 같았음을 깨닫는다.</t>
+          <t>구체제 잔존 세력이 대법원·의회·방송·검찰에서 총공세를 펴고, 카이우가 옛 과오를 고백한 뒤 쓰러진다.</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr"/>
@@ -29388,27 +29389,27 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 9화</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>프라두 판결</t>
+          <t>법안의 최종 완성</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>A Sentença de Prado</t>
+          <t>A Lei Concluída</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 9화</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>프라두에게 유죄가 선고되고 해외 자산이 환수되며, NGO 낙인법 폐지 논의가 시작된다.</t>
+          <t>「권력의 한계」법이 서명되고, 두 번의 임기 뒤 평생 재출마 금지 조항을 하파가 스스로 넣는다.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -29416,111 +29417,111 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
+          <t>8부 10화</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>질다를 기리며</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>Em Memória de Zilda</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>8부 10화</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>추모의 밤, 하파는 ‘커피를 잊지 말 것’이 세베리누의 원칙과 같았음을 깨닫는다.</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>프라두 판결</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>A Sentença de Prado</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>프라두에게 유죄가 선고되고 해외 자산이 환수되며, NGO 낙인법 폐지 논의가 시작된다.</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
           <t>8부 12화</t>
         </is>
       </c>
-      <c r="B150" s="9" t="inlineStr">
+      <c r="B152" s="9" t="inlineStr">
         <is>
           <t>질다를 죽인 돈</t>
         </is>
       </c>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="C152" s="9" t="inlineStr">
         <is>
           <t>O Dinheiro Que Matou Zilda</t>
         </is>
       </c>
-      <c r="D150" s="9" t="inlineStr">
+      <c r="D152" s="9" t="inlineStr">
         <is>
           <t>8부 12화</t>
         </is>
       </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>청산된 민간은행 장부에서 대법관·의원·감독관에게 간 돈과 함께 테러 자금이 오타실리우를 가리키지만, 그는 해외로 빠져나간다.</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>마지막 해</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>O Último Ano</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>임기 1년을 남기고 단타스가 야당 지도자로 돌아오며, ‘누가 다음인가’가 떠오른다.</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>불타는 숲</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>A Floresta em Chamas</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>강이 역대 최저 수위로 마르고 아루아칸 영토가 불타는데 국제 산림기금 약속은 절반에 그치자, 하파가 귀향한다.</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>청산된 민간은행 장부와 파벌의 주유소·핀테크 세탁망에서 테러 자금이 오타실리우를 가리키지만, 그는 해외로 빠져나간다.</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>9부 3화</t>
+          <t>9부 1화</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>낙인</t>
+          <t>마지막 해</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>O Estigma</t>
+          <t>O Último Ano</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>9부 3화</t>
+          <t>9부 1화</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>외국 후원 NGO 등록·낙인법이 최종 폐지되고, 루아나가 첫 독자 정치 행보를 한다.</t>
+          <t>임기 1년을 남기고 단타스가 야당 지도자로 돌아오며, ‘누가 다음인가’가 떠오른다.</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr"/>
@@ -29528,27 +29529,27 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>9부 4화</t>
+          <t>9부 2화</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>병사의 재판</t>
+          <t>불타는 숲</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>O Julgamento do Soldado</t>
+          <t>A Floresta em Chamas</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>9부 4화 변형</t>
+          <t>9부 2화 변형</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>GLO 작전 중 소년을 쏜 귀환 병사가 일반 법원에 서고, 하파는 변호사의 눈으로 방청한다.</t>
+          <t>강이 역대 최저 수위로 마르고 아루아칸 영토가 불타는데 국제 산림기금 약속은 절반에 그치자, 하파가 귀향한다.</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr"/>
@@ -29556,27 +29557,27 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>9부 5화</t>
+          <t>9부 3화</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>루아나, 공식 후계자로</t>
+          <t>낙인</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Luana, a Sucessora</t>
+          <t>O Estigma</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>9부 5화</t>
+          <t>9부 3화</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>하파가 미뤄 둔 대화를 꺼내고, 당 예비경선에서 루아나가 공식 대선 후보로 선출된다.</t>
+          <t>외국 후원 NGO 등록·낙인법이 최종 폐지되고, 루아나가 첫 독자 정치 행보를 한다.</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr"/>
@@ -29584,27 +29585,27 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>9부 6화</t>
+          <t>9부 4화</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>개인적 화해와 정리</t>
+          <t>병사의 재판</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Acertos de Contas</t>
+          <t>O Julgamento do Soldado</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>9부 6화</t>
+          <t>9부 4화 변형</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>하파가 세베리누·아버지·모에마·오타비우·루시아·테레자의 무덤을 차례로 찾아간다.</t>
+          <t>GLO 작전 중 파벨라 소년을 쏜 귀환 병사가 일반 법원에 서고, 하파는 공설변호인의 눈으로 방청한다.</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr"/>
@@ -29612,27 +29613,27 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 5화</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>그림자의 윤곽</t>
+          <t>루아나, 공식 후계자로</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>O Contorno da Sombra</t>
+          <t>Luana, a Sucessora</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 5화</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>브랑당이 홀로 숨지고, 아무도 오지 않은 장례식에 간 하파에게 자금 운반책의 이름이 든 봉투가 남는다.</t>
+          <t>하파가 미뤄 둔 대화를 꺼내고, 당 예비경선에서 루아나가 공식 대선 후보로 선출된다.</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr"/>
@@ -29640,27 +29641,27 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>9부 8화</t>
+          <t>9부 6화</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>임기 종료를 준비하며</t>
+          <t>개인적 화해와 정리</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Preparando a Saída</t>
+          <t>Acertos de Contas</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>9부 8화 변형</t>
+          <t>9부 6화</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>임기 종료 114일 전, 하파는 봉투를 검찰에 넘기고 경호 강화와 비상권한 제안을 거절한다.</t>
+          <t>하파가 세베리누·아버지·모에마·오타비우·루시아·테레자의 무덤을 차례로 찾고, 세베리누 앞에서 처음으로 용서를 청한다.</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
@@ -29668,27 +29669,27 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>9부 7화</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>마릴리아</t>
+          <t>그림자의 윤곽</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Marília</t>
+          <t>O Contorno da Sombra</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>9부 7화</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>결선에서 이긴 당선인 루아나가 마릴리아를 수석장관으로 택하고, 지방 출신 두 사람이 마주 앉는다.</t>
+          <t>브랑당이 홀로 숨지고, 아무도 오지 않은 장례식에 간 하파에게 자금 운반책의 이름이 든 봉투가 남는다.</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
@@ -29696,27 +29697,27 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>9부 8화</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>마지막 이양 준비</t>
+          <t>임기 종료를 준비하며</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Os Últimos Preparativos</t>
+          <t>Preparando a Saída</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>9부 8화 변형</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>임기 마지막 날인 새해 전날 밤, 경호를 줄인 채 강변을 걷던 하파가 저격당해 루아나의 품에서 숨진다.</t>
+          <t>임기 종료 114일 전, 하파는 봉투를 검찰에 넘기고 경호 강화와 비상권한 제안을 거절한다.</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr"/>
@@ -29724,27 +29725,27 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>9부 9화</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>홀로 선 자리</t>
+          <t>마릴리아</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>O Lugar de Quem Fica Só</t>
+          <t>Marília</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>9부 9화</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>사흘 애도 뒤로 취임을 미루자는 권유를 물리치고 루아나가 1월 1일 예정대로 선서한다.</t>
+          <t>결선에서 이긴 당선인 루아나가 마릴리아를 수석장관으로 택하고, 지방 출신 두 사람이 마주 앉는다.</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
@@ -29752,27 +29753,27 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>9부 12화</t>
+          <t>9부 10화</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>수사의 끝</t>
+          <t>마지막 이양 준비</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>O Fim da Investigação</t>
+          <t>Os Últimos Preparativos</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>9부 12화</t>
+          <t>9부 10화</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>독립수사단·검찰·의회 조사위가 각자 절차로 테러와 암살의 돈줄을 오타실리우로 입증하고, 루아나는 개입하지 않는다.</t>
+          <t>임기 마지막 날인 새해 전날 밤, 경호를 줄인 채 강변을 걷던 하파가 저격당해 루아나의 품에서 숨진다.</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr"/>
@@ -29780,47 +29781,103 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
+          <t>9부 11화</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>홀로 선 자리</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>O Lugar de Quem Fica Só</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>9부 11화</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>사흘 애도 뒤로 취임을 미루자는 권유를 물리치고 루아나가 1월 1일 예정대로 선서한다.</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>9부 12화</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>수사의 끝</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>O Fim da Investigação</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>9부 12화</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>독립수사단·검찰·의회 조사위가 각자 절차로 파벌 세탁망을 거친 테러와 암살의 돈줄을 오타실리우로 입증하고, 루아나는 개입하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
           <t>9부 에필로그</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>연결 고리</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
         <is>
           <t>O Elo</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t>9부 에필로그 변형</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>4년 뒤 인도된 오타실리우가 재판정에 서는 아침, 루아나가 임기를 마치고 마릴리아 누니스가 대통령 선서를 한다.</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr"/>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>4년 뒤 인도된 오타실리우가 공설변호인과 함께 재판정에 서는 아침, 루아나가 임기를 마치고 마릴리아 누니스가 선서한다. 제는 공설변호인 시험에 붙는다.</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A41:F41"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A55:F55"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A53:F53"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B9:F9"/>

--- a/기획안/국가별_각색_기획안.xlsx
+++ b/기획안/국가별_각색_기획안.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 상파울루 파우리스타 대로의 대형 로펌에서 시작해 가상 아마존 주 ‘타피라주(Estado de Tapirá)’의 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’(주인공의 고향)와 강변 파벨라 ‘빌라 히반세이라(Vila Ribanceira)’, 아루아칸 원주민 영토를 거쳐 브라질리아로. 교도소에서 태어난 가상 조직범죄 파벌(facção) ‘이르만다지 두 노르치(Irmandade do Norte)’가 강의 코카인 경로·불법 금광·숲속 비행장을 잇고, 도시에서는 전·현직 경찰 출신 민병대(milícia)와 파벨라의 통제권을 다툰다. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회, 헌법기관으로서의 공설변호인청(Defensoria Pública). 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
+          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 상파울루 파우리스타 대로의 대형 로펌(무너진 동부 버스전용로 고가도로, 리우데자네이루주 해안 가상 항구 ‘이타과레’의 조선소 건조독까지 오가는 고객 사건들)에서 시작해 가상 아마존 주 ‘타피라주(Estado de Tapirá)’의 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’(주인공의 고향)와 강변 파벨라 ‘빌라 히반세이라(Vila Ribanceira)’, 아루아칸 원주민 영토를 거쳐 브라질리아로. 교도소에서 태어난 가상 조직범죄 파벌(facção) ‘이르만다지 두 노르치(Irmandade do Norte)’가 강의 코카인 경로·불법 금광·숲속 비행장을 잇고, 도시에서는 전·현직 경찰 출신 민병대(milícia)와 파벨라의 통제권을 다툰다. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회, 헌법기관으로서의 공설변호인청(Defensoria Pública). 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>상파울루 대형 로펌 ‘케이로스 타바리스’ 기업소송 변호사(프라두 그룹 담당) → 사직 → 공설변호인 시험 합격, 노바 카라자이 공설변호인(Defensoria Pública)·인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 출마를 위한 공직 사퇴(desincompatibilização)·땅과노동당(PTT) 창당 참여 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
+          <t>상파울루 대형 로펌 ‘케이로스 타바리스’ 기업소송 변호사(프라두 그룹·건설사·방산업체·조선소 담당) → 사직 → 공설변호인 시험 합격, 노바 카라자이 공설변호인(Defensoria Pública)·인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 출마를 위한 공직 사퇴(desincompatibilização)·땅과노동당(PTT) 창당 참여 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
+          <t>무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 12화 안에서 프라두·세베리누·수은의 척추 사이에 건설사(모라이스 레아우)·방산업체(센치넬라 아우스트랄)·조선소(마레 아우타) 세 고객의 1~2화 사건 아크를 끼워 하파의 재능과 도덕적 대가가 함께 쌓이게 했으며(세 고객은 3·4·6·7·8·9부에 돌아온다), 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다. [4차 개정 추가] 파벨라 주민을 범죄의 배경으로만 소비하지 말 것: 빌라 히반세이라에는 파벌과 민병대 말고도 일하는 어머니, 교회, 삼바·펑크 모임, 공동체 라디오, 대학에 간 아이(카이우)와 변호인이 되려는 청년(제페르송)이 있다. 가상 파벌 ‘이르만다지 두 노르치’는 교도소 태생 파벌이라는 구조만 참고하고 코만두 베르멜류(CV)·PCC의 이름·상징·수감자 규약·실존 지도자·실제 사건을 복제하지 않으며, 멕시코식 카르텔 액션 문법(참수·거물 두목의 쇼)으로 그리지 않는다. 5부 경찰 작전은 2025년 리우 작전을 연상시키므로 지명·날짜·사망자 수·작전명을 겹치지 않게 하고, 경찰관 개인도 일괴암적 악으로 그리지 않는다. 공설변호인을 이상화된 영웅으로 만들지 않는다: 하루 수십 건의 구금심사, 만성 인력 부족, 이기지 못하는 사건, 조직 내부의 신중론과 관료주의, 하파 자신의 조급함까지 보여 준다. 대형 로펌 변호사들도 만화적 악당이 아니라 ‘모든 사람은 변호받을 권리가 있다’는 같은 원칙을 반대편에서 말하는 사람들로 그리고, 오타비우의 선택에는 설득력 있는 논리를 준다. 로펌·기업 이름은 모두 가상이며 실존 로펌을 연상시키는 이름·주소·사건을 쓰지 않는다.</t>
+          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다. [4차 개정 추가] 파벨라 주민을 범죄의 배경으로만 소비하지 말 것: 빌라 히반세이라에는 파벌과 민병대 말고도 일하는 어머니, 교회, 삼바·펑크 모임, 공동체 라디오, 대학에 간 아이(카이우)와 변호인이 되려는 청년(제페르송)이 있다. 가상 파벌 ‘이르만다지 두 노르치’는 교도소 태생 파벌이라는 구조만 참고하고 코만두 베르멜류(CV)·PCC의 이름·상징·수감자 규약·실존 지도자·실제 사건을 복제하지 않으며, 멕시코식 카르텔 액션 문법(참수·거물 두목의 쇼)으로 그리지 않는다. 5부 경찰 작전은 2025년 리우 작전을 연상시키므로 지명·날짜·사망자 수·작전명을 겹치지 않게 하고, 경찰관 개인도 일괴암적 악으로 그리지 않는다. 공설변호인을 이상화된 영웅으로 만들지 않는다: 하루 수십 건의 구금심사, 만성 인력 부족, 이기지 못하는 사건, 조직 내부의 신중론과 관료주의, 하파 자신의 조급함까지 보여 준다. 대형 로펌 변호사들도 만화적 악당이 아니라 ‘모든 사람은 변호받을 권리가 있다’는 같은 원칙을 반대편에서 말하는 사람들로 그리고, 오타비우의 선택에는 설득력 있는 논리를 준다. 로펌·기업 이름은 모두 가상이며 실존 로펌을 연상시키는 이름·주소·사건을 쓰지 않는다. [5차 개정 추가] 1부의 세 고객(건설사 모라이스 레아우 엔지냐리아, 방산업체 센치넬라 아우스트랄, 조선소 마레 아우타)과 그 인물은 모두 가상이며, 오데브레시트·라바 자투, 엠브라에르, 아비브라스, 타우루스, 에코빅스·히우그란지 조선소, 세치 브라지우, PROSUB 등 실제 기업·사건의 이름·지배구조·계약·수치·날짜를 복제하지 않는다. 건설사 사건은 한 도시의 한 입찰 담합과 가상의 버스전용로 고가도로 붕괴로 규모를 좁히고 실제 고가도로 붕괴 참사(예: 2014년 벨루오리존치)의 경위·사망자 수를 따르지 않는다. 방산·무기 소재는 장비 사양, 실제 수출 대상국(수출처는 특정하지 않은 가상의 외국 정부로 둔다), 실존 스파이웨어·장갑차 이름을 쓰지 않고 감청이 사람에게 남긴 결과에 초점을 두며, 군인·방산 노동자를 일괴암적 악으로 그리지 않는다. 조선소 노동자의 죽음은 사고 장면을 선정적으로 재현하지 않고 유족과 동료의 시간으로 그리며, 실제 조선소 파산·산재·해양플랫폼 리베이트 사건을 연상시키는 지명·인원·금액·계약 구조를 피한다. 관용 협정(acordo de leniência)·기업회생(recuperação judicial)·기밀 봉인 같은 제도는 브라질 법에 맞게 쓰되 특정 판결을 옮기지 않는다.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -25654,7 +25654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25691,7 +25691,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>로그라인</t>
@@ -25699,7 +25699,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2015년, 상파울루 최상위 로펌의 떠오르는 별 하파엘 멘지스(32)는 최대 고객 프라두 그룹을 대리해 고향 아마존 광산도시의 수은 오염 소송에서 늙은 상대 변호사 세베리누를 꺾어 간다. 그러나 떨리는 강마을 아이들과 로펌 전략이 덮은 보고서를 보고, 자기 쪽이 만든 ‘증거’로 구금된 세베리누가 석방 당일 숨지자 사직서를 낸다. 공설변호인으로 파벨라 청년과 원주민을 변호하던 그는 공직을 버리고 출마해 주지사와 대통령에 오르고, 헌법기관 점거의 밤과 파벨라에 군을 풀라는 유혹 앞에서 권력을 스스로 묶는다. 퇴임 전날 밤 그는 저격당하지만, 그가 세운 제도는 파벌의 연료·핀테크 세탁망을 거쳐 간 암살의 돈줄을 끝까지 밝혀내 법정에 세운다.</t>
+          <t>2015년, 상파울루 최상위 로펌의 떠오르는 별 하파엘 멘지스(32)는 담합한 고가도로가 무너진 건설사, 장갑차를 수출하고 주 경찰에 감청 소프트웨어를 판 방산업체, 리베이트로 속이 빈 채 용접공이 죽은 조선소를 차례로 구해 내며 이기는 법을 익히고, 최대 고객 프라두 그룹을 대리해 고향 아마존 광산도시의 수은 오염 소송에서 늙은 상대 변호사 세베리누를 꺾어 간다. 그러나 떨리는 강마을 아이들과 로펌 전략이 덮은 보고서를 보고, 자기 쪽이 만든 ‘증거’로 구금된 세베리누가 석방 당일 숨지자 사직서를 낸다. 공설변호인으로 파벨라 청년과 원주민을 변호하던 그는 공직을 버리고 출마해 주지사와 대통령에 오르고, 헌법기관 점거의 밤과 파벨라에 군을 풀라는 유혹 앞에서 권력을 스스로 묶는다. 퇴임 전날 밤 그는 저격당하지만, 그가 세운 제도는 파벌의 연료·핀테크 세탁망을 거쳐 간 암살의 돈줄을 끝까지 밝혀내 법정에 세운다.</t>
         </is>
       </c>
     </row>
@@ -25711,7 +25711,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 상파울루 파우리스타 대로의 대형 로펌에서 시작해 가상 아마존 주 ‘타피라주(Estado de Tapirá)’의 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’(주인공의 고향)와 강변 파벨라 ‘빌라 히반세이라(Vila Ribanceira)’, 아루아칸 원주민 영토를 거쳐 브라질리아로. 교도소에서 태어난 가상 조직범죄 파벌(facção) ‘이르만다지 두 노르치(Irmandade do Norte)’가 강의 코카인 경로·불법 금광·숲속 비행장을 잇고, 도시에서는 전·현직 경찰 출신 민병대(milícia)와 파벨라의 통제권을 다툰다. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회, 헌법기관으로서의 공설변호인청(Defensoria Pública). 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
+          <t>2015년부터 2030년대 초까지의 현재·근미래 브라질. 상파울루 파우리스타 대로의 대형 로펌(무너진 동부 버스전용로 고가도로, 리우데자네이루주 해안 가상 항구 ‘이타과레’의 조선소 건조독까지 오가는 고객 사건들)에서 시작해 가상 아마존 주 ‘타피라주(Estado de Tapirá)’의 광산·제련 도시 ‘노바 카라자이(Nova Carajaí)’(주인공의 고향)와 강변 파벨라 ‘빌라 히반세이라(Vila Ribanceira)’, 아루아칸 원주민 영토를 거쳐 브라질리아로. 교도소에서 태어난 가상 조직범죄 파벌(facção) ‘이르만다지 두 노르치(Irmandade do Norte)’가 강의 코카인 경로·불법 금광·숲속 비행장을 잇고, 도시에서는 전·현직 경찰 출신 민병대(milícia)와 파벨라의 통제권을 다툰다. 연방 대통령제(4년 임기, 연속 재선 1회), 26개 주와 연방구, 주지사 직선, 2원제 의회, 헌법기관으로서의 공설변호인청(Defensoria Pública). 1964~85년 군정은 스승의 과거와 옛 정보기관 네트워크의 유산으로만 등장한다.</t>
         </is>
       </c>
     </row>
@@ -25735,7 +25735,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>상파울루 대형 로펌 ‘케이로스 타바리스’ 기업소송 변호사(프라두 그룹 담당) → 사직 → 공설변호인 시험 합격, 노바 카라자이 공설변호인(Defensoria Pública)·인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 출마를 위한 공직 사퇴(desincompatibilização)·땅과노동당(PTT) 창당 참여 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
+          <t>상파울루 대형 로펌 ‘케이로스 타바리스’ 기업소송 변호사(프라두 그룹·건설사·방산업체·조선소 담당) → 사직 → 공설변호인 시험 합격, 노바 카라자이 공설변호인(Defensoria Pública)·인권 네트워크 ‘헤지 클라레이라’ 공동 설립 → 출마를 위한 공직 사퇴(desincompatibilização)·땅과노동당(PTT) 창당 참여 → 타피라주 주지사 → 대통령(재선) → 퇴임 전날 암살</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
+    <row r="10" ht="120" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>마모</t>
@@ -25759,7 +25759,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>부마다 핵심 인물을 하나씩 잃는다: 상대 변호인이자 뒤늦은 스승 세베리누(하파의 로펌 측이 만든 ‘증거’로 구금 중 사망) → 로펌에 남아 프라두 편에 선 친구 오타비우의 배신·원주민 지도자 모에마의 투옥 → 아버지 뺑소니 사망·기자 루시아 실종 → 모에마 옥중 사망 → 오타비우 피살·루시아 유해 발견·브랑당 퇴장 → 파벌과 민병대 사이 파벨라의 공동체 라디오 진행자 도나 테레자 피살(민병대) → 감사인 질다 테러 사망과 하파 자신의 원칙의 흔들림 → 카이우 사망 → 브랑당의 고독사와 하파 암살. 1부의 상실에는 죄책감이 겹친다: 하파는 스승을 잃는 것이 아니라 자기 손으로 스승을 죽음에 몰아넣은 쪽에 서 있었다. 폭력의 방식(청부 총격, 뺑소니, 실종, 호송 지연)은 브라질에서 활동가·기자가 실제로 당해 온 위협의 가상 등가물이다.</t>
+          <t>부마다 핵심 인물을 하나씩 잃는다: 상대 변호인이자 뒤늦은 스승 세베리누(하파의 로펌 측이 만든 ‘증거’로 구금 중 사망) → 로펌에 남아 프라두 편에 선 친구 오타비우의 배신·원주민 지도자 모에마의 투옥 → 아버지 뺑소니 사망·기자 루시아 실종 → 모에마 옥중 사망 → 오타비우 피살·루시아 유해 발견·브랑당 퇴장 → 파벌과 민병대 사이 파벨라의 공동체 라디오 진행자 도나 테레자 피살(민병대) → 감사인 질다 테러 사망과 하파 자신의 원칙의 흔들림 → 카이우 사망 → 브랑당의 고독사와 하파 암살. 1부의 상실에는 죄책감이 겹친다: 하파는 스승을 잃는 것이 아니라 자기 손으로 스승을 죽음에 몰아넣은 쪽에 서 있었다. 그 죄책감은 한 번에 오지 않고 네 고객의 승리마다 쌓인다 — 담합은 자백하되 깎아 낸 철근은 덮고 현장 기사 한 사람에게 떠넘긴 고가도로 붕괴, 사흘 만에 받아 낸 장갑차 수출 허가와 표적 목록에서 스승과 기자의 번호를 보고도 봉인한 감청 소송, 플랫폼 리베이트는 살리고 죽은 용접공을 탓하며 동료들의 임금을 깎은 회생 계획, 그리고 바로 그 감청에서 나온 날조 증거. 세 고객은 이후 주지사·대통령이 된 하파 앞에 계약 해지 대상·점거 자금원·GLO 로비스트·세탁 경로로 돌아와, 과거의 승리가 권력의 적이 된다. 폭력의 방식(청부 총격, 뺑소니, 실종, 호송 지연)은 브라질에서 활동가·기자가 실제로 당해 온 위협의 가상 등가물이다.</t>
         </is>
       </c>
     </row>
@@ -25811,7 +25811,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="90" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>구성·무게중심</t>
@@ -25819,7 +25819,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>9부 × 12화 + 에필로그. 무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
+          <t>9부 × 12화 + 에필로그. 무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 12화 안에서 프라두·세베리누·수은의 척추 사이에 건설사(모라이스 레아우)·방산업체(센치넬라 아우스트랄)·조선소(마레 아우타) 세 고객의 1~2화 사건 아크를 끼워 하파의 재능과 도덕적 대가가 함께 쌓이게 했으며(세 고객은 3·4·6·7·8·9부에 돌아온다), 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
         </is>
       </c>
     </row>
@@ -25897,7 +25897,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="240" customHeight="1">
+    <row r="20" ht="345" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>민감도·주의</t>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다. [4차 개정 추가] 파벨라 주민을 범죄의 배경으로만 소비하지 말 것: 빌라 히반세이라에는 파벌과 민병대 말고도 일하는 어머니, 교회, 삼바·펑크 모임, 공동체 라디오, 대학에 간 아이(카이우)와 변호인이 되려는 청년(제페르송)이 있다. 가상 파벌 ‘이르만다지 두 노르치’는 교도소 태생 파벌이라는 구조만 참고하고 코만두 베르멜류(CV)·PCC의 이름·상징·수감자 규약·실존 지도자·실제 사건을 복제하지 않으며, 멕시코식 카르텔 액션 문법(참수·거물 두목의 쇼)으로 그리지 않는다. 5부 경찰 작전은 2025년 리우 작전을 연상시키므로 지명·날짜·사망자 수·작전명을 겹치지 않게 하고, 경찰관 개인도 일괴암적 악으로 그리지 않는다. 공설변호인을 이상화된 영웅으로 만들지 않는다: 하루 수십 건의 구금심사, 만성 인력 부족, 이기지 못하는 사건, 조직 내부의 신중론과 관료주의, 하파 자신의 조급함까지 보여 준다. 대형 로펌 변호사들도 만화적 악당이 아니라 ‘모든 사람은 변호받을 권리가 있다’는 같은 원칙을 반대편에서 말하는 사람들로 그리고, 오타비우의 선택에는 설득력 있는 논리를 준다. 로펌·기업 이름은 모두 가상이며 실존 로펌을 연상시키는 이름·주소·사건을 쓰지 않는다.</t>
+          <t>원주민 인물은 구원받는 대상이 아니라 주체로 그리고, 가상 민족 ‘아루아칸’의 언어·의례는 원주민 자문과 원주민 배우 캐스팅을 전제로 한다. 룰라·보우소나루 등 실존 정치인, 마리엘리 프랑쿠, 돔 필립스·브루누 페레이라, 시쿠 멘지스, 도로시 스탱 사건, 2023년 1월 8일 폭동 등 실제 사건을 인물·플롯으로 복제하지 말 것(모티프만 가상화). 좌우 양극화가 극심하므로 군·복음주의 신자·농민을 일괴암적 악으로 그리지 않고, 명령을 거부하는 장교·양심적 농장주를 배치한다. 파벨라 주민을 범죄의 배경으로만 소비하지 말 것. 군정 고문 묘사는 생존자 증언의 무게를 존중해 절제한다. 6부의 헌법기관 점거는 2023년 1월 8일 사건을 연상시키므로 날짜·장소 구성·실존 인물을 겹치지 않게 하고, 가담자 전체를 괴물화하지 말고 단체방에 휩쓸린 평범한 사람들의 얼굴도 보여 준다. 민병대에 살해되는 공동체 라디오 진행자는 마리엘리 프랑쿠 사건의 재현으로 읽히지 않도록 인물의 직업·배경·사건 경위를 다르게 설계한다. 결말의 암살은 정치 폭력을 선정적으로 소비하지 않도록 절제하고, 수사 과정에서 실제 수사기관을 미화하거나 조롱하지 않는다. 3차 개정에서 반영한 최근 실제 사건(전직 대통령 쿠데타 유죄 판결, 미국의 관세·대법관 제재, 2025년 리우 경찰 작전, 방쿠 마스테르 사건, INSS 연금 사기, PCC의 연료·핀테크 침투)은 현안의 뼈대만 가져오고 인물·기관·날짜·수치를 그대로 옮기지 않는다. 2026년 10월 대선이 진행 중이므로 특정 후보·정당의 선거 선전물로 읽히지 않게 양 진영 모두의 논리를 담는다. [4차 개정 추가] 파벨라 주민을 범죄의 배경으로만 소비하지 말 것: 빌라 히반세이라에는 파벌과 민병대 말고도 일하는 어머니, 교회, 삼바·펑크 모임, 공동체 라디오, 대학에 간 아이(카이우)와 변호인이 되려는 청년(제페르송)이 있다. 가상 파벌 ‘이르만다지 두 노르치’는 교도소 태생 파벌이라는 구조만 참고하고 코만두 베르멜류(CV)·PCC의 이름·상징·수감자 규약·실존 지도자·실제 사건을 복제하지 않으며, 멕시코식 카르텔 액션 문법(참수·거물 두목의 쇼)으로 그리지 않는다. 5부 경찰 작전은 2025년 리우 작전을 연상시키므로 지명·날짜·사망자 수·작전명을 겹치지 않게 하고, 경찰관 개인도 일괴암적 악으로 그리지 않는다. 공설변호인을 이상화된 영웅으로 만들지 않는다: 하루 수십 건의 구금심사, 만성 인력 부족, 이기지 못하는 사건, 조직 내부의 신중론과 관료주의, 하파 자신의 조급함까지 보여 준다. 대형 로펌 변호사들도 만화적 악당이 아니라 ‘모든 사람은 변호받을 권리가 있다’는 같은 원칙을 반대편에서 말하는 사람들로 그리고, 오타비우의 선택에는 설득력 있는 논리를 준다. 로펌·기업 이름은 모두 가상이며 실존 로펌을 연상시키는 이름·주소·사건을 쓰지 않는다. [5차 개정 추가] 1부의 세 고객(건설사 모라이스 레아우 엔지냐리아, 방산업체 센치넬라 아우스트랄, 조선소 마레 아우타)과 그 인물은 모두 가상이며, 오데브레시트·라바 자투, 엠브라에르, 아비브라스, 타우루스, 에코빅스·히우그란지 조선소, 세치 브라지우, PROSUB 등 실제 기업·사건의 이름·지배구조·계약·수치·날짜를 복제하지 않는다. 건설사 사건은 한 도시의 한 입찰 담합과 가상의 버스전용로 고가도로 붕괴로 규모를 좁히고 실제 고가도로 붕괴 참사(예: 2014년 벨루오리존치)의 경위·사망자 수를 따르지 않는다. 방산·무기 소재는 장비 사양, 실제 수출 대상국(수출처는 특정하지 않은 가상의 외국 정부로 둔다), 실존 스파이웨어·장갑차 이름을 쓰지 않고 감청이 사람에게 남긴 결과에 초점을 두며, 군인·방산 노동자를 일괴암적 악으로 그리지 않는다. 조선소 노동자의 죽음은 사고 장면을 선정적으로 재현하지 않고 유족과 동료의 시간으로 그리며, 실제 조선소 파산·산재·해양플랫폼 리베이트 사건을 연상시키는 지명·인원·금액·계약 구조를 피한다. 관용 협정(acordo de leniência)·기업회생(recuperação judicial)·기밀 봉인 같은 제도는 브라질 법에 맞게 쓰되 특정 판결을 옮기지 않는다.</t>
         </is>
       </c>
     </row>
@@ -25967,7 +25967,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1부 2화 상대편으로 첫 대면, 9화 하파의 로펌 측 ‘리스크 정보’ 업체가 만든 증인매수 자료로 날조 혐의 체포, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망</t>
+          <t>1부 3화 상대편으로 첫 대면, 6화 하파가 봉인한 감청 표적 목록에 이름이 오르고, 9화 그 감청으로 ‘리스크 정보’ 업체가 만든 증인매수 자료로 날조 혐의 체포, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -25990,12 +25990,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>하파의 법대 동기이자 케이로스 타바리스 로펌의 동료 변호사. ‘모든 고객은 변호받을 권리가 있다’를 끝까지 로펌의 논리로 믿는 사람</t>
+          <t>하파의 법대 동기이자 케이로스 타바리스 로펌의 동료 변호사. ‘모든 고객은 변호받을 권리가 있다’를 끝까지 로펌의 논리로 믿는 사람. 하파가 떠난 뒤 그의 고객 넷을 모두 물려받는다</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1부 9화 증거 조작 정황을 눈치채고 침묵, 12화 사직을 말린다. 2부 6화 파트너 승진과 함께 프라두 변호를 맡아 공익소송의 맞상대가 되고, 11화 증인 명단 유출로 배신 발각. 3부 3화 임신한 아내 앞에서 흔들려 귀환, 10화 대신 체포. 5부 6화 사법 부패 조사 중 청부 총격으로 피살</t>
+          <t>1부 9화 증거 조작 정황을 눈치채고 침묵, 12화 사직을 말린다. 2부 6화 파트너 승진과 함께 프라두와 하파의 옛 고객 셋(모라이스 레아우·센치넬라 아우스트랄·마레 아우타)을 물려받아 공익소송의 맞상대가 되고, 11화 증인 명단 유출로 배신 발각. 3부 3화 임신한 아내 앞에서 흔들려 네 고객의 로펌 내부 자료를 들고 귀환, 10화 대신 체포. 5부 6화 사법 부패 조사 중 청부 총격으로 피살</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -26023,7 +26023,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>1부 3화 프라두 측 변호사인 하파를 적으로 처음 만나고 11화 처음 손잡는다. 2부 4~5화 강의 코카인 경로·불법 금광·비행장의 겹침 추적. 3부 8화 폭로 기사 공개일 밤 실종, 5부 9화 정보기관 하부 조직에 살해된 사실 확인·유해 발견</t>
+          <t>1부 3화 프라두 측 변호사인 하파를 적으로 처음 만나고, 6화 하파가 감청 표적 목록에서 그녀의 번호를 보고도 침묵하며, 11화 처음 손잡는다. 2부 4~5화 강의 코카인 경로·불법 금광·비행장의 겹침 추적. 3부 8화 폭로 기사 공개일 밤 실종, 5부 9화 정보기관 하부 조직에 살해된 사실 확인·유해 발견</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -26143,27 +26143,27 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>크릴로프(보안기관장)</t>
+          <t>신규(로펌 대표 파트너)</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>General Aurélio Brandão</t>
+          <t>Leonor Queiroz</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>아우렐리우 브랑당 장군</t>
+          <t>레오노르 케이로스</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>가상 정보기관 ANSI(국가제도안보청) 청장. 군정 말기 정보 기관원 출신, 1부에서는 로펌이 쓰는 ‘리스크 정보’ 업체의 그림자 고문. 적대자에서 불편한 협력자로</t>
+          <t>케이로스 타바리스 창업자의 딸이자 대표 파트너. 하파를 발탁한 사내 스승으로, ‘우리는 판결을 사지 않는다, 판결이 나오기 전의 사실을 설계할 뿐’이라고 말하는 냉정하고 교양 있는 실무가. 세베리누의 거울상</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1부 8화 로펌 만찬에서 첫 등장, 4부 7화 진압 대신 협상 선택, 5부 9화 루시아 사건 방조가 드러나 사임, 8부 5화 마지막 대화, 9부 7화 홀로 병사(아무도 오지 않은 장례식)</t>
+          <t>1부 1화 하파에게 모라이스 레아우와 프라두 사건을 맡기고, 5화 축하연에서 센치넬라 아우스트랄을 소개, 12화 ‘돌아올 자리는 비워 두겠다’며 사직서를 받는다. 2부 6화 오타비우를 파트너로 올려 옛 고객들을 넘긴다. 5부 6화 오타비우 피살 뒤 로펌 내부 감사를 시작하고, 8부 12화 마레 아우타의 옛 자문 계약서를 수사단에 제출한다. 생존</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -26171,27 +26171,27 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>이리나(후계자)</t>
+          <t>신규(1부 고객: 건설사)</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Luana Marques</t>
+          <t>Válter Moraes Leal · Fabiano Rocha</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>루아나 마르키스</t>
+          <t>바우테르 모라이스 레아우 · 파비아누 호샤</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>스물두 살 법대생 자원활동가 → 수석장관(카자 시비우) → 대통령. ‘대통령의 양심’</t>
+          <t>가상 건설사 ‘모라이스 레아우 엔지냐리아’의 2세 회장 바우테르와, 상파울루 동부 버스전용로 고가도로 붕괴(7명 사망) 현장의 스물여섯 살 현장 기사 파비아누. 붕괴는 시 입찰 담합의 낙찰가를 맞추려 철근과 설계를 깎은 결과였다. 하파는 담합만 자백하는 관용 협정으로 회사를 살리고, 설계 변경은 덮은 채 붕괴 책임을 파비아누 한 사람에게 돌린다</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>4부 3화 합류, 6부 8화 점거의 밤 대통령궁을 지킨다. 7부 2화 테러로 중상, 9부 11화 1월 1일 대통령 취임, 수사 불개입 원칙을 지키고 에필로그에서 4년 임기 뒤 퇴임</t>
+          <t>1부 1~2화 관용 협정 체결, 파비아누 과실치사 기소(4화 뉴스). 3부 12화 형기를 마친 파비아누가 원설계 변경 메모로 증언하고, 주지사 하파가 모라이스 레아우의 부풀린 주 도로 계약을 해지한다. 6부 6화 바우테르의 자회사가 점거 버스 대금을 댄 사실이 드러나 6부 9화 사면 없는 재판에서 기소된다. 파비아누는 에필로그까지 타피라주 도로청 기술자로 생존</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -26199,27 +26199,27 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>카탸(참모)</t>
+          <t>신규(1부 고객: 방산업체)</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Beatriz ‘Bia’ Lisboa</t>
+          <t>Coronel (R) Rodrigo Tolentino</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>베아트리스 ‘비아’ 리스보아</t>
+          <t>호드리구 톨렌치누 예비역 대령</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>공설변호인청 인턴 법대생 출신 실무 총괄·선거본부장</t>
+          <t>가상 방산업체 ‘센치넬라 아우스트랄 방위시스템’ 회장. 개조 장갑차·탄약을 수출하고 감청 프로그램 ‘비지아’를 주 경찰에 파는데, 두 사업이 브랑당과 주 치안 당국·국방부 인맥으로 이어진 하나의 로비망을 탄다. ‘우리는 국가가 원하는 것을 만들 뿐’이라는 논리</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>끝까지 남는다. 7부 10화 처음으로 대통령에게 공개적으로 반대</t>
+          <t>1부 5화 하파가 외교부 권고를 뒤집고 장갑차·탄약 수출 허가를 받아 주고, 6화 같은 로비망의 ‘비지아’ 불법 감청 소송을 국가안보 기밀로 봉인해 준다. 7부 6화 하벨루 국방장관과 함께 파벨라 무기한 GLO(장갑차 조달)·감청 시스템 도입을 로비하고, 7부 8화 수출 장갑차가 외국 시위 진압에 쓰인 사실과 과다 계약이 카이우의 보고서로 드러난다. 8부 5화 ‘비지아’ 해체와 함께 불구속 기소</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -26227,27 +26227,27 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>그레벤시코프(정치 원로)</t>
+          <t>신규(1부 고객: 조선소)</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Anselmo Viana</t>
+          <t>Aldo Figueiró · Damiana Batista</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>안셀무 비아나</t>
+          <t>아우두 피게이로 · 다미아나 바치스타</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>금속노조 원로, 2년간 서명을 모아 땅과노동당을 등록시킨 공동 창당자·선거 전략가</t>
+          <t>리우데자네이루주 가상 항구 이타과레의 조선소 ‘마레 아우타’ 사주 아우두와, 해양플랫폼 선체 건조독 폭발로 숨진 용접공 시세루의 아내 다미아나. 플랫폼 계약 리베이트를 ‘자문료’로 빼돌려 속이 빈 조선소는 안전 설비와 임금부터 멈췄다. 하파는 시세루의 ‘가스 측정 수칙 위반’을 전제로 회생 계획을 짜 리베이트 ‘자문회사’ 채권은 살리고 노동자 3천 명의 밀린 임금을 깎는다</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>7부에서 스스로의 변질을 자각하고 흑색선전 카드를 포기, 끝까지 조언자로 남는다</t>
+          <t>1부 8화 사고와 회생 신청, 10화 채권자 집회에서 회생안 통과(다미아나가 하파에게 남편의 작업화를 내민다). 4부 6화 다미아나가 조선소 미지급 노동자들을 이끌고 전국 파업에 합류하고, 5부 3화 실소유자 공개 법안 공청회에서 체불 임금 뒤의 유령회사를 증언한다. 8부 12화 마레 아우타의 옛 플랫폼 리베이트 계좌가 오타실리우의 세탁 경로로 드러나고, 9부 12화 아우두가 협력 진술(colaboração premiada)로 돈줄을 확정해 준다. 다미아나는 에필로그까지 생존</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -26255,27 +26255,27 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>이졸다·키릴(감사팀)</t>
+          <t>크릴로프(보안기관장)</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Zilda Ferraz · Caio Andrade</t>
+          <t>General Aurélio Brandão</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>질다 페하스 · 카이우 안드라지</t>
+          <t>아우렐리우 브랑당 장군</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>민간 감사사 ‘부솔라 감사(Bússola Auditoria)’. 질다는 경력 30년 감사인으로 손님에게 먼저 커피를 내고, 카이우는 노바 카라자이 강변 파벨라 빌라 히반세이라에서 자라 장학금으로 회계를 공부한 공동창업자로 재정투명성청장이 된다(아내 나지아, 포렌식 회계사 벤자밍과 함께). 파벌 자금이 어떻게 동네 주유소와 송금 앱을 거치는지 몸으로 안다</t>
+          <t>가상 정보기관 ANSI(국가제도안보청) 청장. 군정 말기 정보 기관원 출신, 1부에서는 로펌이 쓰는 ‘리스크 정보’ 업체와 방산업체 센치넬라 아우스트랄의 그림자 고문. 적대자에서 불편한 협력자로</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>3부 12화 첫 등장. 질다는 7부 2화 레시피 유세장 테러로 사망해 카드 ‘커피를 잊지 말 것’을 남기고, 카이우는 7부 8화 대통령의 부탁을 거절한 뒤 8부 8화 12년 전 과오를 고백하고 심장 질환으로 사망</t>
+          <t>1부 5화 승소 축하연에서 첫 등장해 방산업체 수출 허가 로비망을 연결, 9화 ‘비지아’ 감청으로 만든 증인매수 자료를 하파에게 건넨다, 4부 7화 진압 대신 협상 선택, 5부 9화 루시아 사건 방조가 드러나 사임, 8부 5화 마지막 대화, 9부 7화 홀로 병사(아무도 오지 않은 장례식)</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -26283,27 +26283,27 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>조야(스승의 지기)</t>
+          <t>이리나(후계자)</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Zoraide Pereira</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>조라이지 페레이라</t>
+          <t>루아나 마르키스</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>은퇴한 변호사회 서기, 세베리누의 35년 지기. 군정 시절 기록 보관자</t>
+          <t>스물두 살 법대생 자원활동가 → 수석장관(카자 시비우) → 대통령. ‘대통령의 양심’</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>1부 12화 장례식에서 하파에게 세베리누의 커피잔을 건넨다. 7부 11화 세베리누의 기록을 건넨다. 에필로그까지 생존</t>
+          <t>4부 3화 합류, 6부 8화 점거의 밤 대통령궁을 지킨다. 7부 2화 테러로 중상, 9부 11화 1월 1일 대통령 취임, 수사 불개입 원칙을 지키고 에필로그에서 4년 임기 뒤 퇴임</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -26311,27 +26311,27 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>마리나 젤레즈냐크(내부고발자→후임 대통령)</t>
+          <t>카탸(참모)</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Marília Nunes</t>
+          <t>Beatriz ‘Bia’ Lisboa</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>마릴리아 누니스</t>
+          <t>베아트리스 ‘비아’ 리스보아</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>희토류 산지 ‘세하 파리마주’ 부지사, 주지사의 반란 때 내부고발</t>
+          <t>공설변호인청 인턴 법대생 출신 실무 총괄·선거본부장</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>5부 4~5화 제보·파업 수습 협력, 8부 7화 주지사 당선·부채 공개, 9부 9화 루아나의 수석장관, 에필로그 대통령 취임</t>
+          <t>끝까지 남는다. 7부 10화 처음으로 대통령에게 공개적으로 반대</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -26339,27 +26339,27 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>보구슬랍스키(재무차관·자금원)</t>
+          <t>그레벤시코프(정치 원로)</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Otacílio Barreto</t>
+          <t>Anselmo Viana</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>오타실리우 바헤투</t>
+          <t>안셀무 비아나</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>전 재무부 사무차관, 옛 정보기관 비자금의 ‘지갑’</t>
+          <t>금속노조 원로, 2년간 서명을 모아 땅과노동당을 등록시킨 공동 창당자·선거 전략가</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>5부 1화 ‘1년 뒤엔 당신 없다’, 6부 10화 이르만다지 두 노르치의 연료·핀테크 세탁망에 이름이 스친다. 8부 12화 해외 도피, 9부 12화 테러·암살 자금원으로 확정·기소, 에필로그에서 국제 사법공조로 인도되어 공설변호인이 붙은 재판정에 선다</t>
+          <t>7부에서 스스로의 변질을 자각하고 흑색선전 카드를 포기, 끝까지 조언자로 남는다</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -26367,27 +26367,27 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>코발추크(포퓰리스트 경쟁자)</t>
+          <t>이졸다·키릴(감사팀)</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Artur Dantas</t>
+          <t>Zilda Ferraz · Caio Andrade</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>아르투르 단타스</t>
+          <t>질다 페하스 · 카이우 안드라지</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>주 군경 사령관 출신 TV 진행자, 치안 포퓰리스트 대선 후보</t>
+          <t>민간 감사사 ‘부솔라 감사(Bússola Auditoria)’. 질다는 경력 30년 감사인으로 손님에게 먼저 커피를 내고, 카이우는 노바 카라자이 강변 파벨라 빌라 히반세이라에서 자라 장학금으로 회계를 공부한 공동창업자로 재정투명성청장이 된다(아내 나지아, 포렌식 회계사 벤자밍과 함께). 파벌 자금이 어떻게 동네 주유소와 송금 앱을 거치는지 몸으로 안다</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>6부 점거의 밤 거리를 두며 선을 긋고, 7부 4화 패배 인정, 9부 1화 제도권 야당 지도자로 재등장</t>
+          <t>3부 12화 첫 등장. 질다는 7부 2화 레시피 유세장 테러로 사망해 카드 ‘커피를 잊지 말 것’을 남기고, 카이우는 7부 8화 대통령의 부탁을 거절한 뒤 8부 8화 12년 전 과오를 고백하고 심장 질환으로 사망</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -26395,27 +26395,27 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>신규(파벨라 청년)</t>
+          <t>조야(스승의 지기)</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Jéferson ‘Jé’ Souza</t>
+          <t>Zoraide Pereira</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>제페르송 ‘제’ 소우자</t>
+          <t>조라이지 페레이라</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>빌라 히반세이라의 열아홉 살 배달 노동자. 이르만다지 두 노르치의 ‘운반책’으로 몰려 구금심사에 선 하파의 첫 의뢰인</t>
+          <t>은퇴한 변호사회 서기, 세베리누의 35년 지기. 군정 시절 기록 보관자</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2부 2~3화 무죄, 3부 4화 파벌 통제 구역에서 유세단의 길을 협상, 8부 4화 공개 공모에 지원, 에필로그 공설변호인 시험 합격</t>
+          <t>1부 12화 장례식에서 하파에게 세베리누의 커피잔을 건넨다. 7부 11화 세베리누의 기록을 건넨다. 에필로그까지 생존</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -26423,529 +26423,529 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>신규(공동체 라디오)</t>
+          <t>마리나 젤레즈냐크(내부고발자→후임 대통령)</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Tereza Conceição (Dona Tereza)</t>
+          <t>Marília Nunes</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>테레자 콘세이상(도나 테레자)</t>
+          <t>마릴리아 누니스</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>수도권 위성도시 파벨라의 공동체 라디오 진행자, 파벌과 민병대 양쪽의 ‘보호’를 모두 거부하고 가스값·통근 밴·실종을 방송하는 60대 여성</t>
+          <t>희토류 산지 ‘세하 파리마주’ 부지사, 주지사의 반란 때 내부고발</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>6부 1화 등장, 2화 민병대 총격으로 사망. 9부 6화 하파가 무덤을 찾는다</t>
+          <t>5부 4~5화 제보·파업 수습 협력, 8부 7화 주지사 당선·부채 공개, 9부 9화 루아나의 수석장관, 에필로그 대통령 취임</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>보구슬랍스키(재무차관·자금원)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Otacílio Barreto</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>오타실리우 바헤투</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>전 재무부 사무차관, 옛 정보기관 비자금의 ‘지갑’</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화 마레 아우타 회생안 속 해양플랫폼 리베이트 ‘자문료’ 유령회사의 실소유주로 이름 없이 스친다. 5부 1화 ‘1년 뒤엔 당신 없다’, 6부 10화 이르만다지 두 노르치의 연료·핀테크 세탁망에 이름이 스친다. 8부 12화 마레 아우타의 옛 자문료 계좌가 그를 가리키는 가운데 해외 도피, 9부 12화 테러·암살 자금원으로 확정·기소, 에필로그에서 국제 사법공조로 인도되어 공설변호인이 붙은 재판정에 선다</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>3. 부 구성</t>
-        </is>
-      </c>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>코발추크(포퓰리스트 경쟁자)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Artur Dantas</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>아르투르 단타스</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>주 군경 사령관 출신 TV 진행자, 치안 포퓰리스트 대선 후보</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>6부 점거의 밤 거리를 두며 선을 긋고, 7부 4화 패배 인정, 9부 1화 제도권 야당 지도자로 재등장</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>부</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>제목(한국어)</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>제목(현지어)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>시기·주인공 신분</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>줄거리</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>핵심 상실</t>
-        </is>
-      </c>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>신규(파벨라 청년)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Jéferson ‘Jé’ Souza</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>제페르송 ‘제’ 소우자</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>빌라 히반세이라의 열아홉 살 배달 노동자. 이르만다지 두 노르치의 ‘운반책’으로 몰려 구금심사에 선 하파의 첫 의뢰인</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2부 2~3화 무죄, 3부 4화 파벌 통제 구역에서 유세단의 길을 협상, 8부 4화 공개 공모에 지원, 에필로그 공설변호인 시험 합격</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>1부</t>
+          <t>신규(공동체 라디오)</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>강의 금</t>
+          <t>Tereza Conceição (Dona Tereza)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>O Ouro do Rio</t>
+          <t>테레자 콘세이상(도나 테레자)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2015년, 상파울루와 노바 카라자이·아루아칸 영토 / 상파울루 대형 로펌 ‘케이로스 타바리스’의 떠오르는 별(32세), 프라두 그룹 담당 소송 변호사</t>
+          <t>수도권 위성도시 파벨라의 공동체 라디오 진행자, 파벌과 민병대 양쪽의 ‘보호’를 모두 거부하고 가스값·통근 밴·실종을 방송하는 60대 여성</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>하파는 최대 고객 프라두 그룹을 대리해 고향 노바 카라자이의 수은 오염 소송에서 강마을과 아루아칸을 대리한 노변호사 세베리누를 꺾어 가고, 프라두를 쫓는 기자 루시아와는 적으로 만난다. 떨리는 아이들과 로펌 전략이 덮은 내부 보고서를 본 뒤, 자기가 제출한 날조 ‘증거’로 세베리누가 구금돼 석방 당일 숨지자 죄책감 속에 사직서를 낸다.</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>상대 변호인이자 뒤늦은 스승 세베리누 아우부케르키의 구금 중 사망(하파 자신이 가담한 죽음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>2부</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>변호받을 권리</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>O Direito de Defesa</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>2016~2017년, 노바 카라자이·빌라 히반세이라와 브라질리아 / 노바 카라자이 공설변호인(Defensoria Pública), 헤지 클라레이라 공동 설립자</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>공설변호인 시험에 붙은 하파는 파벨라 청년들이 경찰 조서 한 장으로 파벌의 ‘운반책’이 되는 구금심사장에서 일하고, 수은 강마을을 위해 공익소송(ação civil pública)을 낸다. 루시아가 강의 코카인 경로와 불법 금광·비행장의 겹침을 추적하는 사이, 로펌에 남은 오타비우는 프라두 편에서 그를 배신하고 도로를 막은 모에마는 하파의 변론에도 투옥된다.</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>오타비우의 배신과 모에마의 징역 4년</t>
-        </is>
-      </c>
+          <t>6부 1화 등장, 2화 민병대 총격으로 사망. 9부 6화 하파가 무덤을 찾는다</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>3부</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>문턱의 정치</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>A Política do Limiar</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>2018~2020년, 타피라주 / 공설변호인 사퇴 → 땅과노동당 후보 → 타피라주 주지사</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>출마하려면 공직을 떠나야 한다: 하파는 선거 여섯 달 전 공설변호인직을 사퇴하고(아버지는 두 번째로 ‘안정’을 버리는 아들에게 반대한다) 신생 땅과노동당의 주지사 후보가 된다. 파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할 수 있는지 정하는 선거에서 아버지가 뺑소니로 죽고 루시아는 폭로 기사 공개일에 사라진다. 선거 목장을 막고 당선되며, 1년 반 뒤 대선 후보로 지명된다.</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>아버지 니바우두의 죽음과 루시아의 실종</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>3. 부 구성</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>4부</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>플라나우투로 가는 길</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>O Caminho do Planalto</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>2021~2022년 / 대선 후보 → 대통령 당선인</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>물가·가뭄·원주민 영토 침탈로 나라가 흔들린다. 모에마가 옥중 단식 끝에 숨지자 전국 파업이 번지고, 정권의 비밀 자금이 드러나 대통령이 사임한다. 하파는 결선에서 이긴다.</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>모에마의 옥중 사망</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>부</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>제목(한국어)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>제목(현지어)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>시기·주인공 신분</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>줄거리</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>핵심 상실</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>5부</t>
+          <t>1부</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>권력과 전장</t>
+          <t>강의 금</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>O Poder e a Trincheira</t>
+          <t>O Ouro do Rio</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2023~2024년, 첫 임기 전반 / 대통령(1기)</t>
+          <t>2015년, 상파울루와 노바 카라자이·아루아칸 영토 / 상파울루 대형 로펌 ‘케이로스 타바리스’의 떠오르는 별(32세), 프라두 그룹·건설사·방산업체·조선소 담당 소송 변호사</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>재정투명성청이 정보기관 비밀 운영비와 프라두의 제국을 파헤치고, 공설변호인청 예산 자율 개헌을 밀며 세하 파리마주의 반란과 군경 파업을 협상으로 넘긴다. 남동부 한 주 경찰이 파벨라에서 벌인 치명적 소탕 작전이 연방-주 권한 충돌로 번지고, 오타비우가 피살되고 루시아의 죽음이 확인되며 브랑당이 물러나지만, 그 사이 불복의 씨앗이 자란다.</t>
+          <t>하파는 케이로스 타바리스의 떠오르는 별로 네 고객을 한 해에 이긴다: 담합 낙찰가에 맞춰 철근을 뺀 고가도로가 무너진 건설사 모라이스 레아우(담합만 자백하는 관용 협정, 붕괴 책임은 현장 기사 한 사람에게), 같은 로비망으로 장갑차·탄약 수출 허가를 받고 주 경찰의 기자·변호사 감청을 국가 기밀로 봉인한 방산업체 센치넬라 아우스트랄, 플랫폼 리베이트로 속이 빈 채 건조독에서 용접공이 죽은 조선소 마레 아우타(리베이트는 살리고 임금은 깎은 회생 계획), 그리고 고향 노바 카라자이 수은 소송에서 노변호사 세베리누를 꺾어 가는 프라두 그룹. 승리마다 치른 값이 쌓이던 끝에, 자기가 봉인한 감청에서 나온 날조 ‘증거’로 세베리누가 구금돼 석방 당일 숨지자 하파는 네 사건의 이름을 적은 사직서를 낸다.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>오타비우 피살, 루시아 사망 확인, 브랑당의 퇴장</t>
+          <t>상대 변호인이자 뒤늦은 스승 세베리누 아우부케르키의 구금 중 사망(하파 자신이 가담한 죽음)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>6부</t>
+          <t>2부</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>삼권의 밤</t>
+          <t>변호받을 권리</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>A Noite dos Três Poderes</t>
+          <t>O Direito de Defesa</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2025~2026년, 첫 임기 후반 / 대통령(1기)</t>
+          <t>2016~2017년, 노바 카라자이·빌라 히반세이라와 브라질리아 / 노바 카라자이 공설변호인(Defensoria Pública), 헤지 클라레이라 공동 설립자</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>수도권 위성도시 파벨라를 두고 이르만다지 두 노르치와 민병대가 다투는 사이, 민병대와 대선 불복 단체방, 예비역 장교들이 하나의 망으로 엮인다. 양쪽을 모두 방송하던 공동체 라디오 진행자 도나 테레자가 민병대에 살해되고, 불복 세력이 의회·대법원·대통령궁을 점거한 밤을 하파는 비상권한 없이 헌법 절차로 넘긴다. 사면도 보복도 없이 법원에 맡기자 외국 정부가 관세와 대법관 제재로 압박하지만 사법 주권을 지키고, 점거 자금이 파벌의 주유소 체인·핀테크로 세탁된 돈임이 드러난다.</t>
+          <t>공설변호인 시험에 붙은 하파는 파벨라 청년들이 경찰 조서 한 장으로 파벌의 ‘운반책’이 되는 구금심사장에서 일하고, 수은 강마을을 위해 공익소송(ação civil pública)을 낸다. 루시아가 강의 코카인 경로와 불법 금광·비행장의 겹침을 추적하는 사이, 로펌에 남아 하파의 옛 고객들을 물려받은 오타비우는 프라두 편에서 그를 배신하고 도로를 막은 모에마는 하파의 변론에도 투옥된다.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>민병대에 살해된 공동체 라디오 진행자 도나 테레자</t>
+          <t>오타비우의 배신과 모에마의 징역 4년</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>7부</t>
+          <t>3부</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>재신임과 유혹</t>
+          <t>문턱의 정치</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>A Reeleição e a Tentação</t>
+          <t>A Política do Limiar</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2026~2027년, 재선 캠페인과 두 번째 임기 1~7개월 / 대통령(재선 후보 → 2기)</t>
+          <t>2018~2020년, 타피라주 / 공설변호인 사퇴 → 땅과노동당 후보 → 타피라주 주지사</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>박빙의 재선전은 레시피 유세장 테러로 질다를 잃은 채 끝난다. 두 번째 임기 초 이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고 원자재 가격이 폭락하자 파벨라 무기한 GLO·군인 면책·선거 연기·플랫폼 차단의 유혹이 오고, 하파는 한 번 선을 넘은 뒤 루아나와 부딪치고 벼랑 끝에서 백지 권한을 포기한다.</t>
+          <t>출마하려면 공직을 떠나야 한다: 하파는 선거 여섯 달 전 공설변호인직을 사퇴하고(아버지는 두 번째로 ‘안정’을 버리는 아들에게 반대한다) 신생 땅과노동당의 주지사 후보가 된다. 파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할 수 있는지 정하는 선거에서 아버지가 뺑소니로 죽고 루시아는 폭로 기사 공개일에 사라진다. 선거 목장을 막고 당선된 그는 자신이 한때 살려 낸 모라이스 레아우의 부풀린 주 도로 계약을 해지하고, 1년 반 뒤 대선 후보로 지명된다.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>질다 페하스의 테러 사망, 하파 자신의 원칙에 대한 확신</t>
+          <t>아버지 니바우두의 죽음과 루시아의 실종</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>8부</t>
+          <t>4부</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>권력의 무게</t>
+          <t>플라나우투로 가는 길</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>O Peso do Poder</t>
+          <t>O Caminho do Planalto</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2027~2029년, 두 번째 임기 1~2년차 / 대통령(2기)</t>
+          <t>2021~2022년 / 대선 후보 → 대통령 당선인</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>「권력의 한계」법으로 권력을 나누고 루아나에게 실권을 넘긴다. 파벨라에서 돌아온 병사, 감시 체계 해체, 지방 부채를 다루는 사이 카이우가 쓰러지고, 질다를 죽인 돈은 파벌의 세탁망을 거쳐 해외로 빠져나간다.</t>
+          <t>물가·가뭄·원주민 영토 침탈로 나라가 흔들린다. 모에마가 옥중 단식 끝에 숨지자 임금을 떼인 조선소 노동자들까지 합류한 전국 파업이 번지고, 정권의 비밀 자금이 드러나 대통령이 사임한다. 하파는 결선에서 이긴다.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>카이우 안드라지의 죽음, 자금원 오타실리우의 해외 도피</t>
+          <t>모에마의 옥중 사망</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>9부</t>
+          <t>5부</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>홀로 선 자리</t>
+          <t>권력과 전장</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>O Lugar de Quem Fica Só</t>
+          <t>O Poder e a Trincheira</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2030년(마지막 해)~2031년, 에필로그 2035년 / 대통령(임기 마지막 해) → 퇴임 → 사망</t>
+          <t>2023~2024년, 첫 임기 전반 / 대통령(1기)</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>가뭄과 산불 속 귀향, 낙인법 폐지, 파벨라 소년을 쏜 병사의 재판, 후계 선출. 브랑당이 홀로 죽고, 하파는 퇴임 전날 밤 저격당한다. 루아나는 홀로 선서하고, 수사기관·법원·의회가 각자의 절차로 파벌의 연료·핀테크 세탁망을 거친 암살의 돈줄을 끝까지 밝혀낸다.</t>
+          <t>재정투명성청이 정보기관 비밀 운영비와 프라두의 제국과 임금을 떼인 조선소 뒤의 유령회사를 파헤치고, 공설변호인청 예산 자율 개헌을 밀며 세하 파리마주의 반란과 군경 파업을 협상으로 넘긴다. 남동부 한 주 경찰이 파벨라에서 벌인 치명적 소탕 작전이 연방-주 권한 충돌로 번지고, 오타비우가 피살되고 루시아의 죽음이 확인되며 브랑당이 물러나지만, 그 사이 불복의 씨앗이 자란다.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>브랑당의 고독한 죽음과 하파의 암살</t>
+          <t>오타비우 피살, 루시아 사망 확인, 브랑당의 퇴장</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>6부</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>삼권의 밤</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>A Noite dos Três Poderes</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>2025~2026년, 첫 임기 후반 / 대통령(1기)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>수도권 위성도시 파벨라를 두고 이르만다지 두 노르치와 민병대가 다투는 사이, 민병대와 대선 불복 단체방, 예비역 장교들이 하나의 망으로 엮인다. 양쪽을 모두 방송하던 공동체 라디오 진행자 도나 테레자가 민병대에 살해되고, 불복 세력이 의회·대법원·대통령궁을 점거한 밤을 하파는 비상권한 없이 헌법 절차로 넘긴다. 사면도 보복도 없이 법원에 맡기자 외국 정부가 관세와 대법관 제재로 압박하지만 사법 주권을 지키고, 점거 버스 대금이 하파의 옛 고객 모라이스 레아우의 자회사에서, 나머지 자금이 파벌의 주유소 체인·핀테크로 세탁된 돈에서 나왔음이 드러난다.</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>민병대에 살해된 공동체 라디오 진행자 도나 테레자</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>4. 화별 구성</t>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>7부</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>재신임과 유혹</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>A Reeleição e a Tentação</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>2026~2027년, 재선 캠페인과 두 번째 임기 1~7개월 / 대통령(재선 후보 → 2기)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>박빙의 재선전은 레시피 유세장 테러로 질다를 잃은 채 끝난다. 두 번째 임기 초 이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고 원자재 가격이 폭락하자 하벨루 국방장관과 장갑차·감청 장비를 파는 방산업체 센치넬라 아우스트랄의 로비 속에 파벨라 무기한 GLO·군인 면책·선거 연기·플랫폼 차단·감청의 유혹이 오고, 하파는 한때 자신이 봉인해 준 감청 시스템으로 한 번 선을 넘은 뒤 루아나와 부딪치고 벼랑 끝에서 백지 권한을 포기한다.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>질다 페하스의 테러 사망, 하파 자신의 원칙에 대한 확신</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>부·화</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>제목(한국어)</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>제목(현지어)</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>대응 원작 화</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>한 줄 줄거리</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr"/>
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>8부</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>권력의 무게</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>O Peso do Poder</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>2027~2029년, 두 번째 임기 1~2년차 / 대통령(2기)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>「권력의 한계」법으로 권력을 나누고 루아나에게 실권을 넘긴다. 파벨라에서 돌아온 병사, 감시 체계 해체, 지방 부채를 다루는 사이 카이우가 쓰러지고, 질다를 죽인 돈은 파벌의 세탁망과 조선소 마레 아우타의 옛 ‘자문료’ 유령회사를 거쳐 해외로 빠져나간다.</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>카이우 안드라지의 죽음, 자금원 오타실리우의 해외 도피</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>1부 1화</t>
+          <t>9부</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>떠오르는 별</t>
+          <t>홀로 선 자리</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>A Estrela da Casa</t>
+          <t>O Lugar de Quem Fica Só</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1부 1화 변형</t>
+          <t>2030년(마지막 해)~2031년, 에필로그 2035년 / 대통령(임기 마지막 해) → 퇴임 → 사망</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>상파울루 로펌 케이로스 타바리스의 서른두 살 하파가 인수합병을 따내고, 최대 고객 프라두 그룹의 타피라 수은 소송을 맡는다.</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>1부 2화</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>상대편의 커피</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>O Cafezinho do Adversário</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>1부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>고향 노바 카라자이로 간 하파에게 상대 변호인 세베리누가 먼저 커피를 내고, 하파는 그가 군정 말기 제명된 변호사임을 안다.</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
+          <t>가뭄과 산불 속 귀향, 낙인법 폐지, 파벨라 소년을 쏜 병사의 재판, 후계 선출. 브랑당이 홀로 죽고, 하파는 퇴임 전날 밤 저격당한다. 루아나는 홀로 선서하고, 수사기관·법원·의회가 각자의 절차로 파벌의 연료·핀테크 세탁망을 거친 암살의 돈줄을 끝까지 밝혀낸다.</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>브랑당의 고독한 죽음과 하파의 암살</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>1부 3화</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>적으로 만난 기자</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>A Jornalista do Outro Lado</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>1부 6화 변형</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>법원 계단에서 프라두의 금을 쫓는 기자 루시아가 하파를 ‘독의 변호인’이라 몰아붙이고, 둘은 적으로 만난다.</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>4. 화별 구성</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>1부 4화</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>아버지의 식탁</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>A Mesa do Pai</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>1부 4화 변형</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>프라두 제련소 정비공 출신 아버지는 아들을 자랑하지만, 렌터카에 ‘살인자’가 긁히고 밤의 전화가 온다.</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>부·화</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>제목(한국어)</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>제목(현지어)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>대응 원작 화</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>한 줄 줄거리</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>1부 5화</t>
+          <t>1부 1화</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>작은 승리</t>
+          <t>떠오르는 별</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Uma Pequena Vitória</t>
+          <t>A Estrela da Casa</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 변형</t>
+          <t>1부 1화 변형</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>수은을 무허가 채굴꾼 탓으로 돌린 감정서로 하파가 첫 판결을 이기고, 축하연에서 프라두가 직접 그를 치하한다.</t>
+          <t>상파울루 동부 고가도로 붕괴로 일곱 명이 숨지고 담합 낙찰가에 맞춰 뺀 철근 이야기가 돌자, 서른두 살 하파가 시공사 모라이스 레아우와 프라두 수은 소송을 한 주에 맡는다.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -26953,27 +26953,27 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>1부 6화</t>
+          <t>1부 2화</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>회색지대</t>
+          <t>관용 협정</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Zona Cinzenta</t>
+          <t>O Acordo de Leniência</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1부 3화 변형</t>
+          <t>1부 1화 확장</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>로펌이 강마을에 합의금과 비밀유지 서약을 내밀고, 서명하러 간 하파는 손이 떨리는 아이들을 처음 본다.</t>
+          <t>하파는 담합만 자백하고 설계 변경은 덮는 관용 협정으로 회사를 살려 내고, 붕괴 책임은 스물여섯 살 현장 기사 파비아누 한 사람에게 돌린다.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -26981,27 +26981,27 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>1부 7화</t>
+          <t>1부 3화</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>숲의 현장검증</t>
+          <t>상대편의 커피</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>A Inspeção Judicial</t>
+          <t>O Cafezinho do Adversário</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1부 7화 변형</t>
+          <t>1부 2화 변형</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>아루아칸 영토 현장검증에서 모에마와 마주하고, 프라두 광구 경계의 무장 준설선을 기록하던 숲 지킴이 청년이 총에 맞는다.</t>
+          <t>고향 노바 카라자이에서 상대 변호인 세베리누가 먼저 커피를 내고, 법원 계단에서는 기자 루시아가 하파를 ‘독의 변호인’이라 부른다.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -27009,27 +27009,27 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 4화</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>브랑당의 그림자</t>
+          <t>아버지의 식탁</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>A Sombra de Brandão</t>
+          <t>A Mesa do Pai</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1부 8화 변형</t>
+          <t>1부 4화 변형</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>로펌 만찬에서 ‘리스크 정보’ 업체 고문 브랑당 장군이 세베리누가 증인을 매수했다는 자료를 건넨다.</t>
+          <t>파비아누 기소 뉴스에 정비공 출신 아버지가 ‘갚는 건 늘 현장 사람’이라 중얼거리고, 렌터카에 ‘살인자’가 긁히며 밤의 전화가 온다.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -27037,27 +27037,27 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>1부 9화</t>
+          <t>1부 5화</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>고발장</t>
+          <t>작은 승리</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>A Representação</t>
+          <t>Uma Pequena Vitória</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1부 9화 변형</t>
+          <t>1부 5화 변형</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>하파가 그 자료로 형사 고발장을 내고, 오타비우는 증인이 업체에서 돈을 받은 정황을 보고도 침묵한다. 새벽 세베리누가 체포된다.</t>
+          <t>수은을 채굴꾼 탓으로 돌린 감정서로 첫 판결을 이기고, 프라두가 치하하는 축하연에서 브랑당이 소개한 방산업체의 장갑차·탄약 수출 허가를 사흘 만에 받아 낸다.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -27065,27 +27065,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>1부 10화</t>
+          <t>1부 6화</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>덮인 보고서</t>
+          <t>봉인된 목록</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>O Laudo Enterrado</t>
+          <t>A Lista Sigilosa</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1부 10화 변형</t>
+          <t>1부 6화 변형</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>하파는 로펌 자료실에서 제련소 수은을 확인한 2013년 내부 보고서를 찾고, 구치소의 세베리누는 교도관의 커피를 그에게 먼저 민다.</t>
+          <t>같은 로비망을 타고 주 경찰에 팔린 센치넬라 아우스트랄의 감청 프로그램 ‘비지아’ 소송을 국가안보 기밀로 봉인해 이기지만, 표적 목록의 세베리누와 루시아 번호에 침묵한다.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -27093,27 +27093,27 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>1부 11화</t>
+          <t>1부 7화</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>석방의 날</t>
+          <t>숲의 현장검증</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>O Dia da Soltura</t>
+          <t>A Inspeção Judicial</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1부 11화 변형</t>
+          <t>1부 7화 변형</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>하파가 루시아와 손잡고 날조 증거와 끊긴 심장약을 판사에게 넘겨 석방이 결정되지만, 그날 세베리누가 숨진다.</t>
+          <t>합의서를 받으러 간 강마을에서 손 떨리는 아이들을 보고, 아루아칸 현장검증에서 모에마와 마주한 날 숲 지킴이 청년이 총에 맞는다.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
@@ -27121,167 +27121,167 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>1부 8화</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>건조독</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>A Doca Seca</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>1부 3화 변형</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>이타과레 조선소 마레 아우타의 건조독 폭발로 용접공 시세루가 숨지고 석 달 치 임금이 밀린 채 회생이 신청되자, 하파는 그의 ‘수칙 위반’을 계획의 전제로 적는다.</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>1부 9화</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>고발장</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>A Representação</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>1부 8·9화 변형</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>브랑당이 건넨 ‘증인 매수’ 자료로 하파가 세베리누를 고발하고, 오타비우는 증인이 돈을 받은 정황을 보고도 침묵한다. 새벽 세베리누가 체포된다.</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>덮인 보고서</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>O Laudo Enterrado</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>플랫폼 리베이트로 조선소를 비운 ‘자문회사’ 채권은 살리고 임금은 깎은 회생안이 통과된 주, 하파는 2013년 수은 보고서를 찾고 구치소의 세베리누는 커피를 먼저 민다.</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>석방의 날</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>O Dia da Soltura</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>하파가 루시아와 손잡고 날조 증거가 ‘비지아’ 감청에서 나왔다는 사실과 끊긴 심장약을 판사에게 넘겨 석방이 결정되지만, 그날 세베리누가 숨진다.</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
           <t>1부 12화</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>사직서</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>A Demissão</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>1부 12화 변형</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>강마을과 아루아칸 사람들로 가득한 장례식에서 하파는 무심코 조문객에게 커피를 내고, 사직서를 낸다. 아버지와 오타비우가 말린다.</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>공설변호인 시험</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>O Concurso</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>반년 동안 부모 집에서 공부한 하파가 공설변호인 시험에 붙고, 로펌 동료들의 비웃음 속에 노바 카라자이 부임을 고른다.</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>2부 2화</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>구금심사</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>Audiência de Custódia</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>하루 마흔 건의 구금심사, 빌라 히반세이라의 열아홉 살 제페르송이 파벌 ‘운반책’으로 멍든 채 서 있다.</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>2부 3화</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>운반책이 아닌 소년</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>O Menino Que Não Era Mula</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>똑같은 문장이 반복된 경찰 조서를 파고든 하파가 제의 무죄를 받아 내지만, 다른 서른 건은 이기지 못한다.</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>2부 4화</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>루시아의 강</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>O Rio de Lúcia</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>2부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>이제 편이 된 루시아가 이르만다지 두 노르치의 코카인 배가 불법 금 준설선과 같은 강길을 쓰는 것을 추적한다.</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>장례식에서 무심코 조문객에게 커피를 낸 하파가 네 고객의 이름을 적은 사직서를 레오노르에게 내고, 아버지와 오타비우가 말린다.</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2부 5화</t>
+          <t>2부 1화</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>강 위의 비행장</t>
+          <t>공설변호인 시험</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>As Pistas Clandestinas</t>
+          <t>O Concurso</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>2부 1화 변형</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>코카인과 금을 함께 싣는 숲속 불법 비행장 마흔 곳을 좌표로 기록하고, 협조한 원주민 보호청 직원이 협박받는다.</t>
+          <t>반년 동안 부모 집에서 공부한 하파가 공설변호인 시험에 붙고, 로펌 동료들의 비웃음 속에 노바 카라자이 부임을 고른다.</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr"/>
@@ -27289,27 +27289,27 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>2부 2화</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>공익소송</t>
+          <t>구금심사</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>A Ação Civil Pública</t>
+          <t>Audiência de Custódia</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>2부 5화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>하파가 수은 강마을을 위한 공익소송을 내고, 파트너로 승진한 오타비우가 프라두 측 대리인으로 맞은편에 앉는다.</t>
+          <t>하루 마흔 건의 구금심사, 빌라 히반세이라의 열아홉 살 제페르송이 파벌 ‘운반책’으로 멍든 채 서 있다.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr"/>
@@ -27317,27 +27317,27 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2부 7화</t>
+          <t>2부 3화</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>헤지 클라레이라</t>
+          <t>운반책이 아닌 소년</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>A Rede Clareira</t>
+          <t>O Menino Que Não Era Mula</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>2부 1·2화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>모에마·루시아·파벨라 어머니들과 인권 네트워크를 세우고, 인턴 비아가 거액 후원 재단의 돈이 프라두의 것임을 밝힌다.</t>
+          <t>똑같은 문장이 반복된 경찰 조서를 파고든 하파가 제의 무죄를 받아 내지만, 다른 서른 건은 이기지 못한다.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -27345,27 +27345,27 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2부 8화</t>
+          <t>2부 4화</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>기준일</t>
+          <t>루시아의 강</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>O Marco</t>
+          <t>O Rio de Lúcia</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>2부 4화 변형</t>
+          <t>2부 3화 변형</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>원주민 영토 ‘기준일’ 법안과 일괄 허가 법안이 오르고, 모에마가 상원에서 증언하며 원주민들이 수도로 행진한다.</t>
+          <t>이제 편이 된 루시아가 이르만다지 두 노르치의 코카인 배가 불법 금 준설선과 같은 강길을 쓰는 것을 추적한다.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -27373,27 +27373,27 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2부 9화</t>
+          <t>2부 5화</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>모에마의 구금</t>
+          <t>강 위의 비행장</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>A Prisão de Moema</t>
+          <t>As Pistas Clandestinas</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>광산 트럭을 막으려 연방도로를 봉쇄한 모에마가 ‘범죄 결사’로 구속되고, 청장의 신중론을 넘어 하파가 변호를 맡는다.</t>
+          <t>코카인과 금을 함께 싣는 숲속 불법 비행장 마흔 곳을 좌표로 기록하고, 협조한 원주민 보호청 직원이 협박받는다.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -27401,27 +27401,27 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2부 10화</t>
+          <t>2부 6화</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 제안</t>
+          <t>공익소송</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>A Proposta de Brandão</t>
+          <t>A Ação Civil Pública</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>2부 7·8화 변형</t>
+          <t>2부 5화 변형</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>브랑당이 ‘공익소송을 내리면 모에마는 풀려난다’는 거래를 내밀고, 아버지가 정비소에서 해고되며 동료들이 떠난다.</t>
+          <t>하파가 수은 강마을을 위한 공익소송을 내고, 파트너로 승진해 프라두와 하파의 옛 고객 셋을 물려받은 오타비우가 프라두 측 대리인으로 맞은편에 앉는다.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -27429,27 +27429,27 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2부 11화</t>
+          <t>2부 7화</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>오타비우의 배신 발각</t>
+          <t>헤지 클라레이라</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>A Traição Descoberta</t>
+          <t>A Rede Clareira</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>2부 10화 변형</t>
+          <t>2부 1·2화 변형</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>공익소송 감정 증인 명단이 새어 나가 증인 가족이 협박받고, 비아의 추적 끝에 오타비우가 드러난다.</t>
+          <t>모에마·루시아·파벨라 어머니들과 인권 네트워크를 세우고, 인턴 비아가 거액 후원 재단의 돈이 프라두의 것임을 밝힌다.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -27457,167 +27457,167 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
+          <t>2부 8화</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>O Marco</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>2부 4화 변형</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>원주민 영토 ‘기준일’ 법안과 일괄 허가 법안이 오르고, 모에마가 상원에서 증언하며 원주민들이 수도로 행진한다.</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>2부 9화</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>모에마의 구금</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>A Prisão de Moema</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>2부 6화</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>광산 트럭을 막으려 연방도로를 봉쇄한 모에마가 ‘범죄 결사’로 구속되고, 청장의 신중론을 넘어 하파가 변호를 맡는다.</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>2부 10화</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>브랑당의 제안</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>A Proposta de Brandão</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>2부 7·8화 변형</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>브랑당이 ‘공익소송을 내리면 모에마는 풀려난다’는 거래를 내밀고, 아버지가 정비소에서 해고되며 동료들이 떠난다.</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>2부 11화</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>오타비우의 배신 발각</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>A Traição Descoberta</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>2부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>공익소송 감정 증인 명단이 새어 나가 증인 가족이 협박받고, 비아의 추적 끝에 오타비우가 드러난다.</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
           <t>2부 12화</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>모에마의 재판</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>O Julgamento de Moema</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>2부 11·12화 변형</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>통역도 없는 재판에서 하파의 변론에도 모에마에게 징역 4년이 선고되고, ‘모에마에게 자유를’ 운동이 전국으로 번진다.</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>사퇴</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>A Desincompatibilização</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>출마하려면 선거 여섯 달 전 공직을 떠나야 한다. 하파가 공설변호인직 사퇴서를 쓰고, 아버지는 ‘또 안정을 버리냐’며 반대한다.</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>3부 2화</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>정당 창당</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>A Fundação do Partido</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>안셀무가 2년간 서명을 모아 등록시킨 땅과노동당(PTT)에 하파가 입당하고, 창당대회에서 주지사 후보로 추대된다.</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>3부 3화</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>오타비우의 귀환</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>A Volta de Otávio</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>3부 2화</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>임신한 아내 앞에서 흔들린 오타비우가 로펌의 프라두 내부 자료를 들고 하파를 찾아온다.</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>3부 4화</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>들어갈 수 없는 동네</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Onde Não Se Pode Entrar</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>3부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할지 정하고, 제가 유세단의 길을 협상하며 농업 로비 방송들이 공세를 시작한다.</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3부 5화</t>
+          <t>3부 1화</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>아버지의 죽음</t>
+          <t>사퇴</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>A Morte do Pai</t>
+          <t>A Desincompatibilização</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3부 4화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>‘아들이 자랑스럽다’는 유세 영상으로 화제가 된 아버지 니바우두가 새벽길 뺑소니로 숨진다.</t>
+          <t>출마하려면 선거 여섯 달 전 공직을 떠나야 한다. 하파가 공설변호인직 사퇴서를 쓰고, 아버지는 ‘또 안정을 버리냐’며 반대한다.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
@@ -27625,27 +27625,27 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3부 6화</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>루시아의 폭로전</t>
+          <t>정당 창당</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>A Denúncia de Lúcia</t>
+          <t>A Fundação do Partido</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>3부 5화</t>
+          <t>3부 1화 변형</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>루시아가 주정부·프라두 그룹·민병대·파벌 비행장을 잇는 ‘토지 세탁’ 구조의 최종 기사를 준비한다.</t>
+          <t>안셀무가 2년간 서명을 모아 등록시킨 땅과노동당(PTT)에 하파가 입당하고, 창당대회에서 주지사 후보로 추대된다.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr"/>
@@ -27653,27 +27653,27 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 3화</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>선거 조작 저지</t>
+          <t>오타비우의 귀환</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Contra o Curral Eleitoral</t>
+          <t>A Volta de Otávio</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3부 6화</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>민병대가 투표소 길목을 막고 표를 사는 ‘선거 목장’을 파벨라 주민 참관인단이 영상 기록으로 막아선다.</t>
+          <t>임신한 아내 앞에서 흔들린 오타비우가 프라두와 옛 고객들의 로펌 내부 자료를 들고 하파를 찾아온다.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
@@ -27681,27 +27681,27 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>루시아의 실종</t>
+          <t>들어갈 수 없는 동네</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>O Desaparecimento de Lúcia</t>
+          <t>Onde Não Se Pode Entrar</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 3화 변형</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>폭로 기사가 공개되어 전국이 들끓은 날 밤, 루시아가 강변 도로에서 흔적 없이 사라진다.</t>
+          <t>파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할지 정하고, 제가 유세단의 길을 협상하며 농업 로비 방송들이 공세를 시작한다.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr"/>
@@ -27709,27 +27709,27 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>거리로 나선 사람들</t>
+          <t>아버지의 죽음</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>O Povo nas Ruas</t>
+          <t>A Morte do Pai</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>루시아의 사진을 든 자발적 시위가 투표 이틀 전 전국 열두 개 도시로 번진다.</t>
+          <t>‘아들이 자랑스럽다’는 유세 영상으로 화제가 된 아버지 니바우두가 새벽길 뺑소니로 숨진다.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
@@ -27737,27 +27737,27 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>3부 10화</t>
+          <t>3부 6화</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>오타비우의 희생</t>
+          <t>루시아의 폭로전</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>O Sacrifício de Otávio</t>
+          <t>A Denúncia de Lúcia</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>투표 전날 밤, 선거본부 압수수색 직전 루시아의 취재원 자료를 빼돌린 오타비우가 대신 체포된다.</t>
+          <t>루시아가 주정부·프라두 그룹·민병대·파벌 비행장을 잇는 ‘토지 세탁’ 구조의 최종 기사를 준비한다.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr"/>
@@ -27765,27 +27765,27 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>3부 11화</t>
+          <t>3부 7화</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>당선, 그러나</t>
+          <t>선거 조작 저지</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Vitória, Mas…</t>
+          <t>Contra o Curral Eleitoral</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>3부 10·11화 압축</t>
+          <t>3부 6화</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>투표일 밤 브랑당의 담판에 아무것도 약속하지 않은 하파가 당선되지만, 인수 방해와 연방의 재정 압박이 기다린다.</t>
+          <t>민병대가 투표소 길목을 막고 표를 사는 ‘선거 목장’을 파벨라 주민 참관인단이 영상 기록으로 막아선다.</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr"/>
@@ -27793,167 +27793,167 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
+          <t>3부 8화</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>루시아의 실종</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>O Desaparecimento de Lúcia</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>3부 7화</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>폭로 기사가 공개되어 전국이 들끓은 날 밤, 루시아가 강변 도로에서 흔적 없이 사라진다.</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>3부 9화</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>거리로 나선 사람들</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>O Povo nas Ruas</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>3부 8화</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>루시아의 사진을 든 자발적 시위가 투표 이틀 전 전국 열두 개 도시로 번진다.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>3부 10화</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>오타비우의 희생</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>O Sacrifício de Otávio</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>3부 9화</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>투표 전날 밤, 선거본부 압수수색 직전 루시아의 취재원 자료를 빼돌린 오타비우가 대신 체포된다.</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>3부 11화</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>당선, 그러나</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Vitória, Mas…</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>3부 10·11화 압축</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>투표일 밤 브랑당의 담판에 아무것도 약속하지 않은 하파가 당선되지만, 인수 방해와 연방의 재정 압박이 기다린다.</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>전국 무대로</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Rumo ao Palco Nacional</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>1년 반 뒤 투명 예산의 타피라주가 모범이 되고, 대선 후보가 된 하파는 부솔라의 질다와 파벨라 출신 카이우를 만난다.</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>나라의 균열</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>O País Rachado</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>물가 폭등과 가뭄, 원주민 영토 침탈이 겹친 위기 속에 경제 자문을 영입한 대선 캠프가 출범한다.</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>4부 2화</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>모에마의 옥중 투쟁</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>A Luta de Moema na Prisão</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>4부 2화</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>프라두 그룹이 아루아칸 영토 채굴을 재개하자 수감 중인 모에마가 옥중 단식을 시작한다.</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>4부 3화</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>루아나의 등장</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>A Chegada de Luana</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>4부 3화</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>단식 아흐레째, 스물두 살 법대생 루아나 마르키스가 캠프 자원활동가로 합류한다.</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>4부 4화</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>프라두의 배신적 지지</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>O Apoio Traiçoeiro de Prado</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>4부 4화</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>프라두가 은밀히 지지를 제안하고, 하파는 원주민 영토 철수와 노동자 보상을 공개 조건으로 건다.</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>1년 반 뒤, 형기를 마친 파비아누의 증언으로 모라이스 레아우의 부풀린 주 도로 계약을 해지한 타피라주가 투명 예산의 모범이 되고, 대선 후보가 된 하파는 질다와 카이우를 만난다.</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>4부 5화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>모에마의 옥중 사망</t>
+          <t>나라의 균열</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>A Morte de Moema</t>
+          <t>O País Rachado</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>4부 5화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>법원이 병원 이송을 승인했지만 ‘호송 절차’로 지연되는 사이, 단식 14일째 모에마가 숨진다.</t>
+          <t>물가 폭등과 가뭄, 원주민 영토 침탈이 겹친 위기 속에 경제 자문을 영입한 대선 캠프가 출범한다.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -27961,27 +27961,27 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>거리의 혁명</t>
+          <t>모에마의 옥중 투쟁</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>A Revolução nas Ruas</t>
+          <t>A Luta de Moema na Prisão</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>원주민 행진과 트럭·교원 파업이 47개 도시로 번지고, 한 주 군경 장교가 진압 명령을 거부한다.</t>
+          <t>프라두 그룹이 아루아칸 영토 채굴을 재개하자 수감 중인 모에마가 옥중 단식을 시작한다.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -27989,27 +27989,27 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 선택</t>
+          <t>루아나의 등장</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>A Escolha de Brandão</t>
+          <t>A Chegada de Luana</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>대통령궁 긴급회의에서 강경파가 ‘방위 상태’ 선포를 밀어붙이자 브랑당이 협상을 택한다.</t>
+          <t>단식 아흐레째, 스물두 살 법대생 루아나 마르키스가 캠프 자원활동가로 합류한다.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -28017,27 +28017,27 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>암살 시도</t>
+          <t>프라두의 배신적 지지</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>O Atentado</t>
+          <t>O Apoio Traiçoeiro de Prado</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>농업 로비의 아성 도시에서 유세를 강행한 하파를 겨눈 저격이 벌어지고, 저격범이 사살된다.</t>
+          <t>프라두가 은밀히 지지를 제안하고, 하파는 원주민 영토 철수와 노동자 보상을 공개 조건으로 건다.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -28045,27 +28045,27 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>구체제의 붕괴</t>
+          <t>모에마의 옥중 사망</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>A Queda do Velho Regime</t>
+          <t>A Morte de Moema</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>부솔라가 찾은 자금 흐름이 대통령 비서실장과 암살 배후에 닿고, 대통령이 사임한다.</t>
+          <t>법원이 병원 이송을 승인했지만 ‘호송 절차’로 지연되는 사이, 단식 14일째 모에마가 숨진다.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -28073,27 +28073,27 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 6화</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>선거전 최종전</t>
+          <t>거리의 혁명</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>A Batalha Final</t>
+          <t>A Revolução nas Ruas</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 6화</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>부통령 권한대행 아래 치러지는 대선, 마지막 TV 토론과 단체방 가짜뉴스의 공방이 벌어진다.</t>
+          <t>원주민 행진과 트럭·교원 파업에 다미아나가 이끄는 조선소 미지급 노동자들이 합류해 47개 도시로 번지고, 한 주 군경 장교가 진압 명령을 거부한다.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -28101,27 +28101,27 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 7화</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>당선의 밤</t>
+          <t>브랑당의 선택</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>A Noite da Vitória</t>
+          <t>A Escolha de Brandão</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 7화</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>결선 개표가 밤새 이어지고, 새벽 무렵 하파의 승리가 확정되자 비아와 안셀무가 말없이 커피를 따른다.</t>
+          <t>대통령궁 긴급회의에서 강경파가 ‘방위 상태’ 선포를 밀어붙이자 브랑당이 협상을 택한다.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -28129,167 +28129,167 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
+          <t>4부 8화</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>암살 시도</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>O Atentado</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>4부 8화</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>농업 로비의 아성 도시에서 유세를 강행한 하파를 겨눈 저격이 벌어지고, 저격범이 사살된다.</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>4부 9화</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>구체제의 붕괴</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>A Queda do Velho Regime</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>4부 9화</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>부솔라가 찾은 자금 흐름이 대통령 비서실장과 암살 배후에 닿고, 대통령이 사임한다.</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>4부 10화</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>선거전 최종전</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>A Batalha Final</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>4부 10화</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>부통령 권한대행 아래 치러지는 대선, 마지막 TV 토론과 단체방 가짜뉴스의 공방이 벌어진다.</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>당선의 밤</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>A Noite da Vitória</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>결선 개표가 밤새 이어지고, 새벽 무렵 하파의 승리가 확정되자 비아와 안셀무가 말없이 커피를 따른다.</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B108" s="9" t="inlineStr">
         <is>
           <t>취임 전야</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>A Véspera da Posse</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="D108" s="9" t="inlineStr">
         <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="E108" s="9" t="inlineStr">
         <is>
           <t>취임 준비 대신 하파는 세베리누와 아버지, 모에마의 무덤을 차례로 찾아간다.</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>취임과 첫 벽</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>A Posse e o Primeiro Muro</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>재무부가 예비비 자료를 감추자 하파는 부솔라 팀에 신설 재정투명성청을 맡기고, 공설변호인청 예산 자율 개헌안을 첫 법안으로 보낸다.</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>브랑당과의 재계약</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>Um Novo Acordo com Brandão</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>감사가 ANSI의 비밀 운영비로 이어지고, 하파는 브랑당과 조건부 공조를 맺는다.</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>5부 3화</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>프라두의 마지막 카드</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>A Última Carta de Prado</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>5부 3화</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>실소유자 공개·토지 등기 정비 법안이 프라두 제국을 겨누고, 의회 농업 로비가 반격한다.</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>5부 4화</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>지방의 반란</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>A Rebelião de Serra Parima</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>5부 4화 확장</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>희토류 산지 세하 파리마주 주지사가 법 적용을 거부하고 군경 파업을 부추기자 부지사 마릴리아가 자료를 넘긴다.</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr"/>
+      <c r="F108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>파업의 끝</t>
+          <t>취임과 첫 벽</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>O Fim da Greve</t>
+          <t>A Posse e o Primeiro Muro</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>5부 4화 확장</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>연방 개입 대신 군경 가족들과의 협상으로 파업이 풀리고, 반란 주지사는 법정에 선다.</t>
+          <t>재무부가 예비비 자료를 감추자 하파는 부솔라 팀에 신설 재정투명성청을 맡기고, 공설변호인청 예산 자율 개헌안을 첫 법안으로 보낸다.</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr"/>
@@ -28297,27 +28297,27 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>5부 6화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>개혁의 대가</t>
+          <t>브랑당과의 재계약</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>O Preço da Reforma</t>
+          <t>Um Novo Acordo com Brandão</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>판·검사 부패망 조사에 자원한 오타비우가 하파와 옛 우정을 되찾은 직후 청부 총격에 숨진다.</t>
+          <t>감사가 ANSI의 비밀 운영비로 이어지고, 하파는 브랑당과 조건부 공조를 맺는다.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
@@ -28325,27 +28325,27 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>5부 7화</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>국제적 고립과 압박</t>
+          <t>프라두의 마지막 카드</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Isolamento e Pressão</t>
+          <t>A Última Carta de Prado</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>5부 6화</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>무역협정 중단과 자본 유출, 헤알화 급락이 몰아치는 가운데 국방장관이 사임한다.</t>
+          <t>실소유자 공개·토지 등기 정비 법안이 프라두 제국을 겨누고, 공청회에서 다미아나가 체불 임금 뒤에 숨은 조선소 유령회사를 증언하자 의회 농업 로비가 반격한다.</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
@@ -28353,27 +28353,27 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 4화</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>프라두의 최종 제거</t>
+          <t>지방의 반란</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>O Fim de Prado</t>
+          <t>A Rebelião de Serra Parima</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 4화 확장</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>조세 피난처의 마지막 은닉 구조가 드러나고, 프라두가 출국 직전 공항에서 체포된다.</t>
+          <t>희토류 산지 세하 파리마주 주지사가 법 적용을 거부하고 군경 파업을 부추기자 부지사 마릴리아가 자료를 넘긴다.</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
@@ -28381,27 +28381,27 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>브랑당의 최후</t>
+          <t>파업의 끝</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>O Fim de Brandão</t>
+          <t>O Fim da Greve</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 4화 확장</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>오타비우 청부금의 송금 사슬이 루시아 실종일과 겹치고 유해가 발견된다. 브랑당은 사임한다.</t>
+          <t>연방 개입 대신 군경 가족들과의 협상으로 파업이 풀리고, 반란 주지사는 법정에 선다.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
@@ -28409,27 +28409,27 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 6화</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>대의의 완성</t>
+          <t>개혁의 대가</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>A Obra Concluída</t>
+          <t>O Preço da Reforma</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>사법개혁·GLO 의회 승인·공설변호인청 예산 자율을 묶은 개헌안이 통과된다. 자기 정부를 묶는 조항은 하파 자신이 요구했다.</t>
+          <t>판·검사 부패망 조사에 자원한 오타비우가 하파와 옛 우정을 되찾은 직후 청부 총격에 숨진다.</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
@@ -28437,27 +28437,27 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>5부 7화</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>파벨라의 새벽</t>
+          <t>국제적 고립과 압박</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>A Madrugada no Morro</t>
+          <t>Isolamento e Pressão</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 6화</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>남동부 한 주 경찰의 파벨라 소탕 작전으로 수십 명이 죽고, 연방 법의학 조사를 보낸 하파와 주지사가 권한을 두고 충돌한다.</t>
+          <t>무역협정 중단과 자본 유출, 헤알화 급락이 몰아치는 가운데 국방장관이 사임한다.</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr"/>
@@ -28465,167 +28465,167 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
+          <t>5부 8화</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>프라두의 최종 제거</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>O Fim de Prado</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>5부 8화</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>조세 피난처의 마지막 은닉 구조가 드러나고, 프라두가 출국 직전 공항에서 체포된다.</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>5부 9화</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>브랑당의 최후</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>O Fim de Brandão</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>5부 9화</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>오타비우 청부금의 송금 사슬이 루시아 실종일과 겹치고 유해가 발견된다. 브랑당은 사임한다.</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>대의의 완성</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>A Obra Concluída</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>사법개혁·GLO 의회 승인·공설변호인청 예산 자율을 묶은 개헌안이 통과된다. 자기 정부를 묶는 조항은 하파 자신이 요구했다.</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>파벨라의 새벽</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>A Madrugada no Morro</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>남동부 한 주 경찰의 파벨라 소탕 작전으로 수십 명이 죽고, 연방 법의학 조사를 보낸 하파와 주지사가 권한을 두고 충돌한다.</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>경고등</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>O Sinal de Alerta</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>새 정보청장 구르겔이 예비역 장교·민병대·불복 단체방을 잇는 보고서를 올리지만, 증거는 아직 흐릿하다.</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>6부 1화</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>민병대의 도시</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>A Cidade da Milícia</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>수도권 위성도시 파벨라에서 파벌과 민병대가 가스·인터넷·통근 밴을 두고 다투고, 하파는 도나 테레자의 라디오 방송을 직접 듣는다.</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>6부 2화</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>테레자의 라디오</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>A Rádio de Dona Tereza</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>파벌과 민병대 양쪽의 ‘보호’를 거부하고 민병대 비리를 방송하던 도나 테레자가 출근길에 총격으로 숨진다.</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>6부 3화</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>민병대와 의원들</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>Milícia e Mandato</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>테레자 살해 수사가 민병대 두목과 주 의원, 불복 운동 자금책을 잇는 선을 드러낸다.</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>6부 4화</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>병영 앞 천막</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>O Acampamento</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>5부 7화 확장</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>대선 불복 시민들이 병영 앞에 천막을 치고 군의 개입을 요구하며, 예비역 장교 단체방이 들끓는다.</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>6부 5화</t>
+          <t>6부 1화</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>군 내부의 균열</t>
+          <t>민병대의 도시</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>A Fissura nos Quartéis</t>
+          <t>A Cidade da Milícia</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>5부 7화 확장</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>한 대령이 쿠데타 계획 문건을 들고 구르겔을 찾아오고, 합참의장은 침묵을 택한다.</t>
+          <t>수도권 위성도시 파벨라에서 파벌과 민병대가 가스·인터넷·통근 밴을 두고 다투고, 하파는 도나 테레자의 라디오 방송을 직접 듣는다.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -28633,27 +28633,27 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>6부 6화</t>
+          <t>6부 2화</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>점거 전야</t>
+          <t>테레자의 라디오</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>A Véspera</t>
+          <t>A Rádio de Dona Tereza</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>5부 7화 확장</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>수백 대의 버스가 수도로 향하고, 수도 경비 책임자가 방어선을 절반으로 줄인 사실이 드러난다.</t>
+          <t>파벌과 민병대 양쪽의 ‘보호’를 거부하고 민병대 비리를 방송하던 도나 테레자가 출근길에 총격으로 숨진다.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -28661,27 +28661,27 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>6부 7화</t>
+          <t>6부 3화</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>삼권의 밤</t>
+          <t>민병대와 의원들</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>A Noite dos Três Poderes</t>
+          <t>Milícia e Mandato</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>5부 7화 확장</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>불복 군중이 의회·대법원·대통령궁을 점거해 부수고, 하파는 ‘방위 상태’ 선포 요구를 받는다.</t>
+          <t>테레자 살해 수사가 민병대 두목과 주 의원, 불복 운동 자금책을 잇는 선을 드러낸다.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -28689,17 +28689,17 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>6부 8화</t>
+          <t>6부 4화</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>새벽의 몇 시간</t>
+          <t>병영 앞 천막</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>As Horas da Madrugada</t>
+          <t>O Acampamento</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
@@ -28709,7 +28709,7 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>명령을 거부한 장교와 대법원장, 루아나가 버티는 사이 하파는 헌법 절차만으로 청사를 되찾는다.</t>
+          <t>대선 불복 시민들이 병영 앞에 천막을 치고 군의 개입을 요구하며, 예비역 장교 단체방이 들끓는다.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -28717,27 +28717,27 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>6부 9화</t>
+          <t>6부 5화</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>사면은 없다</t>
+          <t>군 내부의 균열</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Sem Anistia</t>
+          <t>A Fissura nos Quartéis</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 7화 확장</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>사면 법안과 보복 입법을 모두 물리치자, 외국 정부가 재판을 ‘마녀사냥’이라 부르며 관세와 대법관 제재로 압박한다.</t>
+          <t>한 대령이 쿠데타 계획 문건을 들고 구르겔을 찾아오고, 합참의장은 침묵을 택한다.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -28745,27 +28745,27 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>6부 10화</t>
+          <t>6부 6화</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>돈의 지도</t>
+          <t>점거 전야</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>O Mapa do Dinheiro</t>
+          <t>A Véspera</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 7화 확장</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>테레자 살해와 점거 자금이 이르만다지 두 노르치의 주유소 체인과 무허가 핀테크로 세탁돼 옛 정보기관의 ‘지갑’에 닿은 흔적을 벤자밍이 찾는다.</t>
+          <t>모라이스 레아우 자회사가 대금을 댄 버스 수백 대가 수도로 향하고, 수도 경비 책임자가 방어선을 절반으로 줄인 사실이 드러난다.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -28773,27 +28773,27 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>6부 11화</t>
+          <t>6부 7화</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>개혁의 피로</t>
+          <t>삼권의 밤</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>O Cansaço das Reformas</t>
+          <t>A Noite dos Três Poderes</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>5부 7화 확장</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>연금 수급자 부정 공제 파문, 불법 채굴 단속으로 일자리를 잃은 금광촌, 끝없는 재판 뉴스 속에 지지율이 떨어진다.</t>
+          <t>불복 군중이 의회·대법원·대통령궁을 점거해 부수고, 하파는 ‘방위 상태’ 선포 요구를 받는다.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -28801,167 +28801,167 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
+          <t>6부 8화</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>새벽의 몇 시간</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>As Horas da Madrugada</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>5부 7화 확장</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>명령을 거부한 장교와 대법원장, 루아나가 버티는 사이 하파는 헌법 절차만으로 청사를 되찾는다.</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>6부 9화</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>사면은 없다</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Sem Anistia</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>사면 법안과 보복 입법을 모두 물리치자, 외국 정부가 재판을 ‘마녀사냥’이라 부르며 관세와 대법관 제재로 압박한다.</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>6부 10화</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>돈의 지도</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>O Mapa do Dinheiro</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>테레자 살해와 점거 자금이 이르만다지 두 노르치의 주유소 체인과 무허가 핀테크로 세탁돼 옛 정보기관의 ‘지갑’에 닿은 흔적을 벤자밍이 찾는다.</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>6부 11화</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>개혁의 피로</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>O Cansaço das Reformas</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>연금 수급자 부정 공제 파문, 불법 채굴 단속으로 일자리를 잃은 금광촌, 끝없는 재판 뉴스 속에 지지율이 떨어진다.</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
           <t>6부 12화</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="B132" s="9" t="inlineStr">
         <is>
           <t>재선의 기로</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C132" s="9" t="inlineStr">
         <is>
           <t>Na Encruzilhada</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>재선을 반년 앞두고 지지율이 45%로 떨어지고, 군경 사령관 출신 방송인 단타스가 부상한다.</t>
         </is>
       </c>
-      <c r="F128" s="9" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>7부 1화</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>거짓의 기계</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>A Máquina de Mentiras</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>6부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>단타스의 치안 공세와 딥페이크, 돈 받은 가짜 증인이 몰아치고 루아나가 처음 단독 유세에 나선다.</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>7부 2화</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>유세장 테러</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>O Atentado no Comício</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>6부 6화</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>레시피의 1만 5천 명 유세장에서 폭탄이 터져 질다가 숨지고, 루아나가 팔을 크게 다친다.</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>7부 3화</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>배후와 토론</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Os Mandantes e o Debate</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>6부 9화 변형</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>수사가 옛 정보기관 네트워크의 돈을 향하는 가운데, 하파는 마지막 토론에서 테러를 표로 바꾸지 않는다.</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>7부 4화</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>재선의 밤</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>A Noite da Reeleição</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>6부 12화 변형</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>여론조사가 끝까지 동률이던 박빙 결선에서 하파가 재선되고, 단타스는 패배를 인정해 제도권 야당의 길을 연다.</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="F132" s="9" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>7부 5화</t>
+          <t>7부 1화</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>복합위기의 발생</t>
+          <t>거짓의 기계</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>A Crise Múltipla</t>
+          <t>A Máquina de Mentiras</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>7부 2화 변형</t>
+          <t>6부 3화 변형</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고, 원자재 가격 폭락이 한꺼번에 덮친다.</t>
+          <t>단타스의 치안 공세와 딥페이크, 돈 받은 가짜 증인이 몰아치고 루아나가 처음 단독 유세에 나선다.</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
@@ -28969,27 +28969,27 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>7부 2화</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>비상대권의 유혹</t>
+          <t>유세장 테러</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>A Tentação da Exceção</t>
+          <t>O Atentado no Comício</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>7부 3화</t>
+          <t>6부 6화</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>하벨루 국방장관이 파벨라 무기한 GLO와 작전 중 살상 군인 면책 조항을 담은 법안을 들고 온다.</t>
+          <t>레시피의 1만 5천 명 유세장에서 폭탄이 터져 질다가 숨지고, 루아나가 팔을 크게 다친다.</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -28997,27 +28997,27 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>연기와 재갈</t>
+          <t>배후와 토론</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Adiar e Calar</t>
+          <t>Os Mandantes e o Debate</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>7부 4화 변형</t>
+          <t>6부 9화 변형</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>보궐선거 연기안과 플랫폼 전면 차단안이 오른 날, 대법원은 플랫폼이 불법 게시물에 직접 책임진다고 판결한다.</t>
+          <t>수사가 옛 정보기관 네트워크의 돈을 향하는 가운데, 하파는 마지막 토론에서 테러를 표로 바꾸지 않는다.</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
@@ -29025,27 +29025,27 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 4화</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>컨설턴트 팀에게 부탁</t>
+          <t>재선의 밤</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Um Pedido à Bússola</t>
+          <t>A Noite da Reeleição</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>6부 12화 변형</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>군 장비 조달 비리 보고서를 미뤄 달라는 하파의 부탁을 카이우가 거절한다.</t>
+          <t>여론조사가 끝까지 동률이던 박빙 결선에서 하파가 재선되고, 단타스는 패배를 인정해 제도권 야당의 길을 연다.</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
@@ -29053,27 +29053,27 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>7부 9화</t>
+          <t>7부 5화</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>작은 월권</t>
+          <t>복합위기의 발생</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Um Pequeno Excesso</t>
+          <t>A Crise Múltipla</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 2화 변형</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>하파가 영장 없는 감청 한 건을 구두로 허락하고, 그 사실이 청문회에서 드러난다.</t>
+          <t>이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고, 원자재 가격 폭락이 한꺼번에 덮친다.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
@@ -29081,27 +29081,27 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>7부 10화</t>
+          <t>7부 6화</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>루아나의 정면 대결</t>
+          <t>비상대권의 유혹</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>O Confronto de Luana</t>
+          <t>A Tentação da Exceção</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>하벨루가 비상 치안 체계의 상설화를 밀자 루아나와 비아가 공개적으로 대통령에게 맞선다.</t>
+          <t>하벨루 국방장관이 센치넬라 아우스트랄의 로비를 등에 업고 파벨라 무기한 GLO와 살상 군인 면책, 감청 시스템 도입을 담은 법안을 들고 온다.</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr"/>
@@ -29109,27 +29109,27 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>7부 11화</t>
+          <t>7부 7화</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>벼랑 끝의 포기</t>
+          <t>연기와 재갈</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>A Renúncia à Beira do Abismo</t>
+          <t>Adiar e Calar</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>7부 10화 변형</t>
+          <t>7부 4화 변형</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>세베리누의 고문실 기록을 읽은 새벽, 경찰서 습격으로 병사가 죽어도 하파는 백지 GLO를 거부한다.</t>
+          <t>보궐선거 연기안과 플랫폼 전면 차단안이 오른 날, 대법원은 플랫폼이 불법 게시물에 직접 책임진다고 판결한다.</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr"/>
@@ -29137,167 +29137,167 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
+          <t>7부 8화</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>컨설턴트 팀에게 부탁</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Um Pedido à Bússola</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>7부 6화</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>수출 장갑차가 외국 시위 진압에 쓰인 사실과 센치넬라 아우스트랄의 과다 계약을 밝힌 조달 비리 보고서를 미뤄 달라는 하파의 부탁을 카이우가 거절한다.</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>7부 9화</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>작은 월권</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Um Pequeno Excesso</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>7부 7화</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>하파가 한때 자신이 봉인해 준 ‘비지아’로 영장 없는 감청 한 건을 구두로 허락하고, 그 사실이 청문회에서 드러난다.</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>7부 10화</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>루아나의 정면 대결</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>O Confronto de Luana</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>7부 8화</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>하벨루가 비상 치안 체계의 상설화를 밀자 루아나와 비아가 공개적으로 대통령에게 맞선다.</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>7부 11화</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>벼랑 끝의 포기</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>A Renúncia à Beira do Abismo</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>7부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>세베리누의 고문실 기록을 읽은 새벽, 경찰서 습격으로 병사가 죽어도 하파는 백지 GLO를 거부한다.</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
           <t>7부 12화</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>새로운 균형</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>Um Novo Equilíbrio</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>7부 12화</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>인질이 풀려나고, 하파는 모든 군 투입을 의회 승인·기한·공설변호인 입회에 묶는 위기결정위원회 법으로 비상권한을 스스로 묶기로 한다.</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>권력의 한계</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>Os Limites do Poder</t>
-        </is>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="E141" s="9" t="inlineStr">
-        <is>
-          <t>위기결정위원회 법 통과 직후, 하파가 「권력의 한계」 법안 착수를 대국민 발표한다.</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t>8부 2화</t>
-        </is>
-      </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>팀의 재편</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>A Equipe Refeita</t>
-        </is>
-      </c>
-      <c r="D142" s="9" t="inlineStr">
-        <is>
-          <t>8부 2화</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>38명이 된 재정투명성청을 재편하다가, 질다의 카드 ‘커피를 잊지 말 것’이 처음 발견된다.</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>8부 3화</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>돌아온 병사들</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>Os Que Voltaram</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>8부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>18개월 파벨라 GLO가 끝나 군이 철수하고, 귀환 병사들의 트라우마와 주민들의 기억이 새 숙제가 된다.</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="9" t="inlineStr">
-        <is>
-          <t>8부 4화</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="inlineStr">
-        <is>
-          <t>세대교체</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="inlineStr">
-        <is>
-          <t>A Troca de Gerações</t>
-        </is>
-      </c>
-      <c r="D144" s="9" t="inlineStr">
-        <is>
-          <t>8부 4화</t>
-        </is>
-      </c>
-      <c r="E144" s="9" t="inlineStr">
-        <is>
-          <t>핵심 요직 12자리를 익명 공모로 뽑고, 강마을 출신 청년 알리니와 빌라 히반세이라의 제가 지원서를 낸다.</t>
-        </is>
-      </c>
-      <c r="F144" s="9" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 마지막 대화</t>
+          <t>권력의 한계</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>A Última Conversa com Brandão</t>
+          <t>Os Limites do Poder</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>병든 브랑당을 찾아가 감시 체계 해체와 군정 기록 공개, 루시아 사건 방조를 마지막으로 묻는다.</t>
+          <t>위기결정위원회 법 통과 직후, 하파가 「권력의 한계」 법안 착수를 대국민 발표한다.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr"/>
@@ -29305,27 +29305,27 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>8부 6화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>루아나에게 실권 위임</t>
+          <t>팀의 재편</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>O Poder nas Mãos de Luana</t>
+          <t>A Equipe Refeita</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>8부 6화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>노후 송전망 붕괴로 북부 주가 암흑에 빠지고, 하파는 루아나에게 실권을 넘긴다.</t>
+          <t>38명이 된 재정투명성청을 재편하다가, 질다의 카드 ‘커피를 잊지 말 것’이 처음 발견된다.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -29333,27 +29333,27 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>8부 3화</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>세하 파리마의 빚</t>
+          <t>돌아온 병사들</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>As Dívidas de Serra Parima</t>
+          <t>Os Que Voltaram</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>8부 3화 변형</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>숨은 보증채무가 드러난 세하 파리마주에서 마릴리아가 주지사로 당선돼 부채를 공개한다.</t>
+          <t>18개월 파벨라 GLO가 끝나 군이 철수하고, 귀환 병사들의 트라우마와 주민들의 기억이 새 숙제가 된다.</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
@@ -29361,27 +29361,27 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>마지막 정치적 결전</t>
+          <t>세대교체</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>O Último Combate</t>
+          <t>A Troca de Gerações</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>구체제 잔존 세력이 대법원·의회·방송·검찰에서 총공세를 펴고, 카이우가 옛 과오를 고백한 뒤 쓰러진다.</t>
+          <t>핵심 요직 12자리를 익명 공모로 뽑고, 강마을 출신 청년 알리니와 빌라 히반세이라의 제가 지원서를 낸다.</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr"/>
@@ -29389,27 +29389,27 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>법안의 최종 완성</t>
+          <t>브랑당의 마지막 대화</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>A Lei Concluída</t>
+          <t>A Última Conversa com Brandão</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>「권력의 한계」법이 서명되고, 두 번의 임기 뒤 평생 재출마 금지 조항을 하파가 스스로 넣는다.</t>
+          <t>병든 브랑당을 찾아가 ‘비지아’를 비롯한 감시 체계 해체와 군정 기록 공개, 루시아 사건 방조를 마지막으로 묻는다.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -29417,27 +29417,27 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>8부 6화</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>질다를 기리며</t>
+          <t>루아나에게 실권 위임</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>Em Memória de Zilda</t>
+          <t>O Poder nas Mãos de Luana</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>8부 6화</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>추모의 밤, 하파는 ‘커피를 잊지 말 것’이 세베리누의 원칙과 같았음을 깨닫는다.</t>
+          <t>노후 송전망 붕괴로 북부 주가 암흑에 빠지고, 하파는 루아나에게 실권을 넘긴다.</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr"/>
@@ -29445,27 +29445,27 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 7화</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>프라두 판결</t>
+          <t>세하 파리마의 빚</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>A Sentença de Prado</t>
+          <t>As Dívidas de Serra Parima</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 7화</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>프라두에게 유죄가 선고되고 해외 자산이 환수되며, NGO 낙인법 폐지 논의가 시작된다.</t>
+          <t>숨은 보증채무가 드러난 세하 파리마주에서 마릴리아가 주지사로 당선돼 부채를 공개한다.</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr"/>
@@ -29473,167 +29473,167 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
+          <t>8부 8화</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>마지막 정치적 결전</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>O Último Combate</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>8부 8화</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>구체제 잔존 세력이 대법원·의회·방송·검찰에서 총공세를 펴고, 카이우가 옛 과오를 고백한 뒤 쓰러진다.</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>8부 9화</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>법안의 최종 완성</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>A Lei Concluída</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>8부 9화</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>「권력의 한계」법이 서명되고, 두 번의 임기 뒤 평생 재출마 금지 조항을 하파가 스스로 넣는다.</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>8부 10화</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>질다를 기리며</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Em Memória de Zilda</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>8부 10화</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>추모의 밤, 하파는 ‘커피를 잊지 말 것’이 세베리누의 원칙과 같았음을 깨닫는다.</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>프라두 판결</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>A Sentença de Prado</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>프라두에게 유죄가 선고되고 해외 자산이 환수되며, NGO 낙인법 폐지 논의가 시작된다.</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
           <t>8부 12화</t>
         </is>
       </c>
-      <c r="B152" s="9" t="inlineStr">
+      <c r="B156" s="9" t="inlineStr">
         <is>
           <t>질다를 죽인 돈</t>
         </is>
       </c>
-      <c r="C152" s="9" t="inlineStr">
+      <c r="C156" s="9" t="inlineStr">
         <is>
           <t>O Dinheiro Que Matou Zilda</t>
         </is>
       </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>8부 12화</t>
         </is>
       </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>청산된 민간은행 장부와 파벌의 주유소·핀테크 세탁망에서 테러 자금이 오타실리우를 가리키지만, 그는 해외로 빠져나간다.</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>마지막 해</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>O Último Ano</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>임기 1년을 남기고 단타스가 야당 지도자로 돌아오며, ‘누가 다음인가’가 떠오른다.</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>불타는 숲</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>A Floresta em Chamas</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>강이 역대 최저 수위로 마르고 아루아칸 영토가 불타는데 국제 산림기금 약속은 절반에 그치자, 하파가 귀향한다.</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>9부 3화</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>낙인</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>O Estigma</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>9부 3화</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>외국 후원 NGO 등록·낙인법이 최종 폐지되고, 루아나가 첫 독자 정치 행보를 한다.</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>9부 4화</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>병사의 재판</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>O Julgamento do Soldado</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>9부 4화 변형</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>GLO 작전 중 파벨라 소년을 쏜 귀환 병사가 일반 법원에 서고, 하파는 공설변호인의 눈으로 방청한다.</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>민간은행 장부와 파벌의 주유소·핀테크 세탁망, 레오노르가 넘긴 마레 아우타의 옛 플랫폼 리베이트 계좌가 테러 자금의 주인으로 오타실리우를 가리키지만, 그는 해외로 빠져나간다.</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>9부 5화</t>
+          <t>9부 1화</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>루아나, 공식 후계자로</t>
+          <t>마지막 해</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Luana, a Sucessora</t>
+          <t>O Último Ano</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>9부 5화</t>
+          <t>9부 1화</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>하파가 미뤄 둔 대화를 꺼내고, 당 예비경선에서 루아나가 공식 대선 후보로 선출된다.</t>
+          <t>임기 1년을 남기고 단타스가 야당 지도자로 돌아오며, ‘누가 다음인가’가 떠오른다.</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr"/>
@@ -29641,27 +29641,27 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>9부 6화</t>
+          <t>9부 2화</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>개인적 화해와 정리</t>
+          <t>불타는 숲</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Acertos de Contas</t>
+          <t>A Floresta em Chamas</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>9부 6화</t>
+          <t>9부 2화 변형</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>하파가 세베리누·아버지·모에마·오타비우·루시아·테레자의 무덤을 차례로 찾고, 세베리누 앞에서 처음으로 용서를 청한다.</t>
+          <t>강이 역대 최저 수위로 마르고 아루아칸 영토가 불타는데 국제 산림기금 약속은 절반에 그치자, 하파가 귀향한다.</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
@@ -29669,27 +29669,27 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 3화</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>그림자의 윤곽</t>
+          <t>낙인</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>O Contorno da Sombra</t>
+          <t>O Estigma</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 3화</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>브랑당이 홀로 숨지고, 아무도 오지 않은 장례식에 간 하파에게 자금 운반책의 이름이 든 봉투가 남는다.</t>
+          <t>외국 후원 NGO 등록·낙인법이 최종 폐지되고, 루아나가 첫 독자 정치 행보를 한다.</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
@@ -29697,27 +29697,27 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>9부 8화</t>
+          <t>9부 4화</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>임기 종료를 준비하며</t>
+          <t>병사의 재판</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Preparando a Saída</t>
+          <t>O Julgamento do Soldado</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>9부 8화 변형</t>
+          <t>9부 4화 변형</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>임기 종료 114일 전, 하파는 봉투를 검찰에 넘기고 경호 강화와 비상권한 제안을 거절한다.</t>
+          <t>GLO 작전 중 파벨라 소년을 쏜 귀환 병사가 일반 법원에 서고, 하파는 공설변호인의 눈으로 방청한다.</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr"/>
@@ -29725,27 +29725,27 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>9부 5화</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>마릴리아</t>
+          <t>루아나, 공식 후계자로</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Marília</t>
+          <t>Luana, a Sucessora</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>9부 5화</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>결선에서 이긴 당선인 루아나가 마릴리아를 수석장관으로 택하고, 지방 출신 두 사람이 마주 앉는다.</t>
+          <t>하파가 미뤄 둔 대화를 꺼내고, 당 예비경선에서 루아나가 공식 대선 후보로 선출된다.</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
@@ -29753,27 +29753,27 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>9부 6화</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>마지막 이양 준비</t>
+          <t>개인적 화해와 정리</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Os Últimos Preparativos</t>
+          <t>Acertos de Contas</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>9부 6화</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>임기 마지막 날인 새해 전날 밤, 경호를 줄인 채 강변을 걷던 하파가 저격당해 루아나의 품에서 숨진다.</t>
+          <t>하파가 세베리누·아버지·모에마·오타비우·루시아·테레자의 무덤을 차례로 찾고, 세베리누 앞에서 처음으로 용서를 청한다.</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr"/>
@@ -29781,27 +29781,27 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>9부 7화</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>홀로 선 자리</t>
+          <t>그림자의 윤곽</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>O Lugar de Quem Fica Só</t>
+          <t>O Contorno da Sombra</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>9부 7화</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>사흘 애도 뒤로 취임을 미루자는 권유를 물리치고 루아나가 1월 1일 예정대로 선서한다.</t>
+          <t>브랑당이 홀로 숨지고, 아무도 오지 않은 장례식에 간 하파에게 자금 운반책의 이름이 든 봉투가 남는다.</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
@@ -29809,27 +29809,27 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>9부 12화</t>
+          <t>9부 8화</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>수사의 끝</t>
+          <t>임기 종료를 준비하며</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>O Fim da Investigação</t>
+          <t>Preparando a Saída</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>9부 12화</t>
+          <t>9부 8화 변형</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>독립수사단·검찰·의회 조사위가 각자 절차로 파벌 세탁망을 거친 테러와 암살의 돈줄을 오타실리우로 입증하고, 루아나는 개입하지 않는다.</t>
+          <t>임기 종료 114일 전, 하파는 봉투를 검찰에 넘기고 경호 강화와 비상권한 제안을 거절한다.</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr"/>
@@ -29837,30 +29837,142 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
+          <t>9부 9화</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>마릴리아</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Marília</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>9부 9화</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>결선에서 이긴 당선인 루아나가 마릴리아를 수석장관으로 택하고, 지방 출신 두 사람이 마주 앉는다.</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>9부 10화</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>마지막 이양 준비</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Os Últimos Preparativos</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>9부 10화</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>임기 마지막 날인 새해 전날 밤, 경호를 줄인 채 강변을 걷던 하파가 저격당해 루아나의 품에서 숨진다.</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>9부 11화</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>홀로 선 자리</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>O Lugar de Quem Fica Só</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>9부 11화</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>사흘 애도 뒤로 취임을 미루자는 권유를 물리치고 루아나가 1월 1일 예정대로 선서한다.</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>9부 12화</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>수사의 끝</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>O Fim da Investigação</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>9부 12화</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>독립수사단·검찰·의회 조사위가 각자 절차로, 협력 진술한 피게이로의 조선소 유령회사와 파벌 세탁망을 거친 테러·암살의 돈줄을 오타실리우로 입증하고, 루아나는 개입하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
           <t>9부 에필로그</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>연결 고리</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr">
         <is>
           <t>O Elo</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="D169" s="4" t="inlineStr">
         <is>
           <t>9부 에필로그 변형</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
+      <c r="E169" s="4" t="inlineStr">
         <is>
           <t>4년 뒤 인도된 오타실리우가 공설변호인과 함께 재판정에 서는 아침, 루아나가 임기를 마치고 마릴리아 누니스가 선서한다. 제는 공설변호인 시험에 붙는다.</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr"/>
+      <c r="F169" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -29868,19 +29980,19 @@
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A43:F43"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>

--- a/기획안/국가별_각색_기획안.xlsx
+++ b/기획안/국가별_각색_기획안.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 7부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
+          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 8부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -656,17 +656,17 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 6부 테러와 암살의 돈이 이르만다지 두 노르치의 주유소 체인·무허가 핀테크 세탁망을 거쳐 전 재무차관 오타실리우에게서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 그의 법정에는 공설변호인이 붙는다 — 하파가 지킨 ‘누구나 변호받을 권리’다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
+          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 7부 유세장 테러와 암살의 돈이 이르만다지 두 노르치의 주유소 체인·무허가 핀테크 세탁망을 거쳐 전 재무차관 오타실리우에게서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 그의 법정에는 공설변호인이 붙는다 — 하파가 지킨 ‘누구나 변호받을 권리’다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>9부</t>
+          <t>10부</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 12화 안에서 프라두·세베리누·수은의 척추 사이에 건설사(모라이스 레아우)·방산업체(센치넬라 아우스트랄)·조선소(마레 아우타) 세 고객의 1~2화 사건 아크를 끼워 하파의 재능과 도덕적 대가가 함께 쌓이게 했으며(세 고객은 3·4·6·7·8·9부에 돌아온다), 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
+          <t>10부 구성. 무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 12화 안에서 프라두·세베리누·수은의 척추 사이에 건설사(모라이스 레아우)·방산업체(센치넬라 아우스트랄)·조선소(마레 아우타) 세 고객의 1~2화 사건 아크를 끼워 하파의 재능과 도덕적 대가가 함께 쌓이게 했으며(세 고객은 3·4·5·6·8·9·10부에 돌아온다), 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했다. 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부로 독립시켰고, 그 대신 압축하지 않고 원작 6부 재선 캠페인 12화를 7부 「재신임」으로, 원작 7부 비상대권의 유혹 12화를 8부 「유혹」으로 각각 온전히 살렸다(파벌·민병대 통제 구역의 유세, 질다의 테러 사망, 하벨루 국방장관과 센치넬라 아우스트랄의 GLO·감청 로비, 작은 월권, 위기결정위원회 법). 그 결과 원작 대비 7부부터 부 번호가 한 칸 밀린다: 원작 6·7·8·9부가 이 판의 7·8·9·10부이며, 각 화의 ‘대응 원작 화’는 원작 번호 그대로 적는다.</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -25654,7 +25654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="120" customHeight="1">
+    <row r="10" ht="135" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>마모</t>
@@ -25759,7 +25759,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>부마다 핵심 인물을 하나씩 잃는다: 상대 변호인이자 뒤늦은 스승 세베리누(하파의 로펌 측이 만든 ‘증거’로 구금 중 사망) → 로펌에 남아 프라두 편에 선 친구 오타비우의 배신·원주민 지도자 모에마의 투옥 → 아버지 뺑소니 사망·기자 루시아 실종 → 모에마 옥중 사망 → 오타비우 피살·루시아 유해 발견·브랑당 퇴장 → 파벌과 민병대 사이 파벨라의 공동체 라디오 진행자 도나 테레자 피살(민병대) → 감사인 질다 테러 사망과 하파 자신의 원칙의 흔들림 → 카이우 사망 → 브랑당의 고독사와 하파 암살. 1부의 상실에는 죄책감이 겹친다: 하파는 스승을 잃는 것이 아니라 자기 손으로 스승을 죽음에 몰아넣은 쪽에 서 있었다. 그 죄책감은 한 번에 오지 않고 네 고객의 승리마다 쌓인다 — 담합은 자백하되 깎아 낸 철근은 덮고 현장 기사 한 사람에게 떠넘긴 고가도로 붕괴, 사흘 만에 받아 낸 장갑차 수출 허가와 표적 목록에서 스승과 기자의 번호를 보고도 봉인한 감청 소송, 플랫폼 리베이트는 살리고 죽은 용접공을 탓하며 동료들의 임금을 깎은 회생 계획, 그리고 바로 그 감청에서 나온 날조 증거. 세 고객은 이후 주지사·대통령이 된 하파 앞에 계약 해지 대상·점거 자금원·GLO 로비스트·세탁 경로로 돌아와, 과거의 승리가 권력의 적이 된다. 폭력의 방식(청부 총격, 뺑소니, 실종, 호송 지연)은 브라질에서 활동가·기자가 실제로 당해 온 위협의 가상 등가물이다.</t>
+          <t>부마다 핵심 인물을 하나씩 잃는다: 상대 변호인이자 뒤늦은 스승 세베리누(하파의 로펌 측이 만든 ‘증거’로 구금 중 사망) → 로펌에 남아 프라두 편에 선 친구 오타비우의 배신·원주민 지도자 모에마의 투옥 → 아버지 뺑소니 사망·기자 루시아 실종 → 모에마 옥중 사망 → 오타비우 피살·루시아 유해 발견·브랑당 퇴장 → 파벌과 민병대 사이 파벨라의 공동체 라디오 진행자 도나 테레자 피살(민병대) → 감사인 질다 테러 사망 → 하파 자신의 원칙의 흔들림(영장 없는 감청 한 건) → 카이우 사망 → 브랑당의 고독사와 하파 암살. 1부의 상실에는 죄책감이 겹친다: 하파는 스승을 잃는 것이 아니라 자기 손으로 스승을 죽음에 몰아넣은 쪽에 서 있었다. 그 죄책감은 한 번에 오지 않고 네 고객의 승리마다 쌓인다 — 담합은 자백하되 깎아 낸 철근은 덮고 현장 기사 한 사람에게 떠넘긴 고가도로 붕괴, 사흘 만에 받아 낸 장갑차 수출 허가와 표적 목록에서 스승과 기자의 번호를 보고도 봉인한 감청 소송, 플랫폼 리베이트는 살리고 죽은 용접공을 탓하며 동료들의 임금을 깎은 회생 계획, 그리고 바로 그 감청에서 나온 날조 증거. 세 고객은 이후 주지사·대통령이 된 하파 앞에 계약 해지 대상·점거 자금원·GLO 로비스트·세탁 경로로 돌아와, 과거의 승리가 권력의 적이 된다. 폭력의 방식(청부 총격, 뺑소니, 실종, 호송 지연)은 브라질에서 활동가·기자가 실제로 당해 온 위협의 가상 등가물이다.</t>
         </is>
       </c>
     </row>
@@ -25771,7 +25771,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 7부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
+          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 8부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
         </is>
       </c>
     </row>
@@ -25783,7 +25783,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>점거의 밤에도 비상권한 없이 헌법 절차와 사법부에 수습을 맡기고, 가담자 사면 요구와 보복 입법을 모두 거부한다. 대통령으로서 가장 먼저 한 일 중 하나가 자기 정부를 상대로 소송할 수 있는 공설변호인청의 예산 자율과 독립을 헌법 개정으로 굳히는 것이다. 7부에서 백지 GLO 서명을 거부하고 모든 군 투입을 의회 승인·기한·사법 통제·공설변호인 입회에 묶는 위기결정위원회 법을 만들며, 「권력의 한계」법에 두 번의 임기 뒤 평생 재출마 금지를 스스로 넣는다. 퇴임 직전 경호 강화와 비상권한 제안도 거절한다.</t>
+          <t>점거의 밤에도 비상권한 없이 헌법 절차와 사법부에 수습을 맡기고, 가담자 사면 요구와 보복 입법을 모두 거부한다. 대통령으로서 가장 먼저 한 일 중 하나가 자기 정부를 상대로 소송할 수 있는 공설변호인청의 예산 자율과 독립을 헌법 개정으로 굳히는 것이다. 8부에서 백지 GLO 서명을 거부하고 모든 군 투입을 의회 승인·기한·사법 통제·공설변호인 입회에 묶는 위기결정위원회 법을 만들며, 「권력의 한계」법에 두 번의 임기 뒤 평생 재출마 금지를 스스로 넣는다. 퇴임 직전 경호 강화와 비상권한 제안도 거절한다.</t>
         </is>
       </c>
     </row>
@@ -25807,11 +25807,11 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 6부 테러와 암살의 돈이 이르만다지 두 노르치의 주유소 체인·무허가 핀테크 세탁망을 거쳐 전 재무차관 오타실리우에게서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 그의 법정에는 공설변호인이 붙는다 — 하파가 지킨 ‘누구나 변호받을 권리’다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
+          <t>하파는 새해 전날 밤 저격당해 죽지만, 루아나는 애도 연기를 물리치고 1월 1일 예정대로 취임하며 수사에 개입하지 않는다. 대통령이 아니라 제도가 범인을 쫓는다: 연방경찰 독립수사단, 검찰, 대법원, 의회 조사위원회가 각자의 절차로 움직여 7부 유세장 테러와 암살의 돈이 이르만다지 두 노르치의 주유소 체인·무허가 핀테크 세탁망을 거쳐 전 재무차관 오타실리우에게서 나왔음을 입증하고, 국제 사법공조로 그를 인도받아 법정에 세운다. 그의 법정에는 공설변호인이 붙는다 — 하파가 지킨 ‘누구나 변호받을 권리’다. 4년 뒤 권력은 다시 선거로 마릴리아에게 넘어간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>구성·무게중심</t>
@@ -25819,7 +25819,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>9부 × 12화 + 에필로그. 무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 12화 안에서 프라두·세베리누·수은의 척추 사이에 건설사(모라이스 레아우)·방산업체(센치넬라 아우스트랄)·조선소(마레 아우타) 세 고객의 1~2화 사건 아크를 끼워 하파의 재능과 도덕적 대가가 함께 쌓이게 했으며(세 고객은 3·4·6·7·8·9부에 돌아온다), 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했으며, 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부 전체로 늘렸다. 대신 원작 6부 재선 캠페인 12화를 7부 앞 4화로, 원작 7부 비상대권의 유혹을 7부 뒤 8화로 압축했다.</t>
+          <t>10부 × 12화 + 에필로그. 10부 구성. 무게중심을 아마존·파벨라와 제도 공격 두 곳에 둔다. 1부를 주인공이 가해자 쪽 대형 로펌 변호사로 서는 ‘반대편에서 시작하는’ 이야기로 뒤집고, 12화 안에서 프라두·세베리누·수은의 척추 사이에 건설사(모라이스 레아우)·방산업체(센치넬라 아우스트랄)·조선소(마레 아우타) 세 고객의 1~2화 사건 아크를 끼워 하파의 재능과 도덕적 대가가 함께 쌓이게 했으며(세 고객은 3·4·5·6·8·9·10부에 돌아온다), 2부를 공설변호인의 파벨라 구금심사·공익소송·강의 코카인-금 경로 서사로 재설계했다. 원작 3부 앞에 공직 사퇴(desincompatibilização) 한 화를 넣고 개표·당선 두 화를 한 화로 압축했다. 원작 5부 7화 한 화였던 쿠데타 시도를 민병대·파벌 서사와 묶어 6부 「삼권의 밤」 한 부로 독립시켰고, 그 대신 압축하지 않고 원작 6부 재선 캠페인 12화를 7부 「재신임」으로, 원작 7부 비상대권의 유혹 12화를 8부 「유혹」으로 각각 온전히 살렸다(파벌·민병대 통제 구역의 유세, 질다의 테러 사망, 하벨루 국방장관과 센치넬라 아우스트랄의 GLO·감청 로비, 작은 월권, 위기결정위원회 법). 그 결과 원작 대비 7부부터 부 번호가 한 칸 밀린다: 원작 6·7·8·9부가 이 판의 7·8·9·10부이며, 각 화의 ‘대응 원작 화’는 원작 번호 그대로 적는다.</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>‘먼저 커피부터(Primeiro o cafezinho)’. 세베리누는 사무실에 온 사람에게, 심지어 자신을 무너뜨리러 온 상대편 로펌 변호사 하파에게도 작은 잔의 커피부터 낸다. 구치소 면회에서도 교도관에게 얻은 커피를 하파에게 먼저 민다. 하파는 공설변호인실에서 겁먹은 피의자 가족에게 같은 커피를 내게 되고, 부솔라 감사의 질다도 그렇다. 질다가 남긴 카드 ‘커피를 잊지 말 것(Não esquecer o cafezinho)’이 8부에서 ‘고통을 안고 온 사람에게는 먼저 커피를’로 해독된다.</t>
+          <t>‘먼저 커피부터(Primeiro o cafezinho)’. 세베리누는 사무실에 온 사람에게, 심지어 자신을 무너뜨리러 온 상대편 로펌 변호사 하파에게도 작은 잔의 커피부터 낸다. 구치소 면회에서도 교도관에게 얻은 커피를 하파에게 먼저 민다. 하파는 공설변호인실에서 겁먹은 피의자 가족에게 같은 커피를 내게 되고, 부솔라 감사의 질다도 그렇다. 질다가 남긴 카드 ‘커피를 잊지 말 것(Não esquecer o cafezinho)’이 9부 10화에서 ‘고통을 안고 온 사람에게는 먼저 커피를’로 해독된다.</t>
         </is>
       </c>
     </row>
@@ -25967,7 +25967,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1부 3화 상대편으로 첫 대면, 6화 하파가 봉인한 감청 표적 목록에 이름이 오르고, 9화 그 감청으로 ‘리스크 정보’ 업체가 만든 증인매수 자료로 날조 혐의 체포, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망</t>
+          <t>1부 3화 상대편으로 첫 대면, 6화 하파가 봉인한 감청 표적 목록에 이름이 오르고, 9화 그 감청으로 ‘리스크 정보’ 업체가 만든 증인매수 자료로 날조 혐의 체포, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망. 8부 9화 조라이지가 그가 ‘언젠가 그 자리에 앉을 사람에게’ 쓴 미발송 편지를 하파에게 건넨다</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -26107,7 +26107,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>9부까지 곁에 있다가 에필로그 이전 화면 밖에서 조용히 사망</t>
+          <t>10부까지 곁에 있다가(7부 10화 루아나 병문안, 8부 9화 전화)  에필로그 이전 화면 밖에서 조용히 사망</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -26135,7 +26135,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 첫 승소 축하연에서 하파를 직접 치하, 4부 4화 조건부 공개 지지, 5부 8화 공항에서 체포, 8부 11화 유죄 판결·해외 자산 환수</t>
+          <t>1부 5화 첫 승소 축하연에서 하파를 직접 치하, 4부 4화 조건부 공개 지지, 5부 8화 공항에서 체포, 9부 11화 유죄 판결·해외 자산 환수</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1부 1화 하파에게 모라이스 레아우와 프라두 사건을 맡기고, 5화 축하연에서 센치넬라 아우스트랄을 소개, 12화 ‘돌아올 자리는 비워 두겠다’며 사직서를 받는다. 2부 6화 오타비우를 파트너로 올려 옛 고객들을 넘긴다. 5부 6화 오타비우 피살 뒤 로펌 내부 감사를 시작하고, 8부 12화 마레 아우타의 옛 자문 계약서를 수사단에 제출한다. 생존</t>
+          <t>1부 1화 하파에게 모라이스 레아우와 프라두 사건을 맡기고, 5화 축하연에서 센치넬라 아우스트랄을 소개, 12화 ‘돌아올 자리는 비워 두겠다’며 사직서를 받는다. 2부 6화 오타비우를 파트너로 올려 옛 고객들을 넘긴다. 5부 6화 오타비우 피살 뒤 로펌 내부 감사를 시작하고, 9부 12화 마레 아우타의 옛 자문 계약서를 수사단에 제출한다. 생존</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -26219,7 +26219,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 하파가 외교부 권고를 뒤집고 장갑차·탄약 수출 허가를 받아 주고, 6화 같은 로비망의 ‘비지아’ 불법 감청 소송을 국가안보 기밀로 봉인해 준다. 7부 6화 하벨루 국방장관과 함께 파벨라 무기한 GLO(장갑차 조달)·감청 시스템 도입을 로비하고, 7부 8화 수출 장갑차가 외국 시위 진압에 쓰인 사실과 과다 계약이 카이우의 보고서로 드러난다. 8부 5화 ‘비지아’ 해체와 함께 불구속 기소</t>
+          <t>1부 5화 하파가 외교부 권고를 뒤집고 장갑차·탄약 수출 허가를 받아 주고, 6화 같은 로비망의 ‘비지아’ 불법 감청 소송을 국가안보 기밀로 봉인해 준다. 8부 3화 하벨루 국방장관과 함께 파벨라 무기한 GLO(장갑차 조달)·감청 시스템 도입을 로비하고, 8부 6화 수출 장갑차가 외국 시위 진압에 쓰인 사실과 과다 계약이 카이우의 보고서로 드러나며, 8부 7화 하파가 바로 그 ‘비지아’로 영장 없는 감청 한 건을 허락한다. 9부 5화 ‘비지아’ 해체와 함께 불구속 기소</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -26247,7 +26247,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>1부 8화 사고와 회생 신청, 10화 채권자 집회에서 회생안 통과(다미아나가 하파에게 남편의 작업화를 내민다). 4부 6화 다미아나가 조선소 미지급 노동자들을 이끌고 전국 파업에 합류하고, 5부 3화 실소유자 공개 법안 공청회에서 체불 임금 뒤의 유령회사를 증언한다. 8부 12화 마레 아우타의 옛 플랫폼 리베이트 계좌가 오타실리우의 세탁 경로로 드러나고, 9부 12화 아우두가 협력 진술(colaboração premiada)로 돈줄을 확정해 준다. 다미아나는 에필로그까지 생존</t>
+          <t>1부 8화 사고와 회생 신청, 10화 채권자 집회에서 회생안 통과(다미아나가 하파에게 남편의 작업화를 내민다). 4부 6화 다미아나가 조선소 미지급 노동자들을 이끌고 전국 파업에 합류하고, 5부 3화 실소유자 공개 법안 공청회에서 체불 임금 뒤의 유령회사를 증언하며, 7부 5화 재선 유세에서 하파를 맞는다. 9부 12화 마레 아우타의 옛 플랫폼 리베이트 계좌가 오타실리우의 세탁 경로로 드러나고, 10부 12화 아우두가 협력 진술(colaboração premiada)로 돈줄을 확정해 준다. 다미아나는 에필로그까지 생존</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 승소 축하연에서 첫 등장해 방산업체 수출 허가 로비망을 연결, 9화 ‘비지아’ 감청으로 만든 증인매수 자료를 하파에게 건넨다, 4부 7화 진압 대신 협상 선택, 5부 9화 루시아 사건 방조가 드러나 사임, 8부 5화 마지막 대화, 9부 7화 홀로 병사(아무도 오지 않은 장례식)</t>
+          <t>1부 5화 승소 축하연에서 첫 등장해 방산업체 수출 허가 로비망을 연결, 9화 ‘비지아’ 감청으로 만든 증인매수 자료를 하파에게 건넨다, 4부 7화 진압 대신 협상 선택, 5부 9화 루시아 사건 방조가 드러나 사임, 9부 5화 마지막 대화, 10부 7화 홀로 병사(아무도 오지 않은 장례식)</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -26303,7 +26303,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>4부 3화 합류, 6부 8화 점거의 밤 대통령궁을 지킨다. 7부 2화 테러로 중상, 9부 11화 1월 1일 대통령 취임, 수사 불개입 원칙을 지키고 에필로그에서 4년 임기 뒤 퇴임</t>
+          <t>4부 3화 합류, 6부 8화 점거의 밤 대통령궁을 지킨다. 7부 2화 첫 단독 유세, 7부 6화 테러로 중상, 8부 1화 수석장관(카자 시비우) 임명, 8부 8화 대통령에게 정면으로 맞선다, 10부 11화 1월 1일 대통령 취임, 수사 불개입 원칙을 지키고 에필로그에서 4년 임기 뒤 퇴임</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>끝까지 남는다. 7부 10화 처음으로 대통령에게 공개적으로 반대</t>
+          <t>끝까지 남는다. 8부 8화 처음으로 대통령에게 공개적으로 반대</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -26359,7 +26359,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>7부에서 스스로의 변질을 자각하고 흑색선전 카드를 포기, 끝까지 조언자로 남는다</t>
+          <t>7부 재선전에서 흑색선전 카드를 포기하고, 8부 3화 비상입법을 옹호하는 자신의 변질을 자각해 불안해한다. 끝까지 조언자로 남는다</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -26387,7 +26387,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>3부 12화 첫 등장. 질다는 7부 2화 레시피 유세장 테러로 사망해 카드 ‘커피를 잊지 말 것’을 남기고, 카이우는 7부 8화 대통령의 부탁을 거절한 뒤 8부 8화 12년 전 과오를 고백하고 심장 질환으로 사망</t>
+          <t>3부 12화 첫 등장. 질다는 7부 4화 가짜 내부고발에 처음 속내를 드러내고 7부 6화 레시피 유세장 테러로 사망해 카드 ‘커피를 잊지 말 것’을 남기고, 카이우는 8부 6화 장갑차 보고서를 미뤄 달라는 대통령의 부탁을 거절한 뒤 9부 8화 12년 전 과오를 고백하고 심장 질환으로 사망</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -26415,7 +26415,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1부 12화 장례식에서 하파에게 세베리누의 커피잔을 건넨다. 7부 11화 세베리누의 기록을 건넨다. 에필로그까지 생존</t>
+          <t>1부 12화 장례식에서 하파에게 세베리누의 커피잔을 건넨다. 8부 9화 세베리누의 군정기 변론 기록과 미발송 편지를 건넨다. 에필로그까지 생존</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -26443,7 +26443,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>5부 4~5화 제보·파업 수습 협력, 8부 7화 주지사 당선·부채 공개, 9부 9화 루아나의 수석장관, 에필로그 대통령 취임</t>
+          <t>5부 4~5화 제보·파업 수습 협력, 9부 7화 주지사 당선·부채 공개, 10부 9화 루아나의 수석장관, 에필로그 대통령 취임</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -26471,7 +26471,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1부 10화 마레 아우타 회생안 속 해양플랫폼 리베이트 ‘자문료’ 유령회사의 실소유주로 이름 없이 스친다. 5부 1화 ‘1년 뒤엔 당신 없다’, 6부 10화 이르만다지 두 노르치의 연료·핀테크 세탁망에 이름이 스친다. 8부 12화 마레 아우타의 옛 자문료 계좌가 그를 가리키는 가운데 해외 도피, 9부 12화 테러·암살 자금원으로 확정·기소, 에필로그에서 국제 사법공조로 인도되어 공설변호인이 붙은 재판정에 선다</t>
+          <t>1부 10화 마레 아우타 회생안 속 해양플랫폼 리베이트 ‘자문료’ 유령회사의 실소유주로 이름 없이 스친다. 5부 1화 ‘1년 뒤엔 당신 없다’, 6부 10화 이르만다지 두 노르치의 연료·핀테크 세탁망에 이름이 스친다. 9부 12화 마레 아우타의 옛 자문료 계좌가 그를 가리키는 가운데 해외 도피, 10부 12화 테러·암살 자금원으로 확정·기소, 에필로그에서 국제 사법공조로 인도되어 공설변호인이 붙은 재판정에 선다</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>6부 점거의 밤 거리를 두며 선을 긋고, 7부 4화 패배 인정, 9부 1화 제도권 야당 지도자로 재등장</t>
+          <t>6부 점거의 밤 거리를 두며 선을 긋고, 7부 1화 경제 공세, 8화 구체제망 자금 발각, 9화 토론에서 치안기관 권한 확대 제안, 12화 패배 인정, 10부 1화 제도권 야당 지도자로 재등장</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -26527,7 +26527,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2부 2~3화 무죄, 3부 4화 파벌 통제 구역에서 유세단의 길을 협상, 8부 4화 공개 공모에 지원, 에필로그 공설변호인 시험 합격</t>
+          <t>2부 2~3화 무죄, 3부 4화 파벌 통제 구역에서 유세단의 길을 협상, 7부 5화 재선 유세에서 다시 길을 연다, 9부 4화 공개 공모에 지원, 에필로그 공설변호인 시험 합격</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -26555,7 +26555,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>6부 1화 등장, 2화 민병대 총격으로 사망. 9부 6화 하파가 무덤을 찾는다</t>
+          <t>6부 1화 등장, 2화 민병대 총격으로 사망. 10부 6화 하파가 무덤을 찾는다</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2025~2026년, 첫 임기 후반 / 대통령(1기)</t>
+          <t>2025~2026년 초, 첫 임기 후반 / 대통령(1기)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -26799,27 +26799,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>재신임과 유혹</t>
+          <t>재신임</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>A Reeleição e a Tentação</t>
+          <t>A Reeleição</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2026~2027년, 재선 캠페인과 두 번째 임기 1~7개월 / 대통령(재선 후보 → 2기)</t>
+          <t>2026년, 첫 임기 마지막 해의 재선 캠페인 / 대통령(1기) · 재선 후보</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>박빙의 재선전은 레시피 유세장 테러로 질다를 잃은 채 끝난다. 두 번째 임기 초 이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고 원자재 가격이 폭락하자 하벨루 국방장관과 장갑차·감청 장비를 파는 방산업체 센치넬라 아우스트랄의 로비 속에 파벨라 무기한 GLO·군인 면책·선거 연기·플랫폼 차단·감청의 유혹이 오고, 하파는 한때 자신이 봉인해 준 감청 시스템으로 한 번 선을 넘은 뒤 루아나와 부딪치고 벼랑 끝에서 백지 권한을 포기한다.</t>
+          <t>개혁의 피로 속에 치안 포퓰리스트 단타스가 딥페이크와 가짜 증인으로 몰아치고, 파벌과 민병대는 다시 누가 파벨라에서 유세할 수 있는지 정한다. 레시피 유세장 테러로 질다가 숨지고 루아나가 다친 뒤, 수사는 옛 정보기관의 돈과 단타스 뒤의 구체제망을 드러내지만 하파는 테러를 표로 바꾸지 않고 첫 임기에 세운 제도를 결산하며 박빙의 결선에서 재선된다.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>질다 페하스의 테러 사망, 하파 자신의 원칙에 대한 확신</t>
+          <t>감사인 질다 페하스의 테러 사망</t>
         </is>
       </c>
     </row>
@@ -26831,27 +26831,27 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>권력의 무게</t>
+          <t>유혹</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>O Peso do Poder</t>
+          <t>A Tentação</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2027~2029년, 두 번째 임기 1~2년차 / 대통령(2기)</t>
+          <t>2027년, 두 번째 임기 첫해 / 대통령(2기)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>「권력의 한계」법으로 권력을 나누고 루아나에게 실권을 넘긴다. 파벨라에서 돌아온 병사, 감시 체계 해체, 지방 부채를 다루는 사이 카이우가 쓰러지고, 질다를 죽인 돈은 파벌의 세탁망과 조선소 마레 아우타의 옛 ‘자문료’ 유령회사를 거쳐 해외로 빠져나간다.</t>
+          <t>두 번째 임기 초 파벌과 민병대의 전쟁이 여러 도시로 번지고 원자재 가격이 폭락하자, 하벨루 국방장관과 방산업체 센치넬라 아우스트랄이 파벨라 무기한 GLO·군인 면책·재선거 연기·플랫폼 차단·영장 없는 감청을 한 묶음으로 내민다. 하파는 카이우의 장갑차 보고서를 미뤄 달라 부탁하고 한때 자신이 봉인해 준 ‘비지아’로 한 번 선을 넘지만, 루아나의 정면 대결과 세베리누의 미발송 편지 끝에 백지 GLO 서명을 거부하고 위기결정위원회 법으로 비상권한을 스스로 묶는다.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>카이우 안드라지의 죽음, 자금원 오타실리우의 해외 도피</t>
+          <t>하파 자신의 원칙에 대한 확신(작은 월권)</t>
         </is>
       </c>
     </row>
@@ -26863,117 +26863,121 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
+          <t>권력의 무게</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>O Peso do Poder</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>2027년 말~2029년, 두 번째 임기 1~3년차 / 대통령(2기)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>「권력의 한계」법으로 권력을 나누고 루아나에게 실권을 넘긴다. 파벨라에서 돌아온 병사, 감시 체계 해체, 지방 부채를 다루는 사이 카이우가 쓰러지고, 질다를 죽인 돈은 파벌의 세탁망과 조선소 마레 아우타의 옛 ‘자문료’ 유령회사를 거쳐 해외로 빠져나간다.</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>카이우 안드라지의 죽음, 자금원 오타실리우의 해외 도피</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>10부</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
           <t>홀로 선 자리</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>O Lugar de Quem Fica Só</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>2030년(마지막 해)~2031년, 에필로그 2035년 / 대통령(임기 마지막 해) → 퇴임 → 사망</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>2030년(임기 마지막 해)~2031년 1월 1일, 에필로그 2035년 / 대통령(임기 마지막 해) → 퇴임 → 사망</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>가뭄과 산불 속 귀향, 낙인법 폐지, 파벨라 소년을 쏜 병사의 재판, 후계 선출. 브랑당이 홀로 죽고, 하파는 퇴임 전날 밤 저격당한다. 루아나는 홀로 선서하고, 수사기관·법원·의회가 각자의 절차로 파벌의 연료·핀테크 세탁망을 거친 암살의 돈줄을 끝까지 밝혀낸다.</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>브랑당의 고독한 죽음과 하파의 암살</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>4. 화별 구성</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>부·화</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>제목(한국어)</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>제목(현지어)</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>대응 원작 화</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>한 줄 줄거리</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>1부 1화</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>떠오르는 별</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>A Estrela da Casa</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>1부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>상파울루 동부 고가도로 붕괴로 일곱 명이 숨지고 담합 낙찰가에 맞춰 뺀 철근 이야기가 돌자, 서른두 살 하파가 시공사 모라이스 레아우와 프라두 수은 소송을 한 주에 맡는다.</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>1부 2화</t>
+          <t>1부 1화</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>관용 협정</t>
+          <t>떠오르는 별</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>O Acordo de Leniência</t>
+          <t>A Estrela da Casa</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1부 1화 확장</t>
+          <t>1부 1화 변형</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>하파는 담합만 자백하고 설계 변경은 덮는 관용 협정으로 회사를 살려 내고, 붕괴 책임은 스물여섯 살 현장 기사 파비아누 한 사람에게 돌린다.</t>
+          <t>상파울루 동부 고가도로 붕괴로 일곱 명이 숨지고 담합 낙찰가에 맞춰 뺀 철근 이야기가 돌자, 서른두 살 하파가 시공사 모라이스 레아우와 프라두 수은 소송을 한 주에 맡는다.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -26981,27 +26985,27 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>1부 3화</t>
+          <t>1부 2화</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>상대편의 커피</t>
+          <t>관용 협정</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>O Cafezinho do Adversário</t>
+          <t>O Acordo de Leniência</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1부 2화 변형</t>
+          <t>1부 1화 확장</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>고향 노바 카라자이에서 상대 변호인 세베리누가 먼저 커피를 내고, 법원 계단에서는 기자 루시아가 하파를 ‘독의 변호인’이라 부른다.</t>
+          <t>하파는 담합만 자백하고 설계 변경은 덮는 관용 협정으로 회사를 살려 내고, 붕괴 책임은 스물여섯 살 현장 기사 파비아누 한 사람에게 돌린다.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -27009,27 +27013,27 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>1부 4화</t>
+          <t>1부 3화</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>아버지의 식탁</t>
+          <t>상대편의 커피</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>A Mesa do Pai</t>
+          <t>O Cafezinho do Adversário</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1부 4화 변형</t>
+          <t>1부 2화 변형</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>파비아누 기소 뉴스에 정비공 출신 아버지가 ‘갚는 건 늘 현장 사람’이라 중얼거리고, 렌터카에 ‘살인자’가 긁히며 밤의 전화가 온다.</t>
+          <t>고향 노바 카라자이에서 상대 변호인 세베리누가 먼저 커피를 내고, 법원 계단에서는 기자 루시아가 하파를 ‘독의 변호인’이라 부른다.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -27037,27 +27041,27 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>1부 5화</t>
+          <t>1부 4화</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>작은 승리</t>
+          <t>아버지의 식탁</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Uma Pequena Vitória</t>
+          <t>A Mesa do Pai</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 변형</t>
+          <t>1부 4화 변형</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>수은을 채굴꾼 탓으로 돌린 감정서로 첫 판결을 이기고, 프라두가 치하하는 축하연에서 브랑당이 소개한 방산업체의 장갑차·탄약 수출 허가를 사흘 만에 받아 낸다.</t>
+          <t>파비아누 기소 뉴스에 정비공 출신 아버지가 ‘갚는 건 늘 현장 사람’이라 중얼거리고, 렌터카에 ‘살인자’가 긁히며 밤의 전화가 온다.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -27065,27 +27069,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>1부 6화</t>
+          <t>1부 5화</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>봉인된 목록</t>
+          <t>작은 승리</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>A Lista Sigilosa</t>
+          <t>Uma Pequena Vitória</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1부 6화 변형</t>
+          <t>1부 5화 변형</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>같은 로비망을 타고 주 경찰에 팔린 센치넬라 아우스트랄의 감청 프로그램 ‘비지아’ 소송을 국가안보 기밀로 봉인해 이기지만, 표적 목록의 세베리누와 루시아 번호에 침묵한다.</t>
+          <t>수은을 채굴꾼 탓으로 돌린 감정서로 첫 판결을 이기고, 프라두가 치하하는 축하연에서 브랑당이 소개한 방산업체의 장갑차·탄약 수출 허가를 사흘 만에 받아 낸다.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -27093,27 +27097,27 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>1부 7화</t>
+          <t>1부 6화</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>숲의 현장검증</t>
+          <t>봉인된 목록</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>A Inspeção Judicial</t>
+          <t>A Lista Sigilosa</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1부 7화 변형</t>
+          <t>1부 6화 변형</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>합의서를 받으러 간 강마을에서 손 떨리는 아이들을 보고, 아루아칸 현장검증에서 모에마와 마주한 날 숲 지킴이 청년이 총에 맞는다.</t>
+          <t>같은 로비망을 타고 주 경찰에 팔린 센치넬라 아우스트랄의 감청 프로그램 ‘비지아’ 소송을 국가안보 기밀로 봉인해 이기지만, 표적 목록의 세베리누와 루시아 번호에 침묵한다.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
@@ -27121,27 +27125,27 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 7화</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>건조독</t>
+          <t>숲의 현장검증</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>A Doca Seca</t>
+          <t>A Inspeção Judicial</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>1부 3화 변형</t>
+          <t>1부 7화 변형</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>이타과레 조선소 마레 아우타의 건조독 폭발로 용접공 시세루가 숨지고 석 달 치 임금이 밀린 채 회생이 신청되자, 하파는 그의 ‘수칙 위반’을 계획의 전제로 적는다.</t>
+          <t>합의서를 받으러 간 강마을에서 손 떨리는 아이들을 보고, 아루아칸 현장검증에서 모에마와 마주한 날 숲 지킴이 청년이 총에 맞는다.</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr"/>
@@ -27149,27 +27153,27 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>1부 9화</t>
+          <t>1부 8화</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>고발장</t>
+          <t>건조독</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>A Representação</t>
+          <t>A Doca Seca</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1부 8·9화 변형</t>
+          <t>1부 3화 변형</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>브랑당이 건넨 ‘증인 매수’ 자료로 하파가 세베리누를 고발하고, 오타비우는 증인이 돈을 받은 정황을 보고도 침묵한다. 새벽 세베리누가 체포된다.</t>
+          <t>이타과레 조선소 마레 아우타의 건조독 폭발로 용접공 시세루가 숨지고 석 달 치 임금이 밀린 채 회생이 신청되자, 하파는 그의 ‘수칙 위반’을 계획의 전제로 적는다.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
@@ -27177,27 +27181,27 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>1부 10화</t>
+          <t>1부 9화</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>덮인 보고서</t>
+          <t>고발장</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>O Laudo Enterrado</t>
+          <t>A Representação</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>1부 10화 변형</t>
+          <t>1부 8·9화 변형</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>플랫폼 리베이트로 조선소를 비운 ‘자문회사’ 채권은 살리고 임금은 깎은 회생안이 통과된 주, 하파는 2013년 수은 보고서를 찾고 구치소의 세베리누는 커피를 먼저 민다.</t>
+          <t>브랑당이 건넨 ‘증인 매수’ 자료로 하파가 세베리누를 고발하고, 오타비우는 증인이 돈을 받은 정황을 보고도 침묵한다. 새벽 세베리누가 체포된다.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr"/>
@@ -27205,27 +27209,27 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>1부 11화</t>
+          <t>1부 10화</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>석방의 날</t>
+          <t>덮인 보고서</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>O Dia da Soltura</t>
+          <t>O Laudo Enterrado</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1부 11화 변형</t>
+          <t>1부 10화 변형</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>하파가 루시아와 손잡고 날조 증거가 ‘비지아’ 감청에서 나왔다는 사실과 끊긴 심장약을 판사에게 넘겨 석방이 결정되지만, 그날 세베리누가 숨진다.</t>
+          <t>플랫폼 리베이트로 조선소를 비운 ‘자문회사’ 채권은 살리고 임금은 깎은 회생안이 통과된 주, 하파는 2013년 수은 보고서를 찾고 구치소의 세베리누는 커피를 먼저 민다.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -27233,83 +27237,83 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
+          <t>1부 11화</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>석방의 날</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>O Dia da Soltura</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>하파가 루시아와 손잡고 날조 증거가 ‘비지아’ 감청에서 나왔다는 사실과 끊긴 심장약을 판사에게 넘겨 석방이 결정되지만, 그날 세베리누가 숨진다.</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
           <t>1부 12화</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>사직서</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>A Demissão</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>1부 12화 변형</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>장례식에서 무심코 조문객에게 커피를 낸 하파가 네 고객의 이름을 적은 사직서를 레오노르에게 내고, 아버지와 오타비우가 말린다.</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>공설변호인 시험</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>O Concurso</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>반년 동안 부모 집에서 공부한 하파가 공설변호인 시험에 붙고, 로펌 동료들의 비웃음 속에 노바 카라자이 부임을 고른다.</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2부 2화</t>
+          <t>2부 1화</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>구금심사</t>
+          <t>공설변호인 시험</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Audiência de Custódia</t>
+          <t>O Concurso</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>2부 1화 변형</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>하루 마흔 건의 구금심사, 빌라 히반세이라의 열아홉 살 제페르송이 파벌 ‘운반책’으로 멍든 채 서 있다.</t>
+          <t>반년 동안 부모 집에서 공부한 하파가 공설변호인 시험에 붙고, 로펌 동료들의 비웃음 속에 노바 카라자이 부임을 고른다.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr"/>
@@ -27317,17 +27321,17 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2부 3화</t>
+          <t>2부 2화</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>운반책이 아닌 소년</t>
+          <t>구금심사</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>O Menino Que Não Era Mula</t>
+          <t>Audiência de Custódia</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -27337,7 +27341,7 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>똑같은 문장이 반복된 경찰 조서를 파고든 하파가 제의 무죄를 받아 내지만, 다른 서른 건은 이기지 못한다.</t>
+          <t>하루 마흔 건의 구금심사, 빌라 히반세이라의 열아홉 살 제페르송이 파벌 ‘운반책’으로 멍든 채 서 있다.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -27345,27 +27349,27 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2부 4화</t>
+          <t>2부 3화</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>루시아의 강</t>
+          <t>운반책이 아닌 소년</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>O Rio de Lúcia</t>
+          <t>O Menino Que Não Era Mula</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>2부 3화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>이제 편이 된 루시아가 이르만다지 두 노르치의 코카인 배가 불법 금 준설선과 같은 강길을 쓰는 것을 추적한다.</t>
+          <t>똑같은 문장이 반복된 경찰 조서를 파고든 하파가 제의 무죄를 받아 내지만, 다른 서른 건은 이기지 못한다.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -27373,27 +27377,27 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2부 5화</t>
+          <t>2부 4화</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>강 위의 비행장</t>
+          <t>루시아의 강</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>As Pistas Clandestinas</t>
+          <t>O Rio de Lúcia</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>2부 3화 변형</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>코카인과 금을 함께 싣는 숲속 불법 비행장 마흔 곳을 좌표로 기록하고, 협조한 원주민 보호청 직원이 협박받는다.</t>
+          <t>이제 편이 된 루시아가 이르만다지 두 노르치의 코카인 배가 불법 금 준설선과 같은 강길을 쓰는 것을 추적한다.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -27401,27 +27405,27 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>2부 5화</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>공익소송</t>
+          <t>강 위의 비행장</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>A Ação Civil Pública</t>
+          <t>As Pistas Clandestinas</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>2부 5화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>하파가 수은 강마을을 위한 공익소송을 내고, 파트너로 승진해 프라두와 하파의 옛 고객 셋을 물려받은 오타비우가 프라두 측 대리인으로 맞은편에 앉는다.</t>
+          <t>코카인과 금을 함께 싣는 숲속 불법 비행장 마흔 곳을 좌표로 기록하고, 협조한 원주민 보호청 직원이 협박받는다.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -27429,27 +27433,27 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2부 7화</t>
+          <t>2부 6화</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>헤지 클라레이라</t>
+          <t>공익소송</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>A Rede Clareira</t>
+          <t>A Ação Civil Pública</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>2부 1·2화 변형</t>
+          <t>2부 5화 변형</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>모에마·루시아·파벨라 어머니들과 인권 네트워크를 세우고, 인턴 비아가 거액 후원 재단의 돈이 프라두의 것임을 밝힌다.</t>
+          <t>하파가 수은 강마을을 위한 공익소송을 내고, 파트너로 승진해 프라두와 하파의 옛 고객 셋을 물려받은 오타비우가 프라두 측 대리인으로 맞은편에 앉는다.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -27457,27 +27461,27 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2부 8화</t>
+          <t>2부 7화</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>기준일</t>
+          <t>헤지 클라레이라</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>O Marco</t>
+          <t>A Rede Clareira</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>2부 4화 변형</t>
+          <t>2부 1·2화 변형</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>원주민 영토 ‘기준일’ 법안과 일괄 허가 법안이 오르고, 모에마가 상원에서 증언하며 원주민들이 수도로 행진한다.</t>
+          <t>모에마·루시아·파벨라 어머니들과 인권 네트워크를 세우고, 인턴 비아가 거액 후원 재단의 돈이 프라두의 것임을 밝힌다.</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -27485,27 +27489,27 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2부 9화</t>
+          <t>2부 8화</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>모에마의 구금</t>
+          <t>기준일</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>A Prisão de Moema</t>
+          <t>O Marco</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>2부 4화 변형</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>광산 트럭을 막으려 연방도로를 봉쇄한 모에마가 ‘범죄 결사’로 구속되고, 청장의 신중론을 넘어 하파가 변호를 맡는다.</t>
+          <t>원주민 영토 ‘기준일’ 법안과 일괄 허가 법안이 오르고, 모에마가 상원에서 증언하며 원주민들이 수도로 행진한다.</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr"/>
@@ -27513,27 +27517,27 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2부 10화</t>
+          <t>2부 9화</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 제안</t>
+          <t>모에마의 구금</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>A Proposta de Brandão</t>
+          <t>A Prisão de Moema</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>2부 7·8화 변형</t>
+          <t>2부 6화</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>브랑당이 ‘공익소송을 내리면 모에마는 풀려난다’는 거래를 내밀고, 아버지가 정비소에서 해고되며 동료들이 떠난다.</t>
+          <t>광산 트럭을 막으려 연방도로를 봉쇄한 모에마가 ‘범죄 결사’로 구속되고, 청장의 신중론을 넘어 하파가 변호를 맡는다.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr"/>
@@ -27541,27 +27545,27 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2부 11화</t>
+          <t>2부 10화</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>오타비우의 배신 발각</t>
+          <t>브랑당의 제안</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>A Traição Descoberta</t>
+          <t>A Proposta de Brandão</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>2부 10화 변형</t>
+          <t>2부 7·8화 변형</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>공익소송 감정 증인 명단이 새어 나가 증인 가족이 협박받고, 비아의 추적 끝에 오타비우가 드러난다.</t>
+          <t>브랑당이 ‘공익소송을 내리면 모에마는 풀려난다’는 거래를 내밀고, 아버지가 정비소에서 해고되며 동료들이 떠난다.</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr"/>
@@ -27569,83 +27573,83 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
+          <t>2부 11화</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>오타비우의 배신 발각</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>A Traição Descoberta</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>2부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>공익소송 감정 증인 명단이 새어 나가 증인 가족이 협박받고, 비아의 추적 끝에 오타비우가 드러난다.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
           <t>2부 12화</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>모에마의 재판</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>O Julgamento de Moema</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>2부 11·12화 변형</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>통역도 없는 재판에서 하파의 변론에도 모에마에게 징역 4년이 선고되고, ‘모에마에게 자유를’ 운동이 전국으로 번진다.</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>사퇴</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>A Desincompatibilização</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>출마하려면 선거 여섯 달 전 공직을 떠나야 한다. 하파가 공설변호인직 사퇴서를 쓰고, 아버지는 ‘또 안정을 버리냐’며 반대한다.</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="F85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3부 2화</t>
+          <t>3부 1화</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>정당 창당</t>
+          <t>사퇴</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>A Fundação do Partido</t>
+          <t>A Desincompatibilização</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>3부 1화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>안셀무가 2년간 서명을 모아 등록시킨 땅과노동당(PTT)에 하파가 입당하고, 창당대회에서 주지사 후보로 추대된다.</t>
+          <t>출마하려면 선거 여섯 달 전 공직을 떠나야 한다. 하파가 공설변호인직 사퇴서를 쓰고, 아버지는 ‘또 안정을 버리냐’며 반대한다.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr"/>
@@ -27653,27 +27657,27 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3부 3화</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>오타비우의 귀환</t>
+          <t>정당 창당</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>A Volta de Otávio</t>
+          <t>A Fundação do Partido</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>3부 2화</t>
+          <t>3부 1화 변형</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>임신한 아내 앞에서 흔들린 오타비우가 프라두와 옛 고객들의 로펌 내부 자료를 들고 하파를 찾아온다.</t>
+          <t>안셀무가 2년간 서명을 모아 등록시킨 땅과노동당(PTT)에 하파가 입당하고, 창당대회에서 주지사 후보로 추대된다.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
@@ -27681,27 +27685,27 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3부 4화</t>
+          <t>3부 3화</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>들어갈 수 없는 동네</t>
+          <t>오타비우의 귀환</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Onde Não Se Pode Entrar</t>
+          <t>A Volta de Otávio</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>3부 3화 변형</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할지 정하고, 제가 유세단의 길을 협상하며 농업 로비 방송들이 공세를 시작한다.</t>
+          <t>임신한 아내 앞에서 흔들린 오타비우가 프라두와 옛 고객들의 로펌 내부 자료를 들고 하파를 찾아온다.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr"/>
@@ -27709,27 +27713,27 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3부 5화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>아버지의 죽음</t>
+          <t>들어갈 수 없는 동네</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>A Morte do Pai</t>
+          <t>Onde Não Se Pode Entrar</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>3부 4화</t>
+          <t>3부 3화 변형</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>‘아들이 자랑스럽다’는 유세 영상으로 화제가 된 아버지 니바우두가 새벽길 뺑소니로 숨진다.</t>
+          <t>파벌과 민병대가 누가 파벨라와 강변 마을에서 유세할지 정하고, 제가 유세단의 길을 협상하며 농업 로비 방송들이 공세를 시작한다.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
@@ -27737,27 +27741,27 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>3부 6화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>루시아의 폭로전</t>
+          <t>아버지의 죽음</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>A Denúncia de Lúcia</t>
+          <t>A Morte do Pai</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>3부 5화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>루시아가 주정부·프라두 그룹·민병대·파벌 비행장을 잇는 ‘토지 세탁’ 구조의 최종 기사를 준비한다.</t>
+          <t>‘아들이 자랑스럽다’는 유세 영상으로 화제가 된 아버지 니바우두가 새벽길 뺑소니로 숨진다.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr"/>
@@ -27765,27 +27769,27 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 6화</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>선거 조작 저지</t>
+          <t>루시아의 폭로전</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Contra o Curral Eleitoral</t>
+          <t>A Denúncia de Lúcia</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>3부 6화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>민병대가 투표소 길목을 막고 표를 사는 ‘선거 목장’을 파벨라 주민 참관인단이 영상 기록으로 막아선다.</t>
+          <t>루시아가 주정부·프라두 그룹·민병대·파벌 비행장을 잇는 ‘토지 세탁’ 구조의 최종 기사를 준비한다.</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr"/>
@@ -27793,27 +27797,27 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 7화</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>루시아의 실종</t>
+          <t>선거 조작 저지</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>O Desaparecimento de Lúcia</t>
+          <t>Contra o Curral Eleitoral</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 6화</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>폭로 기사가 공개되어 전국이 들끓은 날 밤, 루시아가 강변 도로에서 흔적 없이 사라진다.</t>
+          <t>민병대가 투표소 길목을 막고 표를 사는 ‘선거 목장’을 파벨라 주민 참관인단이 영상 기록으로 막아선다.</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr"/>
@@ -27821,27 +27825,27 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 8화</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>거리로 나선 사람들</t>
+          <t>루시아의 실종</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>O Povo nas Ruas</t>
+          <t>O Desaparecimento de Lúcia</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 7화</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>루시아의 사진을 든 자발적 시위가 투표 이틀 전 전국 열두 개 도시로 번진다.</t>
+          <t>폭로 기사가 공개되어 전국이 들끓은 날 밤, 루시아가 강변 도로에서 흔적 없이 사라진다.</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr"/>
@@ -27849,27 +27853,27 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>3부 10화</t>
+          <t>3부 9화</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>오타비우의 희생</t>
+          <t>거리로 나선 사람들</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>O Sacrifício de Otávio</t>
+          <t>O Povo nas Ruas</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 8화</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>투표 전날 밤, 선거본부 압수수색 직전 루시아의 취재원 자료를 빼돌린 오타비우가 대신 체포된다.</t>
+          <t>루시아의 사진을 든 자발적 시위가 투표 이틀 전 전국 열두 개 도시로 번진다.</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr"/>
@@ -27877,27 +27881,27 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>3부 11화</t>
+          <t>3부 10화</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>당선, 그러나</t>
+          <t>오타비우의 희생</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Vitória, Mas…</t>
+          <t>O Sacrifício de Otávio</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>3부 10·11화 압축</t>
+          <t>3부 9화</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>투표일 밤 브랑당의 담판에 아무것도 약속하지 않은 하파가 당선되지만, 인수 방해와 연방의 재정 압박이 기다린다.</t>
+          <t>투표 전날 밤, 선거본부 압수수색 직전 루시아의 취재원 자료를 빼돌린 오타비우가 대신 체포된다.</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr"/>
@@ -27905,83 +27909,83 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
+          <t>3부 11화</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>당선, 그러나</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Vitória, Mas…</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>3부 10·11화 압축</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>투표일 밤 브랑당의 담판에 아무것도 약속하지 않은 하파가 당선되지만, 인수 방해와 연방의 재정 압박이 기다린다.</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>전국 무대로</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Rumo ao Palco Nacional</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>1년 반 뒤, 형기를 마친 파비아누의 증언으로 모라이스 레아우의 부풀린 주 도로 계약을 해지한 타피라주가 투명 예산의 모범이 되고, 대선 후보가 된 하파는 질다와 카이우를 만난다.</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>나라의 균열</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>O País Rachado</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>물가 폭등과 가뭄, 원주민 영토 침탈이 겹친 위기 속에 경제 자문을 영입한 대선 캠프가 출범한다.</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>4부 2화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>모에마의 옥중 투쟁</t>
+          <t>나라의 균열</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>A Luta de Moema na Prisão</t>
+          <t>O País Rachado</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>4부 2화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>프라두 그룹이 아루아칸 영토 채굴을 재개하자 수감 중인 모에마가 옥중 단식을 시작한다.</t>
+          <t>물가 폭등과 가뭄, 원주민 영토 침탈이 겹친 위기 속에 경제 자문을 영입한 대선 캠프가 출범한다.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -27989,27 +27993,27 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>4부 3화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>루아나의 등장</t>
+          <t>모에마의 옥중 투쟁</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>A Chegada de Luana</t>
+          <t>A Luta de Moema na Prisão</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>4부 3화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>단식 아흐레째, 스물두 살 법대생 루아나 마르키스가 캠프 자원활동가로 합류한다.</t>
+          <t>프라두 그룹이 아루아칸 영토 채굴을 재개하자 수감 중인 모에마가 옥중 단식을 시작한다.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -28017,27 +28021,27 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>4부 4화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>프라두의 배신적 지지</t>
+          <t>루아나의 등장</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>O Apoio Traiçoeiro de Prado</t>
+          <t>A Chegada de Luana</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>4부 4화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>프라두가 은밀히 지지를 제안하고, 하파는 원주민 영토 철수와 노동자 보상을 공개 조건으로 건다.</t>
+          <t>단식 아흐레째, 스물두 살 법대생 루아나 마르키스가 캠프 자원활동가로 합류한다.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -28045,27 +28049,27 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>4부 5화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>모에마의 옥중 사망</t>
+          <t>프라두의 배신적 지지</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>A Morte de Moema</t>
+          <t>O Apoio Traiçoeiro de Prado</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>4부 5화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>법원이 병원 이송을 승인했지만 ‘호송 절차’로 지연되는 사이, 단식 14일째 모에마가 숨진다.</t>
+          <t>프라두가 은밀히 지지를 제안하고, 하파는 원주민 영토 철수와 노동자 보상을 공개 조건으로 건다.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -28073,27 +28077,27 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>거리의 혁명</t>
+          <t>모에마의 옥중 사망</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>A Revolução nas Ruas</t>
+          <t>A Morte de Moema</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>원주민 행진과 트럭·교원 파업에 다미아나가 이끄는 조선소 미지급 노동자들이 합류해 47개 도시로 번지고, 한 주 군경 장교가 진압 명령을 거부한다.</t>
+          <t>법원이 병원 이송을 승인했지만 ‘호송 절차’로 지연되는 사이, 단식 14일째 모에마가 숨진다.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -28101,27 +28105,27 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 6화</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 선택</t>
+          <t>거리의 혁명</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>A Escolha de Brandão</t>
+          <t>A Revolução nas Ruas</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 6화</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>대통령궁 긴급회의에서 강경파가 ‘방위 상태’ 선포를 밀어붙이자 브랑당이 협상을 택한다.</t>
+          <t>원주민 행진과 트럭·교원 파업에 다미아나가 이끄는 조선소 미지급 노동자들이 합류해 47개 도시로 번지고, 한 주 군경 장교가 진압 명령을 거부한다.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -28129,27 +28133,27 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 7화</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>암살 시도</t>
+          <t>브랑당의 선택</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>O Atentado</t>
+          <t>A Escolha de Brandão</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 7화</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>농업 로비의 아성 도시에서 유세를 강행한 하파를 겨눈 저격이 벌어지고, 저격범이 사살된다.</t>
+          <t>대통령궁 긴급회의에서 강경파가 ‘방위 상태’ 선포를 밀어붙이자 브랑당이 협상을 택한다.</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -28157,27 +28161,27 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 8화</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>구체제의 붕괴</t>
+          <t>암살 시도</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>A Queda do Velho Regime</t>
+          <t>O Atentado</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 8화</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>부솔라가 찾은 자금 흐름이 대통령 비서실장과 암살 배후에 닿고, 대통령이 사임한다.</t>
+          <t>농업 로비의 아성 도시에서 유세를 강행한 하파를 겨눈 저격이 벌어지고, 저격범이 사살된다.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr"/>
@@ -28185,27 +28189,27 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 9화</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>선거전 최종전</t>
+          <t>구체제의 붕괴</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>A Batalha Final</t>
+          <t>A Queda do Velho Regime</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 9화</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>부통령 권한대행 아래 치러지는 대선, 마지막 TV 토론과 단체방 가짜뉴스의 공방이 벌어진다.</t>
+          <t>부솔라가 찾은 자금 흐름이 대통령 비서실장과 암살 배후에 닿고, 대통령이 사임한다.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
@@ -28213,27 +28217,27 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 10화</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>당선의 밤</t>
+          <t>선거전 최종전</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>A Noite da Vitória</t>
+          <t>A Batalha Final</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 10화</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>결선 개표가 밤새 이어지고, 새벽 무렵 하파의 승리가 확정되자 비아와 안셀무가 말없이 커피를 따른다.</t>
+          <t>부통령 권한대행 아래 치러지는 대선, 마지막 TV 토론과 단체방 가짜뉴스의 공방이 벌어진다.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
@@ -28241,83 +28245,83 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>당선의 밤</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>A Noite da Vitória</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>결선 개표가 밤새 이어지고, 새벽 무렵 하파의 승리가 확정되자 비아와 안셀무가 말없이 커피를 따른다.</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>취임 전야</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>A Véspera da Posse</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
         <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="E109" s="9" t="inlineStr">
         <is>
           <t>취임 준비 대신 하파는 세베리누와 아버지, 모에마의 무덤을 차례로 찾아간다.</t>
         </is>
       </c>
-      <c r="F108" s="9" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>취임과 첫 벽</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>A Posse e o Primeiro Muro</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>재무부가 예비비 자료를 감추자 하파는 부솔라 팀에 신설 재정투명성청을 맡기고, 공설변호인청 예산 자율 개헌안을 첫 법안으로 보낸다.</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>5부 2화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>브랑당과의 재계약</t>
+          <t>취임과 첫 벽</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Um Novo Acordo com Brandão</t>
+          <t>A Posse e o Primeiro Muro</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>5부 2화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>감사가 ANSI의 비밀 운영비로 이어지고, 하파는 브랑당과 조건부 공조를 맺는다.</t>
+          <t>재무부가 예비비 자료를 감추자 하파는 부솔라 팀에 신설 재정투명성청을 맡기고, 공설변호인청 예산 자율 개헌안을 첫 법안으로 보낸다.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
@@ -28325,27 +28329,27 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>5부 3화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>프라두의 마지막 카드</t>
+          <t>브랑당과의 재계약</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>A Última Carta de Prado</t>
+          <t>Um Novo Acordo com Brandão</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>5부 3화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>실소유자 공개·토지 등기 정비 법안이 프라두 제국을 겨누고, 공청회에서 다미아나가 체불 임금 뒤에 숨은 조선소 유령회사를 증언하자 의회 농업 로비가 반격한다.</t>
+          <t>감사가 ANSI의 비밀 운영비로 이어지고, 하파는 브랑당과 조건부 공조를 맺는다.</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
@@ -28353,27 +28357,27 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>5부 4화</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>지방의 반란</t>
+          <t>프라두의 마지막 카드</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>A Rebelião de Serra Parima</t>
+          <t>A Última Carta de Prado</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>5부 4화 확장</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>희토류 산지 세하 파리마주 주지사가 법 적용을 거부하고 군경 파업을 부추기자 부지사 마릴리아가 자료를 넘긴다.</t>
+          <t>실소유자 공개·토지 등기 정비 법안이 프라두 제국을 겨누고, 공청회에서 다미아나가 체불 임금 뒤에 숨은 조선소 유령회사를 증언하자 의회 농업 로비가 반격한다.</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
@@ -28381,17 +28385,17 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 4화</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>파업의 끝</t>
+          <t>지방의 반란</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>O Fim da Greve</t>
+          <t>A Rebelião de Serra Parima</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -28401,7 +28405,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>연방 개입 대신 군경 가족들과의 협상으로 파업이 풀리고, 반란 주지사는 법정에 선다.</t>
+          <t>희토류 산지 세하 파리마주 주지사가 법 적용을 거부하고 군경 파업을 부추기자 부지사 마릴리아가 자료를 넘긴다.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
@@ -28409,27 +28413,27 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>5부 6화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>개혁의 대가</t>
+          <t>파업의 끝</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>O Preço da Reforma</t>
+          <t>O Fim da Greve</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 4화 확장</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>판·검사 부패망 조사에 자원한 오타비우가 하파와 옛 우정을 되찾은 직후 청부 총격에 숨진다.</t>
+          <t>연방 개입 대신 군경 가족들과의 협상으로 파업이 풀리고, 반란 주지사는 법정에 선다.</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
@@ -28437,27 +28441,27 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>5부 7화</t>
+          <t>5부 6화</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>국제적 고립과 압박</t>
+          <t>개혁의 대가</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Isolamento e Pressão</t>
+          <t>O Preço da Reforma</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>5부 6화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>무역협정 중단과 자본 유출, 헤알화 급락이 몰아치는 가운데 국방장관이 사임한다.</t>
+          <t>판·검사 부패망 조사에 자원한 오타비우가 하파와 옛 우정을 되찾은 직후 청부 총격에 숨진다.</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr"/>
@@ -28465,27 +28469,27 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 7화</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>프라두의 최종 제거</t>
+          <t>국제적 고립과 압박</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>O Fim de Prado</t>
+          <t>Isolamento e Pressão</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 6화</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>조세 피난처의 마지막 은닉 구조가 드러나고, 프라두가 출국 직전 공항에서 체포된다.</t>
+          <t>무역협정 중단과 자본 유출, 헤알화 급락이 몰아치는 가운데 국방장관이 사임한다.</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr"/>
@@ -28493,27 +28497,27 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 8화</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>브랑당의 최후</t>
+          <t>프라두의 최종 제거</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>O Fim de Brandão</t>
+          <t>O Fim de Prado</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 8화</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>오타비우 청부금의 송금 사슬이 루시아 실종일과 겹치고 유해가 발견된다. 브랑당은 사임한다.</t>
+          <t>조세 피난처의 마지막 은닉 구조가 드러나고, 프라두가 출국 직전 공항에서 체포된다.</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr"/>
@@ -28521,27 +28525,27 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 9화</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>대의의 완성</t>
+          <t>브랑당의 최후</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>A Obra Concluída</t>
+          <t>O Fim de Brandão</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 9화</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>사법개혁·GLO 의회 승인·공설변호인청 예산 자율을 묶은 개헌안이 통과된다. 자기 정부를 묶는 조항은 하파 자신이 요구했다.</t>
+          <t>오타비우 청부금의 송금 사슬이 루시아 실종일과 겹치고 유해가 발견된다. 브랑당은 사임한다.</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr"/>
@@ -28549,27 +28553,27 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>5부 10화</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>파벨라의 새벽</t>
+          <t>대의의 완성</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>A Madrugada no Morro</t>
+          <t>A Obra Concluída</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 10화</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>남동부 한 주 경찰의 파벨라 소탕 작전으로 수십 명이 죽고, 연방 법의학 조사를 보낸 하파와 주지사가 권한을 두고 충돌한다.</t>
+          <t>사법개혁·GLO 의회 승인·공설변호인청 예산 자율을 묶은 개헌안이 통과된다. 자기 정부를 묶는 조항은 하파 자신이 요구했다.</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr"/>
@@ -28577,73 +28581,73 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>파벨라의 새벽</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>A Madrugada no Morro</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>남동부 한 주 경찰의 파벨라 소탕 작전으로 수십 명이 죽고, 연방 법의학 조사를 보낸 하파와 주지사가 권한을 두고 충돌한다.</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>경고등</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>O Sinal de Alerta</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>새 정보청장 구르겔이 예비역 장교·민병대·불복 단체방을 잇는 보고서를 올리지만, 증거는 아직 흐릿하다.</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>6부 1화</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>민병대의 도시</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>A Cidade da Milícia</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>수도권 위성도시 파벨라에서 파벌과 민병대가 가스·인터넷·통근 밴을 두고 다투고, 하파는 도나 테레자의 라디오 방송을 직접 듣는다.</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>6부 2화</t>
+          <t>6부 1화</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>테레자의 라디오</t>
+          <t>민병대의 도시</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>A Rádio de Dona Tereza</t>
+          <t>A Cidade da Milícia</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
@@ -28653,7 +28657,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>파벌과 민병대 양쪽의 ‘보호’를 거부하고 민병대 비리를 방송하던 도나 테레자가 출근길에 총격으로 숨진다.</t>
+          <t>수도권 위성도시 파벨라에서 파벌과 민병대가 가스·인터넷·통근 밴을 두고 다투고, 하파는 도나 테레자의 라디오 방송을 직접 듣는다.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -28661,17 +28665,17 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>6부 3화</t>
+          <t>6부 2화</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>민병대와 의원들</t>
+          <t>테레자의 라디오</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Milícia e Mandato</t>
+          <t>A Rádio de Dona Tereza</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
@@ -28681,7 +28685,7 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>테레자 살해 수사가 민병대 두목과 주 의원, 불복 운동 자금책을 잇는 선을 드러낸다.</t>
+          <t>파벌과 민병대 양쪽의 ‘보호’를 거부하고 민병대 비리를 방송하던 도나 테레자가 출근길에 총격으로 숨진다.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -28689,27 +28693,27 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>6부 4화</t>
+          <t>6부 3화</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>병영 앞 천막</t>
+          <t>민병대와 의원들</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>O Acampamento</t>
+          <t>Milícia e Mandato</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>5부 7화 확장</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>대선 불복 시민들이 병영 앞에 천막을 치고 군의 개입을 요구하며, 예비역 장교 단체방이 들끓는다.</t>
+          <t>테레자 살해 수사가 민병대 두목과 주 의원, 불복 운동 자금책을 잇는 선을 드러낸다.</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -28717,17 +28721,17 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>6부 5화</t>
+          <t>6부 4화</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>군 내부의 균열</t>
+          <t>병영 앞 천막</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>A Fissura nos Quartéis</t>
+          <t>O Acampamento</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
@@ -28737,7 +28741,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>한 대령이 쿠데타 계획 문건을 들고 구르겔을 찾아오고, 합참의장은 침묵을 택한다.</t>
+          <t>대선 불복 시민들이 병영 앞에 천막을 치고 군의 개입을 요구하며, 예비역 장교 단체방이 들끓는다.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -28745,17 +28749,17 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>6부 6화</t>
+          <t>6부 5화</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>점거 전야</t>
+          <t>군 내부의 균열</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>A Véspera</t>
+          <t>A Fissura nos Quartéis</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
@@ -28765,7 +28769,7 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>모라이스 레아우 자회사가 대금을 댄 버스 수백 대가 수도로 향하고, 수도 경비 책임자가 방어선을 절반으로 줄인 사실이 드러난다.</t>
+          <t>한 대령이 쿠데타 계획 문건을 들고 구르겔을 찾아오고, 합참의장은 침묵을 택한다.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -28773,17 +28777,17 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>6부 7화</t>
+          <t>6부 6화</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>삼권의 밤</t>
+          <t>점거 전야</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>A Noite dos Três Poderes</t>
+          <t>A Véspera</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
@@ -28793,7 +28797,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>불복 군중이 의회·대법원·대통령궁을 점거해 부수고, 하파는 ‘방위 상태’ 선포 요구를 받는다.</t>
+          <t>모라이스 레아우 자회사가 대금을 댄 버스 수백 대가 수도로 향하고, 수도 경비 책임자가 방어선을 절반으로 줄인 사실이 드러난다.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -28801,17 +28805,17 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>6부 8화</t>
+          <t>6부 7화</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>새벽의 몇 시간</t>
+          <t>삼권의 밤</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>As Horas da Madrugada</t>
+          <t>A Noite dos Três Poderes</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
@@ -28821,7 +28825,7 @@
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>명령을 거부한 장교와 대법원장, 루아나가 버티는 사이 하파는 헌법 절차만으로 청사를 되찾는다.</t>
+          <t>불복 군중이 의회·대법원·대통령궁을 점거해 부수고, 하파는 ‘방위 상태’ 선포 요구를 받는다.</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr"/>
@@ -28829,27 +28833,27 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>6부 9화</t>
+          <t>6부 8화</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>사면은 없다</t>
+          <t>새벽의 몇 시간</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Sem Anistia</t>
+          <t>As Horas da Madrugada</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 7화 확장</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>사면 법안과 보복 입법을 모두 물리치자, 외국 정부가 재판을 ‘마녀사냥’이라 부르며 관세와 대법관 제재로 압박한다.</t>
+          <t>명령을 거부한 장교와 대법원장, 루아나가 버티는 사이 하파는 헌법 절차만으로 청사를 되찾는다.</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -28857,17 +28861,17 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>6부 10화</t>
+          <t>6부 9화</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>돈의 지도</t>
+          <t>사면은 없다</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>O Mapa do Dinheiro</t>
+          <t>Sem Anistia</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
@@ -28877,7 +28881,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>테레자 살해와 점거 자금이 이르만다지 두 노르치의 주유소 체인과 무허가 핀테크로 세탁돼 옛 정보기관의 ‘지갑’에 닿은 흔적을 벤자밍이 찾는다.</t>
+          <t>사면 법안과 보복 입법을 모두 물리치자, 외국 정부가 재판을 ‘마녀사냥’이라 부르며 관세와 대법관 제재로 압박한다.</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr"/>
@@ -28885,27 +28889,27 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>6부 11화</t>
+          <t>6부 10화</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>개혁의 피로</t>
+          <t>돈의 지도</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>O Cansaço das Reformas</t>
+          <t>O Mapa do Dinheiro</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>연금 수급자 부정 공제 파문, 불법 채굴 단속으로 일자리를 잃은 금광촌, 끝없는 재판 뉴스 속에 지지율이 떨어진다.</t>
+          <t>테레자 살해와 점거 자금이 이르만다지 두 노르치의 주유소 체인과 무허가 핀테크로 세탁돼 옛 정보기관의 ‘지갑’에 닿은 흔적을 벤자밍이 찾는다.</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr"/>
@@ -28913,83 +28917,83 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
+          <t>6부 11화</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>개혁의 피로</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>O Cansaço das Reformas</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>연금 수급자 부정 공제 파문, 불법 채굴 단속으로 일자리를 잃은 금광촌, 끝없는 재판 뉴스 속에 지지율이 떨어진다.</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
           <t>6부 12화</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B133" s="9" t="inlineStr">
         <is>
           <t>재선의 기로</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>Na Encruzilhada</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>재선을 반년 앞두고 지지율이 45%로 떨어지고, 군경 사령관 출신 방송인 단타스가 부상한다.</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>7부 1화</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>거짓의 기계</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>A Máquina de Mentiras</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>6부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>단타스의 치안 공세와 딥페이크, 돈 받은 가짜 증인이 몰아치고 루아나가 처음 단독 유세에 나선다.</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="F133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>7부 2화</t>
+          <t>7부 1화</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>유세장 테러</t>
+          <t>경제 실책 공방</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>O Atentado no Comício</t>
+          <t>A Batalha dos Números</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>6부 6화</t>
+          <t>6부 1화 변형</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>레시피의 1만 5천 명 유세장에서 폭탄이 터져 질다가 숨지고, 루아나가 팔을 크게 다친다.</t>
+          <t>재선을 반년 앞두고 단타스가 ‘불법 채굴 단속과 개혁이 금광촌 일자리를 없앴다’고 몰아치자, 부솔라 팀이 합법 일자리로 옮겨 간 수치로 반박하고 하파는 투표 직전 물가 상승 전망을 먼저 공개한다.</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -28997,27 +29001,27 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>7부 3화</t>
+          <t>7부 2화</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>배후와 토론</t>
+          <t>루아나의 정치 신고식</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Os Mandantes e o Debate</t>
+          <t>O Batismo de Luana</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>6부 9화 변형</t>
+          <t>6부 2화 변형</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>수사가 옛 정보기관 네트워크의 돈을 향하는 가운데, 하파는 마지막 토론에서 테러를 표로 바꾸지 않는다.</t>
+          <t>일정이 겹친 하파 대신 벨렝 유세를 맡은 루아나가 교과서 같은 원고를 버리고, 광산 폐수를 고발했다가 명예훼손으로 옥살이한 할아버지 이야기로 3천 명 앞에 선다.</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
@@ -29025,27 +29029,27 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>7부 4화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>재선의 밤</t>
+          <t>거짓의 기계</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>A Noite da Reeleição</t>
+          <t>A Máquina de Mentiras</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>6부 12화 변형</t>
+          <t>6부 3화 변형</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>여론조사가 끝까지 동률이던 박빙 결선에서 하파가 재선되고, 단타스는 패배를 인정해 제도권 야당의 길을 연다.</t>
+          <t>하파가 물가 수치 조작을 지시하는 딥페이크가 메신저 단체방을 타고 퍼지고, 그 유포망이 루시아 비방 때 쓰인 인프라와 겹친다. 하파는 ‘설탕 없는 커피가 무섭다’는 셀프 패러디로 맞선다.</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
@@ -29053,27 +29057,27 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>7부 5화</t>
+          <t>7부 4화</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>복합위기의 발생</t>
+          <t>부솔라 흔들기</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>A Crise Múltipla</t>
+          <t>O Ataque à Bússola</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>7부 2화 변형</t>
+          <t>6부 4화 변형</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고, 원자재 가격 폭락이 한꺼번에 덮친다.</t>
+          <t>‘부솔라 전 직원’이라는 남자가 방송에 나와 감사 은폐를 폭로하지만 가짜 노동수첩을 든 광고 배우로 드러나고, 질다가 처음으로 평판이 무너지는 두려움을 털어놓는다.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
@@ -29081,27 +29085,27 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>7부 5화</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>비상대권의 유혹</t>
+          <t>들어갈 수 없는 동네, 다시</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>A Tentação da Exceção</t>
+          <t>Onde Não Se Pode Entrar, de Novo</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>7부 3화</t>
+          <t>6부 5화 변형</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>하벨루 국방장관이 센치넬라 아우스트랄의 로비를 등에 업고 파벨라 무기한 GLO와 살상 군인 면책, 감청 시스템 도입을 담은 법안을 들고 온다.</t>
+          <t>파벌과 민병대가 다시 누가 파벨라와 강변 마을에서 유세할지 정하는 가운데 제가 유세단의 길을 협상하고, 다미아나·파비아누와 세베리누 장학금에 지원하려는 아루아칸 청년이 하파를 맞는다.</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr"/>
@@ -29109,27 +29113,27 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 6화</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>연기와 재갈</t>
+          <t>유세장 테러</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Adiar e Calar</t>
+          <t>O Atentado no Comício</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>7부 4화 변형</t>
+          <t>6부 6화 변형</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>보궐선거 연기안과 플랫폼 전면 차단안이 오른 날, 대법원은 플랫폼이 불법 게시물에 직접 책임진다고 판결한다.</t>
+          <t>처음으로 현장에 동행한 질다가 레시피 1만 5천 명 유세장의 폭발로 숨지고 루아나가 팔을 크게 다친다. 하파는 떠난 이들의 이름을 혼자 부른다.</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr"/>
@@ -29137,27 +29141,27 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 7화</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>컨설턴트 팀에게 부탁</t>
+          <t>배후 수사</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Um Pedido à Bússola</t>
+          <t>A Investigação</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>6부 7화 변형</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>수출 장갑차가 외국 시위 진압에 쓰인 사실과 센치넬라 아우스트랄의 과다 계약을 밝힌 조달 비리 보고서를 미뤄 달라는 하파의 부탁을 카이우가 거절한다.</t>
+          <t>설치범이 체포되고 벤자밍이 추적한 암호화폐 지갑이 오타비우 청부와 루시아 감시에 돈을 댄 옛 정보기관 인프라에 닿는다. 단타스 후원 재단의 설립자가 옥중의 전 세하 파리마 주지사 측근으로 드러난다.</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr"/>
@@ -29165,27 +29169,27 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>7부 9화</t>
+          <t>7부 8화</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>작은 월권</t>
+          <t>단타스의 배후</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Um Pequeno Excesso</t>
+          <t>Quem Está Por Trás de Dantas</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>6부 8화 변형</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>하파가 한때 자신이 봉인해 준 ‘비지아’로 영장 없는 감청 한 건을 구두로 허락하고, 그 사실이 청문회에서 드러난다.</t>
+          <t>단타스의 ‘독립 전략가’가 교도소를 드나든 반란 주지사의 옛 보좌관이고 선거자금 30% 이상이 구체제망에서 왔음이 드러나지만, 루아나는 비난 대신 공개 질의를 고집한다.</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr"/>
@@ -29193,27 +29197,27 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>7부 10화</t>
+          <t>7부 9화</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>루아나의 정면 대결</t>
+          <t>TV 토론</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>O Confronto de Luana</t>
+          <t>O Debate Decisivo</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>6부 9화 변형</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>하벨루가 비상 치안 체계의 상설화를 밀자 루아나와 비아가 공개적으로 대통령에게 맞선다.</t>
+          <t>마지막 토론에서 단타스가 ‘파벨라 군 투입 상시화와 치안기관 권한의 일시 확대’를 내걸자, 하파는 ‘일시적 조치가 수십 년의 통제 불능을 낳는다’고 맞서고 테러를 표로 바꾸지 않는다.</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr"/>
@@ -29221,27 +29225,27 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>7부 11화</t>
+          <t>7부 10화</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>벼랑 끝의 포기</t>
+          <t>루아나의 회복</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>A Renúncia à Beira do Abismo</t>
+          <t>A Recuperação de Luana</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>7부 10화 변형</t>
+          <t>6부 10화 변형</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>세베리누의 고문실 기록을 읽은 새벽, 경찰서 습격으로 병사가 죽어도 하파는 백지 GLO를 거부한다.</t>
+          <t>퇴원한 루아나가 ‘1미터 차이로 살았다’는 죄책감과 폭발음 플래시백에 시달리고, 병문안 온 아나가 남편을 잃은 뒤에도 매일 아침 일어났다고 말한다. 루아나는 마지막 유세에 서기로 한다.</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr"/>
@@ -29249,83 +29253,83 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
+          <t>7부 11화</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>첫 임기의 결산</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>O Balanço do Primeiro Mandato</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>6부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>투표 전야, 공설변호인청 예산 자율과 실소유자 공개법이 이미 뿌리내렸음을 확인한 팀이 ‘져도 제도는 남는다’고 말하고, 단타스와 하파가 전화로 서로를 존중한다. 어머니는 ‘무엇이 되든 자랑스럽다’고 한다.</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
           <t>7부 12화</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>새로운 균형</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>Um Novo Equilíbrio</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>7부 12화</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>인질이 풀려나고, 하파는 모든 군 투입을 의회 승인·기한·공설변호인 입회에 묶는 위기결정위원회 법으로 비상권한을 스스로 묶기로 한다.</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>권력의 한계</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>Os Limites do Poder</t>
-        </is>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="E145" s="9" t="inlineStr">
-        <is>
-          <t>위기결정위원회 법 통과 직후, 하파가 「권력의 한계」 법안 착수를 대국민 발표한다.</t>
-        </is>
-      </c>
-      <c r="F145" s="9" t="inlineStr"/>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>재선의 밤</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>A Noite da Reeleição</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>6부 12화 변형</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>끝까지 박빙이던 결선에서 하파가 재선되고, 먼저 전화해 패배를 인정한 단타스는 제도권 야당의 길을 연다. 하파는 ‘기쁨은 덜하고 책임은 더 크다’고 말한다.</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>8부 2화</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>팀의 재편</t>
+          <t>두 번째 임기의 시작</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>A Equipe Refeita</t>
+          <t>O Início do Segundo Mandato</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>8부 2화</t>
+          <t>7부 1화 변형</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>38명이 된 재정투명성청을 재편하다가, 질다의 카드 ‘커피를 잊지 말 것’이 처음 발견된다.</t>
+          <t>환희보다 결의가 앞선 두 번째 취임식. 하파는 죽은 이들의 이름에 질다를 더하고, 치우지 않은 질다의 책상을 남긴 채 루아나를 수석장관(카자 시비우)으로 임명한다.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -29333,27 +29337,27 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>8부 3화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>돌아온 병사들</t>
+          <t>복합위기의 발생</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>Os Que Voltaram</t>
+          <t>A Crise Múltipla</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>8부 3화 변형</t>
+          <t>7부 2화 변형</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>18개월 파벨라 GLO가 끝나 군이 철수하고, 귀환 병사들의 트라우마와 주민들의 기억이 새 숙제가 된다.</t>
+          <t>이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고 원자재 가격이 폭락한다. 하벨루 국방장관이 ‘치안 정상화까지’ 대통령 권한 확대안을 처음 내밀자 하파는 ‘검토하겠다’고 답한다.</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
@@ -29361,27 +29365,27 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>8부 4화</t>
+          <t>8부 3화</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>세대교체</t>
+          <t>비상대권의 유혹</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>A Troca de Gerações</t>
+          <t>A Tentação da Exceção</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>8부 4화</t>
+          <t>7부 3화 변형</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>핵심 요직 12자리를 익명 공모로 뽑고, 강마을 출신 청년 알리니와 빌라 히반세이라의 제가 지원서를 낸다.</t>
+          <t>하벨루가 센치넬라 아우스트랄의 장갑차 조달과 ‘비지아’ 영장 없는 감청을 끼운 파벨라 무기한 GLO·작전 중 살상 군인 면책 법안을 들고 오고, 안셀무는 그 법을 옹호하는 자신에게 놀란다.</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr"/>
@@ -29389,27 +29393,27 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>브랑당의 마지막 대화</t>
+          <t>연기의 논리</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>A Última Conversa com Brandão</t>
+          <t>A Lógica do Adiamento</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>7부 4화 변형</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>병든 브랑당을 찾아가 ‘비지아’를 비롯한 감시 체계 해체와 군정 기록 공개, 루시아 사건 방조를 마지막으로 묻는다.</t>
+          <t>파벌 영향 아래 시장이 궐위된 지자체들의 재선거(eleição suplementar)를 ‘치안 안정 때까지’ 미루자는 안이 오르고, 루아나가 메이렐리스의 ‘자유’ 시구로 반격한다.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -29417,27 +29421,27 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>8부 6화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>루아나에게 실권 위임</t>
+          <t>재갈의 유혹</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>O Poder nas Mãos de Luana</t>
+          <t>A Tentação da Mordaça</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>8부 6화</t>
+          <t>7부 5화 변형</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>노후 송전망 붕괴로 북부 주가 암흑에 빠지고, 하파는 루아나에게 실권을 넘긴다.</t>
+          <t>메신저 허위정보로 사재기와 피난이 번지자 하벨루가 행정부 위원회의 플랫폼 차단 권한을 요구한다. 루아나는 루시아를 불러내고, 대법원은 플랫폼의 직접 책임을 판결한다.</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr"/>
@@ -29445,27 +29449,27 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>8부 6화</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>세하 파리마의 빚</t>
+          <t>카이우에게 한 부탁</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>As Dívidas de Serra Parima</t>
+          <t>Um Pedido a Caio</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>7부 6화 변형</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>숨은 보증채무가 드러난 세하 파리마주에서 마릴리아가 주지사로 당선돼 부채를 공개한다.</t>
+          <t>카이우의 조달 감사가 센치넬라 아우스트랄 장갑차의 40% 부풀린 단가와 수출 장갑차의 외국 시위 진압 사용을 밝히자, 하파가 휴전 협상을 이유로 공개를 3주 미뤄 달라 부탁하고 카이우가 거절한다.</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr"/>
@@ -29473,27 +29477,27 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 7화</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>마지막 정치적 결전</t>
+          <t>작은 월권</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>O Último Combate</t>
+          <t>Um Pequeno Excesso</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>7부 7화 변형</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>구체제 잔존 세력이 대법원·의회·방송·검찰에서 총공세를 펴고, 카이우가 옛 과오를 고백한 뒤 쓰러진다.</t>
+          <t>파벌의 호송차 습격 첩보에 40분이 주어지자 하파는 한때 자신이 봉인해 준 ‘비지아’로 영장 없는 감청 한 건을 구두로 허락하고, 하루 만에 새어 나가 청문회에 불려 나온다.</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr"/>
@@ -29501,27 +29505,27 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>8부 8화</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>법안의 최종 완성</t>
+          <t>루아나의 정면 대결</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>A Lei Concluída</t>
+          <t>O Confronto de Luana</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>7부 8화 변형</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>「권력의 한계」법이 서명되고, 두 번의 임기 뒤 평생 재출마 금지 조항을 하파가 스스로 넣는다.</t>
+          <t>하벨루가 ‘사후 72시간 통보’ 상설 신속대응 체계를 밀자 루아나와 비아가 공개적으로 맞선다. ‘당신은 편안함을 필요라 부르는 지친 사람이 되어 간다.’</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr"/>
@@ -29529,27 +29533,27 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>8부 9화</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>질다를 기리며</t>
+          <t>세베리누의 편지</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>Em Memória de Zilda</t>
+          <t>A Carta de Severino</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>7부 9화 변형</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>추모의 밤, 하파는 ‘커피를 잊지 말 것’이 세베리누의 원칙과 같았음을 깨닫는다.</t>
+          <t>조라이지가 군정기 변론 기록과 함께 세베리누가 ‘언젠가 그 자리에 앉을 사람에게’ 쓴 미발송 편지를 건넨다. ‘너는 지칠 것이고 쉬운 길을 찾을 것이다.’</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr"/>
@@ -29557,27 +29561,27 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 10화</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>프라두 판결</t>
+          <t>벼랑 끝의 포기</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>A Sentença de Prado</t>
+          <t>A Renúncia à Beira do Abismo</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>7부 10화 변형</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>프라두에게 유죄가 선고되고 해외 자산이 환수되며, NGO 낙인법 폐지 논의가 시작된다.</t>
+          <t>파벌이 경찰서 세 곳을 동시에 습격해 병사가 죽고 인질이 잡힌 밤, 하벨루가 내민 백지 GLO 서명 앞에서 하파는 먼저 루아나에게 전화하고 기존 권한 안의 제한적 작전과 새벽 의회 긴급회의를 택한다.</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr"/>
@@ -29585,83 +29589,83 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
+          <t>8부 11화</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>정치적 대가</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>O Preço Político</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>7부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>인질이 풀려나지만 여론은 ‘우유부단’과 ‘확전 방지’로 반반 갈리고, 재정투명성청은 전면 GLO의 비용을 공개한다. 하파는 TV로 직접 설명하고 루아나와 파벨라를 찾는다.</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
           <t>8부 12화</t>
         </is>
       </c>
-      <c r="B156" s="9" t="inlineStr">
-        <is>
-          <t>질다를 죽인 돈</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
-        <is>
-          <t>O Dinheiro Que Matou Zilda</t>
-        </is>
-      </c>
-      <c r="D156" s="9" t="inlineStr">
-        <is>
-          <t>8부 12화</t>
-        </is>
-      </c>
-      <c r="E156" s="9" t="inlineStr">
-        <is>
-          <t>민간은행 장부와 파벌의 주유소·핀테크 세탁망, 레오노르가 넘긴 마레 아우타의 옛 플랫폼 리베이트 계좌가 테러 자금의 주인으로 오타실리우를 가리키지만, 그는 해외로 빠져나간다.</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>마지막 해</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>O Último Ano</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>임기 1년을 남기고 단타스가 야당 지도자로 돌아오며, ‘누가 다음인가’가 떠오른다.</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>새로운 균형</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Um Novo Equilíbrio</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>7부 12화 변형</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>하파가 모든 군 투입을 의회 승인·기한·사법 통제·공설변호인 입회에 묶는 위기결정위원회 법을 제안하고, ‘이 위원회가 나도 막아 줬을 것’이라 인정한 하벨루가 군 대표로 참여한다.</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>9부 2화</t>
+          <t>9부 1화</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>불타는 숲</t>
+          <t>권력의 한계</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>A Floresta em Chamas</t>
+          <t>Os Limites do Poder</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>9부 2화 변형</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>강이 역대 최저 수위로 마르고 아루아칸 영토가 불타는데 국제 산림기금 약속은 절반에 그치자, 하파가 귀향한다.</t>
+          <t>위기결정위원회 법 통과 직후, 하파가 「권력의 한계」 법안 착수를 대국민 발표한다.</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
@@ -29669,27 +29673,27 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>9부 3화</t>
+          <t>9부 2화</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>낙인</t>
+          <t>팀의 재편</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>O Estigma</t>
+          <t>A Equipe Refeita</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>9부 3화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>외국 후원 NGO 등록·낙인법이 최종 폐지되고, 루아나가 첫 독자 정치 행보를 한다.</t>
+          <t>38명이 된 재정투명성청을 재편하다가, 질다의 카드 ‘커피를 잊지 말 것’이 처음 발견된다.</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
@@ -29697,27 +29701,27 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>9부 4화</t>
+          <t>9부 3화</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>병사의 재판</t>
+          <t>돌아온 병사들</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>O Julgamento do Soldado</t>
+          <t>Os Que Voltaram</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>9부 4화 변형</t>
+          <t>8부 3화 변형</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>GLO 작전 중 파벨라 소년을 쏜 귀환 병사가 일반 법원에 서고, 하파는 공설변호인의 눈으로 방청한다.</t>
+          <t>18개월 파벨라 GLO가 끝나 군이 철수하고, 귀환 병사들의 트라우마와 주민들의 기억이 새 숙제가 된다.</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr"/>
@@ -29725,27 +29729,27 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>9부 5화</t>
+          <t>9부 4화</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>루아나, 공식 후계자로</t>
+          <t>세대교체</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Luana, a Sucessora</t>
+          <t>A Troca de Gerações</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>9부 5화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>하파가 미뤄 둔 대화를 꺼내고, 당 예비경선에서 루아나가 공식 대선 후보로 선출된다.</t>
+          <t>핵심 요직 12자리를 익명 공모로 뽑고, 강마을 출신 청년 알리니와 빌라 히반세이라의 제가 지원서를 낸다.</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
@@ -29753,27 +29757,27 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>9부 6화</t>
+          <t>9부 5화</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>개인적 화해와 정리</t>
+          <t>브랑당의 마지막 대화</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Acertos de Contas</t>
+          <t>A Última Conversa com Brandão</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>9부 6화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>하파가 세베리누·아버지·모에마·오타비우·루시아·테레자의 무덤을 차례로 찾고, 세베리누 앞에서 처음으로 용서를 청한다.</t>
+          <t>병든 브랑당을 찾아가 ‘비지아’를 비롯한 감시 체계 해체와 군정 기록 공개, 루시아 사건 방조를 마지막으로 묻는다.</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr"/>
@@ -29781,27 +29785,27 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 6화</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>그림자의 윤곽</t>
+          <t>루아나에게 실권 위임</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>O Contorno da Sombra</t>
+          <t>O Poder nas Mãos de Luana</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>8부 6화</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>브랑당이 홀로 숨지고, 아무도 오지 않은 장례식에 간 하파에게 자금 운반책의 이름이 든 봉투가 남는다.</t>
+          <t>노후 송전망 붕괴로 북부 주가 암흑에 빠지고, 하파는 루아나에게 실권을 넘긴다.</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
@@ -29809,27 +29813,27 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>9부 8화</t>
+          <t>9부 7화</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>임기 종료를 준비하며</t>
+          <t>세하 파리마의 빚</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Preparando a Saída</t>
+          <t>As Dívidas de Serra Parima</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>9부 8화 변형</t>
+          <t>8부 7화</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>임기 종료 114일 전, 하파는 봉투를 검찰에 넘기고 경호 강화와 비상권한 제안을 거절한다.</t>
+          <t>숨은 보증채무가 드러난 세하 파리마주에서 마릴리아가 주지사로 당선돼 부채를 공개한다.</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr"/>
@@ -29837,27 +29841,27 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>9부 8화</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>마릴리아</t>
+          <t>마지막 정치적 결전</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Marília</t>
+          <t>O Último Combate</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>8부 8화</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>결선에서 이긴 당선인 루아나가 마릴리아를 수석장관으로 택하고, 지방 출신 두 사람이 마주 앉는다.</t>
+          <t>구체제 잔존 세력이 대법원·의회·방송·검찰에서 총공세를 펴고, 카이우가 옛 과오를 고백한 뒤 쓰러진다.</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr"/>
@@ -29865,27 +29869,27 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>9부 9화</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>마지막 이양 준비</t>
+          <t>법안의 최종 완성</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Os Últimos Preparativos</t>
+          <t>A Lei Concluída</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>8부 9화</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>임기 마지막 날인 새해 전날 밤, 경호를 줄인 채 강변을 걷던 하파가 저격당해 루아나의 품에서 숨진다.</t>
+          <t>「권력의 한계」법이 서명되고, 두 번의 임기 뒤 평생 재출마 금지 조항을 하파가 스스로 넣는다.</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr"/>
@@ -29893,27 +29897,27 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>9부 10화</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>홀로 선 자리</t>
+          <t>질다를 기리며</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>O Lugar de Quem Fica Só</t>
+          <t>Em Memória de Zilda</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>8부 10화</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>사흘 애도 뒤로 취임을 미루자는 권유를 물리치고 루아나가 1월 1일 예정대로 선서한다.</t>
+          <t>추모의 밤, 하파는 ‘커피를 잊지 말 것’이 세베리누의 원칙과 같았음을 깨닫는다.</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr"/>
@@ -29921,27 +29925,27 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>9부 12화</t>
+          <t>9부 11화</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>수사의 끝</t>
+          <t>프라두 판결</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>O Fim da Investigação</t>
+          <t>A Sentença de Prado</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>9부 12화</t>
+          <t>8부 11화</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>독립수사단·검찰·의회 조사위가 각자 절차로, 협력 진술한 피게이로의 조선소 유령회사와 파벌 세탁망을 거친 테러·암살의 돈줄을 오타실리우로 입증하고, 루아나는 개입하지 않는다.</t>
+          <t>프라두에게 유죄가 선고되고 해외 자산이 환수되며, NGO 낙인법 폐지 논의가 시작된다.</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr"/>
@@ -29949,30 +29953,394 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>9부 에필로그</t>
+          <t>9부 12화</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
+          <t>질다를 죽인 돈</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>O Dinheiro Que Matou Zilda</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>8부 12화</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>민간은행 장부와 파벌의 주유소·핀테크 세탁망, 레오노르가 넘긴 마레 아우타의 옛 플랫폼 리베이트 계좌가 테러 자금의 주인으로 오타실리우를 가리키지만, 그는 해외로 빠져나간다.</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>10부 1화</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>마지막 해</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>O Último Ano</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>9부 1화</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>임기 1년을 남기고 단타스가 야당 지도자로 돌아오며, ‘누가 다음인가’가 떠오른다.</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>10부 2화</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>불타는 숲</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>A Floresta em Chamas</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>9부 2화 변형</t>
+        </is>
+      </c>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>강이 역대 최저 수위로 마르고 아루아칸 영토가 불타는데 국제 산림기금 약속은 절반에 그치자, 하파가 귀향한다.</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>10부 3화</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>낙인</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>O Estigma</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>9부 3화</t>
+        </is>
+      </c>
+      <c r="E172" s="9" t="inlineStr">
+        <is>
+          <t>외국 후원 NGO 등록·낙인법이 최종 폐지되고, 루아나가 첫 독자 정치 행보를 한다.</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>10부 4화</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>병사의 재판</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>O Julgamento do Soldado</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>9부 4화 변형</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>GLO 작전 중 파벨라 소년을 쏜 귀환 병사가 일반 법원에 서고, 하파는 공설변호인의 눈으로 방청한다.</t>
+        </is>
+      </c>
+      <c r="F173" s="9" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>10부 5화</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>루아나, 공식 후계자로</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Luana, a Sucessora</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>9부 5화</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>하파가 미뤄 둔 대화를 꺼내고, 당 예비경선에서 루아나가 공식 대선 후보로 선출된다.</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>10부 6화</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>개인적 화해와 정리</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>Acertos de Contas</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>9부 6화</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="inlineStr">
+        <is>
+          <t>하파가 세베리누·아버지·모에마·오타비우·루시아·테레자의 무덤을 차례로 찾고, 세베리누 앞에서 처음으로 용서를 청한다.</t>
+        </is>
+      </c>
+      <c r="F175" s="9" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>10부 7화</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>그림자의 윤곽</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>O Contorno da Sombra</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>9부 7화</t>
+        </is>
+      </c>
+      <c r="E176" s="9" t="inlineStr">
+        <is>
+          <t>브랑당이 홀로 숨지고, 아무도 오지 않은 장례식에 간 하파에게 자금 운반책의 이름이 든 봉투가 남는다.</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>10부 8화</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>임기 종료를 준비하며</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>Preparando a Saída</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>9부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>임기 종료 114일 전, 하파는 봉투를 검찰에 넘기고 경호 강화와 비상권한 제안을 거절한다.</t>
+        </is>
+      </c>
+      <c r="F177" s="9" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>10부 9화</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>마릴리아</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>Marília</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>9부 9화</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>결선에서 이긴 당선인 루아나가 마릴리아를 수석장관으로 택하고, 지방 출신 두 사람이 마주 앉는다.</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>10부 10화</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>마지막 이양 준비</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>Os Últimos Preparativos</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>9부 10화</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>임기 마지막 날인 새해 전날 밤, 경호를 줄인 채 강변을 걷던 하파가 저격당해 루아나의 품에서 숨진다.</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>10부 11화</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>홀로 선 자리</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>O Lugar de Quem Fica Só</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>9부 11화</t>
+        </is>
+      </c>
+      <c r="E180" s="9" t="inlineStr">
+        <is>
+          <t>사흘 애도 뒤로 취임을 미루자는 권유를 물리치고 루아나가 1월 1일 예정대로 선서한다.</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>10부 12화</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>수사의 끝</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>O Fim da Investigação</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>9부 12화</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>독립수사단·검찰·의회 조사위가 각자 절차로, 협력 진술한 피게이로의 조선소 유령회사와 파벌 세탁망을 거친 테러·암살의 돈줄을 오타실리우로 입증하고, 루아나는 개입하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>10부 에필로그</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
           <t>연결 고리</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C182" s="9" t="inlineStr">
         <is>
           <t>O Elo</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>9부 에필로그 변형</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
+      <c r="E182" s="9" t="inlineStr">
         <is>
           <t>4년 뒤 인도된 오타실리우가 공설변호인과 함께 재판정에 서는 아침, 루아나가 임기를 마치고 마릴리아 누니스가 선서한다. 제는 공설변호인 시험에 붙는다.</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr"/>
+      <c r="F182" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -29992,8 +30360,8 @@
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A59:F59"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B5:F5"/>

--- a/기획안/국가별_각색_기획안.xlsx
+++ b/기획안/국가별_각색_기획안.xlsx
@@ -25962,12 +25962,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>노바 카라자이의 노변호사. 1부 수은 소송에서 강마을 주민과 아루아칸을 대리하는 하파의 상대편 변호인이자 뒤늦게 스승이 되는 사람. 1980년 군정 말기 댐 부실을 고발한 기술자를 변호하다 변호사회에서 제명된 과거. 적에게도 먼저 커피를 낸다</t>
+          <t>노바 카라자이의 노변호사. 1부 수은 소송에서 강마을 주민과 아루아칸을 대리하는 하파의 상대편 변호인이자 뒤늦게 스승이 되는 사람. 1980년 군정 말기 댐 부실을 고발한 기술자를 변호하다 변호사회에서 제명된 과거. 적에게도 먼저 커피를 낸다. 2000년 성당 백일장 심사위원으로 열일곱 살 하파의 글을 읽고 그의 USP 장학금(생활비 장학) 추천서에 서명한 사람이지만(1994년 제련소 사고로 해고된 니바우두의 동료 제 벤투의 변호인이기도 했다), 하파는 이를 잊었고 세베리누는 말하지 않는다. 상대편으로서 하파를 가르친다: 5화 하파 측의 서명 누락 감정서를 판사 앞에서 이용하지 않고 알려 주며 ‘제대로 이기시오(Vença direito, doutor)’, 7화 총격의 밤 ‘실력이 아니라 누구를 위해서냐가 문제’</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>1부 3화 상대편으로 첫 대면, 6화 하파가 봉인한 감청 표적 목록에 이름이 오르고, 9화 그 감청으로 ‘리스크 정보’ 업체가 만든 증인매수 자료로 날조 혐의 체포, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망. 8부 9화 조라이지가 그가 ‘언젠가 그 자리에 앉을 사람에게’ 쓴 미발송 편지를 하파에게 건넨다</t>
+          <t>1부 3화 상대편으로 첫 대면, 6화 하파가 봉인한 감청 표적 목록에 이름이 오르고, 9화 그 감청으로 ‘리스크 정보’ 업체가 만든 증인매수 자료로 날조 혐의 체포, 10화 구치소 면회에서 ‘내가 너를 거기 보낸 편지에 서명했다’고 밝히며 자기에게 불리한 녹취의 약점(잘린 통화 시간·VG 코드)을 하파에게 짚어 주고, 11화 심장약을 끊긴 구금 끝에 석방 당일 사망. 12화 조라이지가 정리하던 그의 2000년 노트에서 추천서 먹지 사본이 나온다. 8부 9화 조라이지가 그가 ‘언젠가 그 자리에 앉을 사람에게’ 쓴 미발송 편지를 하파에게 건넨다</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -27033,7 +27033,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>고향 노바 카라자이에서 상대 변호인 세베리누가 먼저 커피를 내고, 법원 계단에서는 기자 루시아가 하파를 ‘독의 변호인’이라 부른다.</t>
+          <t>고향 노바 카라자이에서 상대 변호인 세베리누가 먼저 커피를 내며 하파의 열일곱 살 시절을 아는 듯한 말을 흘리고, 법원 계단에서는 기자 루시아가 하파를 ‘독의 변호인’이라 부른다.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>수은을 채굴꾼 탓으로 돌린 감정서로 첫 판결을 이기고, 프라두가 치하하는 축하연에서 브랑당이 소개한 방산업체의 장갑차·탄약 수출 허가를 사흘 만에 받아 낸다.</t>
+          <t>선고 직전 세베리누가 하파 측 감정서의 서명 누락을 판사 앞에서 이용하지 않고 알려 주며 ‘제대로 이기시오’라 한 뒤 하파는 수은을 채굴꾼 탓으로 돌린 감정서로 첫 판결을 이기고, 프라두가 치하하는 축하연에서 브랑당이 소개한 방산업체의 장갑차·탄약 수출 허가를 사흘 만에 받아 낸다.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -27145,7 +27145,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>합의서를 받으러 간 강마을에서 손 떨리는 아이들을 보고, 아루아칸 현장검증에서 모에마와 마주한 날 숲 지킴이 청년이 총에 맞는다.</t>
+          <t>합의서를 받으러 간 강마을에서 손 떨리는 아이들을 보고, 아루아칸 현장검증에서 모에마와 마주한 날 숲 지킴이 청년이 총에 맞는다. 그날 밤 세베리누는 ‘실력이 아니라 누구를 위해서냐’고 묻는다.</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr"/>
@@ -27229,7 +27229,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>플랫폼 리베이트로 조선소를 비운 ‘자문회사’ 채권은 살리고 임금은 깎은 회생안이 통과된 주, 하파는 2013년 수은 보고서를 찾고 구치소의 세베리누는 커피를 먼저 민다.</t>
+          <t>플랫폼 리베이트로 조선소를 비운 ‘자문회사’ 채권은 살리고 임금은 깎은 회생안이 통과된 주, 하파는 2013년 수은 보고서를 찾고, 구치소의 세베리누는 커피를 먼저 밀며 열일곱 살 하파의 장학금 추천서에 서명한 사람이 자신이었음을 밝히고 자기에게 불리한 녹취의 약점(잘린 통화 시간·VG 코드)을 짚어 준다.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -27285,7 +27285,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>장례식에서 무심코 조문객에게 커피를 낸 하파가 네 고객의 이름을 적은 사직서를 레오노르에게 내고, 아버지와 오타비우가 말린다.</t>
+          <t>장례식에서 무심코 조문객에게 커피를 낸 하파가 조라이지가 건넨 장학금 추천서 먹지 사본을 품고 네 고객의 이름을 적은 사직서를 레오노르에게 내고, 아버지와 오타비우가 말린다.</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr"/>

--- a/기획안/국가별_각색_기획안.xlsx
+++ b/기획안/국가별_각색_기획안.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 8부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
+          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 8부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 하파 자신이 5부에서 헌법에 넣은 GLO 족쇄(24시간 안 의회 제출·10일 미승인 시 실효·최장 60일)를 비켜 가는 길 — ‘조직범죄 분쟁지역’에 한해 기한 조항을 정지하는 긴급 개헌, 60일마다 같은 명령을 새로 내는 연속 재발령, GLO가 아닌 ‘연방 신속지원대’ 상설화 — 에 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 묶어 요구한다. 그를 막는 것은 상대편이 아니라 자기가 만든 조항이다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -26543,7 +26543,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="360" customHeight="1">
+    <row r="7" ht="375" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>기획 대비 변경</t>
@@ -26559,7 +26559,7 @@
 · 브랑당 사임 사유 → 2018년 감시팀 보고서를 받고도 알리지 않은 ‘침묵’의 책임(방조), 연방경찰 참고인 신분
 · 4부 가상 정권 인물 신설 → 대통령 헤난 마르사우·수석장관 아밀통 비지가우·승계 대통령 셀리우 아라강, 결선 상대는 단타스가 아니라 상원의원 마르시우 포르텔라(50.3 대 49.7)
 · 주요 신규 인물 추가 → 에드바우두 핀투·소니아 게지스(공설변호인청), 데보라 나카무라(경제장관), 조제 아우구스투 테이세이라(법무장관), 아니바우 시케이라(국방장관, 5부 7화 사임), 에우제니우 구르겔(ANSI 청장, 5부 12화) 등
-· 공설변호인청 개헌 → ‘예산 자율·독립’이 실제 제도에 맞춰 예산 하한과 연방 재원 이전으로 정리되고, 5부 10화 개헌에 GLO 의회 사후 승인·기한과 판사 징계 공개가 함께 들어감(8부의 GLO 유혹은 이미 헌법화된 족쇄를 우회·완화하려는 형태로 써야 함)
+· 공설변호인청 개헌 → ‘예산 자율·독립’이 실제 제도에 맞춰 예산 하한과 연방 재원 이전으로 정리되고, 5부 10화 개헌에 GLO 의회 사후 승인·기한과 판사 징계 공개가 함께 들어감 → 8부 기획을 이에 맞춰 수정: 유혹은 ‘무기한 GLO’가 아니라 자기가 만든 헌법 족쇄를 비켜 가는 긴급 개헌·연속 재발령·‘연방 신속지원대’ 상설화로, 해법은 그 빈틈을 막는 위기결정위원회 법으로(8부 요약, 2·3·8·10·11·12화)
 · 5부 11화 파벨라 작전 → 실제 사건과 겹치지 않게 가상 파벨라 자케이라 알타·페홀류 작전·사망 26명, 연방 이관 청구는 검찰총장 몫으로
 · 타임라인 고정 → 세베리누 2015년 11월 19일 사망, 니바우두 2018년 9월 4일, 루시아 2018년 10월 17일 실종·2024년 2월 유해 발견, 모에마 2022년 3월 20일, 오타비우 2023년 8월, 프라두 체포 2024년 1월
 · 2부 10화 대응 원작 화 → 아버지 해고와 헤나타 등 동료 이탈까지 담아 ‘2부 7·8·9화 변형’으로 수정</t>
@@ -26657,7 +26657,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="90" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>권력의 유혹</t>
@@ -26665,11 +26665,11 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 8부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 파벨라 무기한 치안유지(GLO) 군 투입, 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 한꺼번에 요구한다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="75" customHeight="1">
+          <t>두 번 온다. 6부 헌법기관 점거의 밤에는 ‘방위 상태’ 선포와 무기한 군 통치의 유혹을, 8부 이르만다지 두 노르치와 민병대의 파벨라 전쟁과 원자재 폭락 속에서는 하벨루 국방장관이 하파 자신이 5부에서 헌법에 넣은 GLO 족쇄(24시간 안 의회 제출·10일 미승인 시 실효·최장 60일)를 비켜 가는 길 — ‘조직범죄 분쟁지역’에 한해 기한 조항을 정지하는 긴급 개헌, 60일마다 같은 명령을 새로 내는 연속 재발령, GLO가 아닌 ‘연방 신속지원대’ 상설화 — 에 작전 중 살상 군인 면책, 보궐선거 연기, 플랫폼 차단, 영장 없는 감청을 묶어 요구한다. 그를 막는 것은 상대편이 아니라 자기가 만든 조항이다. 공설변호인 시절 경찰 조서 한 장으로 끌려온 파벨라 청년들을 변호하던 그가 이번엔 그 청년들의 골목에 군을 보낼 서명을 앞에 둔다. 하파는 영장 없는 감청 한 건을 구두로 허락하는 ‘작은 월권’까지 간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>자기 제한</t>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>점거의 밤에도 비상권한 없이 헌법 절차와 사법부에 수습을 맡기고, 가담자 사면 요구와 보복 입법을 모두 거부한다. 대통령으로서 가장 먼저 한 일 중 하나가 자기 정부를 상대로 소송할 수 있는 공설변호인청에 예산 하한과 연방 재원 이전(‘예산 자율’)을 주는 개헌안을 첫 법안으로 보내는 것이고(2023년 1월), 2024년 7월 판사 징계 공개·GLO 의회 사후 승인과 기한을 함께 묶은 개헌을 자기 임기부터 적용하게 한다. 8부에서 백지 GLO 서명을 거부하고 모든 군 투입을 의회 승인·기한·사법 통제·공설변호인 입회에 묶는 위기결정위원회 법을 만들며, 「권력의 한계」법에 두 번의 임기 뒤 평생 재출마 금지를 스스로 넣는다. 퇴임 직전 경호 강화와 비상권한 제안도 거절한다.</t>
+          <t>점거의 밤에도 비상권한 없이 헌법 절차와 사법부에 수습을 맡기고, 가담자 사면 요구와 보복 입법을 모두 거부한다. 대통령으로서 가장 먼저 한 일 중 하나가 자기 정부를 상대로 소송할 수 있는 공설변호인청에 예산 하한과 연방 재원 이전(‘예산 자율’)을 주는 개헌안을 첫 법안으로 보내는 것이고(2023년 1월), 2024년 7월 판사 징계 공개·GLO 의회 사후 승인과 기한을 함께 묶은 개헌을 자기 임기부터 적용하게 한다. 8부에서 기한 없는 연속 재발령 백지 명령에 서명하지 않고 헌법 조항 그대로(의회 제출·기한) 제한적 GLO만 내며, 위기결정위원회 법으로 그 조항의 빈틈(연속 재발령·‘신속지원대’ 같은 우회 명칭·사후 통보)을 스스로 막고 사법 통제와 공설변호인 입회를 시행 규정으로 채우며, 「권력의 한계」법에 두 번의 임기 뒤 평생 재출마 금지를 스스로 넣는다. 퇴임 직전 경호 강화와 비상권한 제안도 거절한다.</t>
         </is>
       </c>
     </row>
@@ -27113,7 +27113,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>1부 5화 하파가 장갑차·탄약 수출 허가를 받아 주고, 6화 같은 로비망의 ‘비지아’ 불법 감청 소송을 국가안보 기밀로 봉인해 준다. 3부 3화 오타비우의 자료에 주 경찰 시스템 유지보수 수의 계약 갱신이 나오고, 5부 7화 무역블록과의 장갑차 계약을 잃자 예비역들에게 전화를 돌린다. 8부 3화 하벨루 국방장관과 함께 파벨라 무기한 GLO·감청 시스템 도입을 로비하고, 8부 6화 수출 장갑차의 외국 시위 진압 사용과 과다 계약이 카이우의 보고서로 드러나며, 8부 7화 하파가 바로 그 ‘비지아’로 영장 없는 감청 한 건을 허락한다. 9부 5화 ‘비지아’ 해체와 함께 불구속 기소</t>
+          <t>1부 5화 하파가 장갑차·탄약 수출 허가를 받아 주고, 6화 같은 로비망의 ‘비지아’ 불법 감청 소송을 국가안보 기밀로 봉인해 준다. 3부 3화 오타비우의 자료에 주 경찰 시스템 유지보수 수의 계약 갱신이 나오고, 5부 7화 무역블록과의 장갑차 계약을 잃자 예비역들에게 전화를 돌린다. 8부 3화 하벨루 국방장관과 함께 GLO 기한 정지 개헌·감청 시스템 도입을 로비하고, 8부 6화 수출 장갑차의 외국 시위 진압 사용과 과다 계약이 카이우의 보고서로 드러나며, 8부 7화 하파가 바로 그 ‘비지아’로 영장 없는 감청 한 건을 허락한다. 9부 5화 ‘비지아’ 해체와 함께 불구속 기소</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -28244,7 +28244,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>두 번째 임기 초 파벌과 민병대의 전쟁이 여러 도시로 번지고 원자재 가격이 폭락하자, 하벨루 국방장관과 방산업체 센치넬라 아우스트랄이 파벨라 무기한 GLO·군인 면책·재선거 연기·플랫폼 차단·영장 없는 감청을 한 묶음으로 내민다. 하파는 카이우의 장갑차 보고서를 미뤄 달라 부탁하고 한때 자신이 봉인해 준 ‘비지아’로 한 번 선을 넘지만, 루아나의 정면 대결과 세베리누의 미발송 편지 끝에 백지 GLO 서명을 거부하고 위기결정위원회 법으로 비상권한을 스스로 묶는다.</t>
+          <t>두 번째 임기 초 파벌과 민병대의 전쟁이 여러 도시로 번지고 원자재 가격이 폭락하자, 하벨루 국방장관과 방산업체 센치넬라 아우스트랄이 하파 자신이 2024년 헌법에 넣은 GLO 족쇄(의회 24시간 제출·10일 실효·최장 60일)를 비켜 갈 묶음 — 분쟁지역 기한 정지 긴급 개헌, 연속 재발령, ‘연방 신속지원대’ 상설화, 군인 면책·재선거 연기·플랫폼 차단·영장 없는 감청 — 을 내민다. 하파는 카이우의 장갑차 보고서를 미뤄 달라 부탁하고 한때 자신이 봉인해 준 ‘비지아’로 한 번 선을 넘지만, 루아나의 정면 대결과 세베리누의 미발송 편지 끝에 기한 없는 백지 명령을 거부하고 헌법 조항 안의 제한적 작전을 택한 뒤, 위기결정위원회 법으로 자기 조항의 빈틈까지 막는다.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -30999,7 +30999,7 @@
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고 원자재 가격이 폭락한다. 하벨루 국방장관이 ‘치안 정상화까지’ 대통령 권한 확대안을 처음 내밀자 하파는 ‘검토하겠다’고 답한다.</t>
+          <t>이르만다지 두 노르치와 민병대의 전쟁이 여러 도시 파벨라로 번지고 원자재 가격이 폭락한다. 하벨루 국방장관이 ‘60일로는 골목 하나도 못 되찾는다’며 2024년 GLO 조항의 기한부터 손보자고 처음 내밀자 하파는 ‘검토하겠다’고 답한다.</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr"/>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>하벨루가 센치넬라 아우스트랄의 장갑차 조달과 ‘비지아’ 영장 없는 감청을 끼운 파벨라 무기한 GLO·작전 중 살상 군인 면책 법안을 들고 오고, 안셀무는 그 법을 옹호하는 자신에게 놀란다.</t>
+          <t>하벨루가 ‘조직범죄 분쟁지역’에 한해 GLO 기한·의회 실효 조항을 정지하는 긴급 개헌안에 작전 중 살상 군인 면책, 센치넬라 아우스트랄 장갑차 조달, ‘비지아’ 영장 없는 감청을 끼워 들고 오고, 안셀무는 자기가 표결했던 조항을 허무는 법을 옹호하는 자신에게 놀란다.</t>
         </is>
       </c>
       <c r="F172" s="10" t="inlineStr"/>
@@ -31167,7 +31167,7 @@
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>하벨루가 ‘사후 72시간 통보’ 상설 신속대응 체계를 밀자 루아나와 비아가 공개적으로 맞선다. ‘당신은 편안함을 필요라 부르는 지친 사람이 되어 간다.’</t>
+          <t>개헌이 막히자 하벨루가 GLO가 아닌 ‘연방 신속지원대’를 상설화해 헌법 조항 밖에서 ‘사후 72시간 통보’로 움직이자는 안을 밀고, 루아나와 비아가 ‘이름만 바꾼 GLO’라며 공개적으로 맞선다. ‘당신은 편안함을 필요라 부르는 지친 사람이 되어 간다.’</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr"/>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>파벌이 경찰서 세 곳을 동시에 습격해 병사가 죽고 인질이 잡힌 밤, 하벨루가 내민 백지 GLO 서명 앞에서 하파는 먼저 루아나에게 전화하고 기존 권한 안의 제한적 작전과 새벽 의회 긴급회의를 택한다.</t>
+          <t>파벌이 경찰서 세 곳을 동시에 습격해 병사가 죽고 인질이 잡힌 밤, 하벨루가 60일마다 자동으로 다시 내도록 날짜를 비워 둔 연속 재발령 GLO 명령서를 내밀지만, 하파는 먼저 루아나에게 전화하고 헌법 조항 그대로 24시간 안 의회 제출·30일 시한의 제한적 GLO에 서명한 뒤 새벽 의회 긴급회의를 부른다.</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr"/>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
-          <t>인질이 풀려나지만 여론은 ‘우유부단’과 ‘확전 방지’로 반반 갈리고, 재정투명성청은 전면 GLO의 비용을 공개한다. 하파는 TV로 직접 설명하고 루아나와 파벨라를 찾는다.</t>
+          <t>인질이 풀려나지만 여론은 ‘우유부단’과 ‘확전 방지’로 반반 갈리고, 의회는 제한적 GLO를 8일째 승인하며 재정투명성청은 무기한 작전의 비용을 공개한다. 하파는 TV로 직접 설명하고 루아나와 파벨라를 찾는다.</t>
         </is>
       </c>
       <c r="F180" s="10" t="inlineStr"/>
@@ -31279,7 +31279,7 @@
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>하파가 모든 군 투입을 의회 승인·기한·사법 통제·공설변호인 입회에 묶는 위기결정위원회 법을 제안하고, ‘이 위원회가 나도 막아 줬을 것’이라 인정한 하벨루가 군 대표로 참여한다.</t>
+          <t>하파가 2024년 GLO 조항의 빈틈 — 연속 재발령, ‘신속지원대’ 같은 우회 명칭, 사후 통보 — 를 막고 사법 통제·공설변호인 입회를 시행 규정으로 채우는 위기결정위원회 법을 제안하고, ‘이 위원회가 나도 막아 줬을 것’이라 인정한 하벨루가 군 대표로 참여한다.</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr"/>
